--- a/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
+++ b/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="505">
   <si>
     <t xml:space="preserve">DETAILED QUANTITY TAKEOFF — EXTERIOR ELECTRICAL &amp; COMMUNICATIONS</t>
   </si>
@@ -35,7 +35,7 @@
     <t xml:space="preserve">Basis: 65% Submittal QC set (Kenall-FSC JV / HDR, issue date Sept 02 2026; elec sheets dated Feb 23 2026) — Contract W9128F24D0010. NOT FOR CONSTRUCTION.</t>
   </si>
   <si>
-    <t xml:space="preserve">Scope per direction: EXTERIOR electrical &amp; communications only (ES/E, TSN, TSY series). Civil, wet utilities, fire protection &amp; building interior systems excluded.</t>
+    <t xml:space="preserve">Scope per direction: EXTERIOR electrical &amp; communications only (ES/E, TSN, TSY series + CD101 demo). Civil, wet utilities, fire protection &amp; building interior systems excluded.</t>
   </si>
   <si>
     <t xml:space="preserve">TOTALS BY SYSTEM</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">Remarks</t>
   </si>
   <si>
-    <t xml:space="preserve">Site Electrical (power, lighting, generator, service)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-001, ES101, ES601</t>
+    <t xml:space="preserve">Site Electrical (power, lighting, generator, service, demo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-001, ES101, ES601, CD101</t>
   </si>
   <si>
     <t xml:space="preserve">Utility primary &amp; transformer by Xcel Energy; lighting branch circuits carried as allowance (not drawn at 65%).</t>
@@ -104,10 +104,16 @@
     <t xml:space="preserve">Open question / QC-comment risk — verify before bid (see notes column).</t>
   </si>
   <si>
+    <t xml:space="preserve">Size &amp; Type columns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sizes and types/materials/models are from drawing schedules &amp; details; entries marked '(assumed)' or 'TBD' are not on the 65% drawings — confirm in specs or next submittal.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Basis column</t>
   </si>
   <si>
-    <t xml:space="preserve">Counted = symbol count from plan · Dimensioned = printed plan dimension · Scaled = measured at 1"=30' · Allowance = not shown at 65% · By Others-NIC = coordination only, no direct cost unless priced · Calc = formula-driven from other rows.</t>
+    <t xml:space="preserve">Counted = symbol count from plan · Dimensioned = printed plan dimension · Scaled = measured at 1"=30' · Allowance = not shown at 65% · By Others-NIC = coordination only · Calc = formula-driven from other rows.</t>
   </si>
   <si>
     <t xml:space="preserve">Example</t>
@@ -122,7 +128,7 @@
     <t xml:space="preserve">1. Site photometric plan to be added (QC on ES101) — fixture counts/locations may change; one EA1 pole flagged for relocation (fire-truck access conflict near relocated generator).</t>
   </si>
   <si>
-    <t xml:space="preserve">2. Site lighting branch circuiting, panel sources &amp; one-line references are not in the site set — carried as allowances.</t>
+    <t xml:space="preserve">2. Site lighting branch circuiting, panel sources &amp; one-line references are not in the site set — carried as allowances; conduit/wire sizes assumed and so noted.</t>
   </si>
   <si>
     <t xml:space="preserve">3. TSN100 duct bank overall dim 508'-8 3/4" at HH1-6 does not reconcile with segment dims (sums ±300 LF) — RFI recommended.</t>
@@ -137,13 +143,16 @@
     <t xml:space="preserve">6. Civil background on TSN100/TSY100 to be updated to most current — handhole/pedestal positions (HH1-1 labeling) to be confirmed.</t>
   </si>
   <si>
-    <t xml:space="preserve">7. OSP copper backbone questioned on TSN300 ('Where is the OSP copper?') — matrix lists it as contractor scope; allowance carried.</t>
+    <t xml:space="preserve">7. OSP copper backbone questioned on TSN300 ('Where is the OSP copper?') — matrix lists it as contractor scope; allowance carried, pair count TBD.</t>
   </si>
   <si>
     <t xml:space="preserve">8. Demarcation between Xcel Energy work and contract work to be documented in Design Analysis (QC on ES101) — primary work carried as NIC.</t>
   </si>
   <si>
-    <t xml:space="preserve">SITE ELECTRICAL TAKEOFF (Sheets E-001, ES101, ES601)</t>
+    <t xml:space="preserve">9. Luminaire schedule wattage/lumens/CCT columns largely blank at 65%; transformer kVA, generator kW, and secondary conductor sizes await one-line (building package).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE ELECTRICAL TAKEOFF (Sheets E-001, ES101, ES601 + CD101 demo)</t>
   </si>
   <si>
     <t xml:space="preserve">DOE Legacy Management – Site Improvement Package | 764 Horizon Dr., Grand Junction, CO | 65% Submittal (Issue 02 SEP 2026) | Contract W9128F24D0010</t>
@@ -155,6 +164,12 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
+    <t xml:space="preserve">Size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type / Material / Model No.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Ref (Sheet / Detail / Keynote)</t>
   </si>
   <si>
@@ -182,6 +197,12 @@
     <t xml:space="preserve">Remove existing utility primary conduit &amp; conductors back to splice point</t>
   </si>
   <si>
+    <t xml:space="preserve">Size unknown (existing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing UG primary conduit &amp; cable — remove &amp; dispose</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 2</t>
   </si>
   <si>
@@ -200,6 +221,12 @@
     <t xml:space="preserve">Existing utility transformer demolition — BY UTILITY (Xcel); coordination only</t>
   </si>
   <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing pad-mount utility transformer</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 9</t>
   </si>
   <si>
@@ -218,6 +245,12 @@
     <t xml:space="preserve">Relocate existing government-owned generator to Building 'A' site, incl. all testing for manufacturer recertification</t>
   </si>
   <si>
+    <t xml:space="preserve">Rating TBD (existing unit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing gov't-owned engine generator — rig, relocate, reconnect, recertify</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 8</t>
   </si>
   <si>
@@ -227,7 +260,7 @@
     <t xml:space="preserve">LS</t>
   </si>
   <si>
-    <t xml:space="preserve">Building EC responsible for relocation per KN 8. Includes rigging, disconnection/reconnection, recertification testing.</t>
+    <t xml:space="preserve">Building EC responsible per KN 8. Nameplate/kW not shown in site set — confirm from building package.</t>
   </si>
   <si>
     <t xml:space="preserve">A4</t>
@@ -236,10 +269,16 @@
     <t xml:space="preserve">Utility PRIMARY boring/trenching, conduit &amp; wiring, splice point to new transformer — BY XCEL ENERGY</t>
   </si>
   <si>
+    <t xml:space="preserve">Per XE standards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary conduit &amp; MV cable per Xcel Energy standards; 24" min trench, warning tape</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 1,3,4; 1/ES601</t>
   </si>
   <si>
-    <t xml:space="preserve">XE provides all primary conduit/wiring/trenching (KN 4). Route scaled ±150 LF for coordination. EC coordinates routing &amp; termination. Primary trench detail 1/ES601 (24" min depth, warning tape) if EC performs any portion.</t>
+    <t xml:space="preserve">XE provides all primary conduit/wiring/trenching (KN 4). Route scaled ±150 LF for coordination. EC coordinates routing &amp; termination.</t>
   </si>
   <si>
     <t xml:space="preserve">A5</t>
@@ -248,6 +287,12 @@
     <t xml:space="preserve">Remove existing parking lot light pole and foundation (NW parking, Tract I)</t>
   </si>
   <si>
+    <t xml:space="preserve">Height unknown (existing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Existing site light pole + concrete foundation — remove &amp; dispose</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD101 / KN 6</t>
   </si>
   <si>
@@ -260,6 +305,9 @@
     <t xml:space="preserve">Remove existing underground electric line (UGE) serving demo'd poles</t>
   </si>
   <si>
+    <t xml:space="preserve">Existing UG electric branch — remove &amp; dispose</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD101 / KN 6, legend</t>
   </si>
   <si>
@@ -272,6 +320,9 @@
     <t xml:space="preserve">Remove existing underground telephone line (T linetype)</t>
   </si>
   <si>
+    <t xml:space="preserve">Existing UG telephone cable/duct — remove &amp; dispose</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD101 legend</t>
   </si>
   <si>
@@ -284,6 +335,9 @@
     <t xml:space="preserve">Demolish existing electric meter</t>
   </si>
   <si>
+    <t xml:space="preserve">Existing utility meter — demolish, coordinate w/ XE</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD101 legend (EM)</t>
   </si>
   <si>
@@ -296,7 +350,10 @@
     <t xml:space="preserve">Demolish existing communications junction box</t>
   </si>
   <si>
-    <t xml:space="preserve">Legend item; verify count. Comm pedestal at NW corner of Bldg C to be PROTECTED (QC fence-removal comment references it).</t>
+    <t xml:space="preserve">Existing comm JB — demolish</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legend item; verify count. Comm pedestal at NW corner of Bldg C to be PROTECTED (QC fence-removal comment).</t>
   </si>
   <si>
     <t xml:space="preserve">A10</t>
@@ -305,10 +362,13 @@
     <t xml:space="preserve">Protect in place: (2) existing transformers &amp; pads, existing overhead power &amp; poles (south boundary), comm pedestal at Bldg C</t>
   </si>
   <si>
+    <t xml:space="preserve">Temporary protection / barricades / coordination</t>
+  </si>
+  <si>
     <t xml:space="preserve">CD101 notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Protection/coordination during demolition &amp; paving. Any utility damaged repaired at no additional cost (CD101 GN 1).</t>
+    <t xml:space="preserve">Any utility damaged repaired at no additional cost (CD101 GN 1).</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal A</t>
@@ -320,13 +380,19 @@
     <t xml:space="preserve">B1</t>
   </si>
   <si>
-    <t xml:space="preserve">New 480/277V, 3-phase pad-mounted utility transformer — BY XCEL; concrete pad by GC (coordinate w/ XE reqmts)</t>
+    <t xml:space="preserve">New pad-mounted utility transformer — BY XCEL; coordination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480/277V, 3-phase (kVA TBD by XE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad-mount, XE-furnished &amp; installed; XE makes primary &amp; secondary connections</t>
   </si>
   <si>
     <t xml:space="preserve">ES101 / KN 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Carry transformer concrete pad + grounding per XE standards; XE furnishes/installs transformer &amp; makes primary/secondary connections at transformer landings.</t>
+    <t xml:space="preserve">kVA sizing by utility from building load letter — not shown in site set.</t>
   </si>
   <si>
     <t xml:space="preserve">B2</t>
@@ -335,6 +401,12 @@
     <t xml:space="preserve">Transformer concrete pad w/ clearances per XE</t>
   </si>
   <si>
+    <t xml:space="preserve">Per XE standard dwg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cast-in-place concrete pad + ground grid per XE requirements</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pad by GC per KN 4 — coordinate pad &amp; clearance requirements with XE.</t>
   </si>
   <si>
@@ -344,7 +416,13 @@
     <t xml:space="preserve">Utility meter housing (furnish &amp; install, coordinate w/ XE) + CT cabinet</t>
   </si>
   <si>
-    <t xml:space="preserve">EC furnishes &amp; installs required meter housing; XE furnishes/installs/connects meter in that housing. CT cabinet shown at Bldg A.</t>
+    <t xml:space="preserve">Per XE metering std</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meter housing + CT cabinet, NEMA 3R; meter device by XE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC furnishes &amp; installs housing; XE furnishes/installs/connects meter.</t>
   </si>
   <si>
     <t xml:space="preserve">B4</t>
@@ -353,10 +431,16 @@
     <t xml:space="preserve">UG secondary conduit system, transformer to Bldg A main service disconnect / MDP</t>
   </si>
   <si>
+    <t xml:space="preserve">Conduit qty &amp; size TBD per one-line</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC Sch 40 (assumed) w/ XHHW-2 Cu secondary conductors per one-line</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 5</t>
   </si>
   <si>
-    <t xml:space="preserve">Conduit count/size per electrical one-line (building package — not in site set). Carry duct bank/trench LF; verify conduit qty at next submittal.</t>
+    <t xml:space="preserve">One-line is in building package — verify conduit count/size &amp; conductor schedule at next submittal.</t>
   </si>
   <si>
     <t xml:space="preserve">B5</t>
@@ -365,6 +449,9 @@
     <t xml:space="preserve">UG conduits, generator to automatic transfer switch(es)</t>
   </si>
   <si>
+    <t xml:space="preserve">PVC Sch 40 power + control (assumed); stub-ups field coordinated</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 6</t>
   </si>
   <si>
@@ -380,28 +467,40 @@
     <t xml:space="preserve">C1</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EA1 — 35' pole-mounted LED site light, Type 3 backlight control, glare shield, house-side shield (Lithonia DSX1-LED-P3-30K, 277V) w/ pole</t>
+    <t xml:space="preserve">Fixture EA1 — pole-mounted LED area light, Type 3 backlight control, glare shield, house-side shield, w/ pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35' pole; 277V; 3000K, 80 CRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithonia DSX1-LED-P3-30K-80CRI-BLC3-MVOLT-PIR-SPD20KV-HS-EGSR-DDXX</t>
   </si>
   <si>
     <t xml:space="preserve">ES101/ES601 sched.</t>
   </si>
   <si>
-    <t xml:space="preserve">Tag count from plan. Integral PIR motion (SPD20KV), dims to 30% after 10 min.</t>
+    <t xml:space="preserve">Tag count from plan. Integral PIR motion, dims to 30% after 10 min. Wattage/lumens columns blank in 65% schedule.</t>
   </si>
   <si>
     <t xml:space="preserve">C2</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EA2 — 35' pole-mounted LED site light, Type 5 distribution, glare shield (Lithonia DSX1-LED-P3-30K-T5W, 277V) w/ pole</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7 tagged poles; plan symbols show TWIN heads on EA2 poles — verify heads/pole (14 luminaires on 7 poles if twin). Priced per pole assembly.</t>
+    <t xml:space="preserve">Fixture EA2 — pole-mounted LED area light, Type 5 wide distribution, glare shield, w/ pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithonia DSX1-LED-P3-30K-80CRI-T5W-MVOLT-PIR-SPD20KV-EGSR-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7 tagged poles; plan symbols show TWIN heads on EA2 poles — verify heads/pole (14 luminaires if twin). Priced per pole assembly.</t>
   </si>
   <si>
     <t xml:space="preserve">C3</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EA3 — 35' pole-mounted LED site light, short-throw distribution, glare shield, house-side shield (277V) w/ pole</t>
+    <t xml:space="preserve">Fixture EA3 — pole-mounted LED area light, short-throw (T1S) distribution, glare shield, house-side shield, w/ pole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithonia DSX1-LED-P3-30K-80CRI-T1S-MVOLT-PIR-SPD20KV-HS-EGSR-DDXX</t>
   </si>
   <si>
     <t xml:space="preserve">Tag count from plan (east parking).</t>
@@ -410,40 +509,64 @@
     <t xml:space="preserve">C4</t>
   </si>
   <si>
-    <t xml:space="preserve">Pole base foundation, 2'-0" dia. x 9'-6" deep, 8-#5 vert., #4@10" ties, w/ anchor bolts, grout, ground stud</t>
+    <t xml:space="preserve">Pole base foundation w/ anchor bolts, grout, ground stud, handhole access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2'-0" dia. x 9'-6" deep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIP concrete (Div 03); 8-#5 vert., #4@10" ring ties; round in unpaved / square at paving</t>
   </si>
   <si>
     <t xml:space="preserve">2/ES601 dim. sched.</t>
   </si>
   <si>
-    <t xml:space="preserve">31'-40' pole row of dimension schedule. Round base in unpaved, square in/adjacent paving. Conc. &amp; reinf. see Div 3.</t>
+    <t xml:space="preserve">31'-40' pole row of dimension schedule governs for 35' poles.</t>
   </si>
   <si>
     <t xml:space="preserve">C5</t>
   </si>
   <si>
-    <t xml:space="preserve">Ground rod, #6 bare Cu bond to rebar &amp; pole, per pole base detail</t>
+    <t xml:space="preserve">Ground rod &amp; pole bond</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/8" x 8' rod (assumed — not sized on dwg)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu-clad steel rod; #6 AWG bare Cu bonded to rebar &amp; pole ground stud</t>
   </si>
   <si>
     <t xml:space="preserve">2/ES601</t>
   </si>
   <si>
-    <t xml:space="preserve">One per pole base.</t>
+    <t xml:space="preserve">One per pole base per detail. Rod size to be confirmed in Div 26 specs.</t>
   </si>
   <si>
     <t xml:space="preserve">C6</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EB1 — exterior LED bollard (Luminis RADB-LED-P1-30K, 3000K/80CRI, 277V), at grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 bollards along Bldg A south walk.</t>
+    <t xml:space="preserve">Fixture EB1 — exterior LED bollard, at grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">277V; 3000K, 80 CRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Luminis RADB-LED-P1-30K-SYM-PIR-BTT-BCF-HXX-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 bollards along Bldg A south walk; integral PIR.</t>
   </si>
   <si>
     <t xml:space="preserve">C7</t>
   </si>
   <si>
-    <t xml:space="preserve">Bollard base foundation 1'-2" w/ 4-#5 vert., #3 ties @10"</t>
+    <t xml:space="preserve">Bollard base foundation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1'-2" x depth per detail</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIP concrete (Div 03); 4-#5 vert., #3 ties @10"; anchor bolts &amp; leveling nuts per mfr</t>
   </si>
   <si>
     <t xml:space="preserve">3/ES601</t>
@@ -455,10 +578,16 @@
     <t xml:space="preserve">C8</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EF1 — exterior flagpole light, truck-mounted (Eagle Mountain SG-3K-EHS-M-XX)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 at flagpoles NW of Bldg A.</t>
+    <t xml:space="preserve">Fixture EF1 — exterior flagpole light, truck (trunnion) mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remote-driver LED; 3000K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eagle Mountain SG-3K-EHS-M-XX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 at flagpoles NW of Bldg A. Schedule voltage column shows 0V at 65% — driver remote (see C9).</t>
   </si>
   <si>
     <t xml:space="preserve">C9</t>
@@ -467,10 +596,16 @@
     <t xml:space="preserve">Weatherproof box w/ remote drivers for EF1 fixtures, buried in adjacent landscaped area</t>
   </si>
   <si>
+    <t xml:space="preserve">NEMA 4/6P burial-rated (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WP enclosure + (3) remote LED drivers</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 10</t>
   </si>
   <si>
-    <t xml:space="preserve">Field verify exact location of remote drivers prior to rough-in.</t>
+    <t xml:space="preserve">Field verify exact location of remote drivers prior to rough-in (KN 10).</t>
   </si>
   <si>
     <t xml:space="preserve">C10</t>
@@ -479,13 +614,19 @@
     <t xml:space="preserve">Site lighting branch circuits — conduit, conductors &amp; trench (ALLOWANCE — circuiting not shown at 65%)</t>
   </si>
   <si>
+    <t xml:space="preserve">1" PVC Sch 40 (assumed), 24" bury</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2#10 + 1#10G Cu THWN-2 (assumed), 277V circuits; warning tape</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101</t>
   </si>
   <si>
     <t xml:space="preserve">Allowance</t>
   </si>
   <si>
-    <t xml:space="preserve">No homeruns/circuit routing drawn at 65%; photometric plan to be added per QC comment. Allowance = pole-to-pole loop + homeruns; revise at 95%. Assume 1" PVC, 2#10+1#10G typ., 24" bury.</t>
+    <t xml:space="preserve">No homeruns/circuit routing drawn at 65%; photometric plan to be added per QC. Allowance = pole-to-pole loop + homeruns; revise at 95%.</t>
   </si>
   <si>
     <t xml:space="preserve">C11</t>
@@ -494,10 +635,13 @@
     <t xml:space="preserve">Lighting control interface — timeclock via lighting control panel in Bldg A</t>
   </si>
   <si>
+    <t xml:space="preserve">Control/interface wiring to LCP (panel in building package)</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES601 seq. of ops</t>
   </si>
   <si>
-    <t xml:space="preserve">Panel itself in building package; carry site interface/controls wiring allowance.</t>
+    <t xml:space="preserve">Carry site interface/controls wiring allowance.</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal C</t>
@@ -512,19 +656,31 @@
     <t xml:space="preserve">Exterior-rated junction box, 120V power connection to exterior gate operator</t>
   </si>
   <si>
+    <t xml:space="preserve">Size per NEC 314 (min 4-11/16" sq assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEMA 3R/4 galvanized steel JB, stamped, gasketed</t>
+  </si>
+  <si>
     <t xml:space="preserve">ES101 / KN 7</t>
   </si>
   <si>
-    <t xml:space="preserve">One at each vehicle gate (Bldg B west gate, and 2 east gate pedestals). Verify exact locations w/ approved shop drawings. QC: JB may shift closer to card reader.</t>
+    <t xml:space="preserve">One at each vehicle gate (Bldg B west gate + 2 east gate pedestals). Verify exact locations w/ approved shop dwgs. QC: JB may shift closer to card reader.</t>
   </si>
   <si>
     <t xml:space="preserve">D2</t>
   </si>
   <si>
-    <t xml:space="preserve">3/4" conduit w/ 2#10 + 1#10G to gate operator JBs (ALLOWANCE — source panel/routing not shown)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Branch circuit source &amp; routing not indicated at 65%. Allowance for 3 runs; revise when circuiting issued.</t>
+    <t xml:space="preserve">Branch circuit to gate operator JBs (ALLOWANCE — source panel/routing not shown)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4" PVC (assumed conduit type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2#10 + 1#10G Cu, 120V per KN 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conductors/size per KN 7; conduit material &amp; source panel not indicated at 65%. Allowance for 3 runs.</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal D</t>
@@ -539,16 +695,28 @@
     <t xml:space="preserve">A. UNDERGROUND STRUCTURES</t>
   </si>
   <si>
-    <t xml:space="preserve">MH1 — Telecom maintenance hole, 8'-0" x 96" x 96" precast (4260 base 9,275 lb / top 2,100 lb), cover, duct terminators, bonding ribbon, sump</t>
+    <t xml:space="preserve">MH1 — telecom maintenance hole w/ cover, duct terminators/knockouts, bonding ribbon (4 plcs), sump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8'-0" L x 96" W x 96" H; 13" dia sump</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Precast concrete, 4260 base (9,275 lb) + 4260 top deck (2,100 lb), traffic-rated cover</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 sched.; H1/TSN400</t>
   </si>
   <si>
-    <t xml:space="preserve">MH1-1 thru MH1-4. Provide knockouts to avoid 90° turns in duct bank.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HH1 — Telecom handhole, 3'-0" x 24" x 48", polymer concrete box &amp; slip-resistant cover (non-traffic rated)</t>
+    <t xml:space="preserve">MH1-1 thru MH1-4. Provide knockouts to avoid 90° turns in duct bank (TSN400 note).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1 — telecom handhole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3'-0" L x 24" W x 48" H</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymer concrete box w/ slip-resistant polymer concrete cover, fasteners — NOT vehicle-traffic rated</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 sched.; A1/TSN400</t>
@@ -560,25 +728,37 @@
     <t xml:space="preserve">HH1-1 handhole (appears on TSY100 security plan only — VERIFY if additional)</t>
   </si>
   <si>
+    <t xml:space="preserve">3'-0" x 24" x 48"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymer concrete (same as A2)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSY100</t>
   </si>
   <si>
-    <t xml:space="preserve">TSY100 labels an HH1-1 near Horizon Dr. that is not tagged on TSN100 — confirm whether this is a 6th handhole or a re-label of MH1-1 area.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B. DUCT BANKS (schedule TSN100; sections TSN400; concrete-encased, 3000 psi, #4 rebar, #3 hoops @18")</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB1 [(2) 4" PVC, ea. w/ (1) 4" 3-cell MaxCell] — MH1-1 to ISP telecom pedestal (east along Horizon Dr.)</t>
+    <t xml:space="preserve">TSY100 labels an HH1-1 near Horizon Dr. not tagged on TSN100 — confirm 6th handhole vs. re-label.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B. DUCT BANKS (schedule TSN100; sections TSN400)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB1 duct bank — MH1-1 to ISP telecom pedestal (east along Horizon Dr.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 4" conduits, 1H x 2W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4" PVC DB duct, ea. w/ (1) 4" 3-cell MaxCell innerduct; concrete-encased</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 / KN 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Scaled at 1"=30' (±10%). ISP pedestal location approximate — coordinate exact location with ISP.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DB1 — MH1-1 to MH1-2</t>
+    <t xml:space="preserve">Scaled at 1"=30' (±10%). ISP pedestal location approximate — coordinate w/ ISP.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB1 duct bank — MH1-1 to MH1-2</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100</t>
@@ -587,7 +767,7 @@
     <t xml:space="preserve">Scaled at 1"=30' (±10%).</t>
   </si>
   <si>
-    <t xml:space="preserve">DB1 — MH1-2 to HH1-2 (Bldg C / pedestrian gate)</t>
+    <t xml:space="preserve">DB1 duct bank — MH1-2 to HH1-2 (Bldg C / pedestrian gate)</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 / KN 3</t>
@@ -596,7 +776,7 @@
     <t xml:space="preserve">Future conduit connection to Bldg C; coordinate final HH location w/ security contractor.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB1 — MH1-2 to HH1-4 (Bldg B)</t>
+    <t xml:space="preserve">DB1 duct bank — MH1-2 to HH1-4 (Bldg B)</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 / KN 4</t>
@@ -605,7 +785,7 @@
     <t xml:space="preserve">Coordinate final location w/ security contractor for connection to security gate.</t>
   </si>
   <si>
-    <t xml:space="preserve">DB1 — MH1-3 to MH1-4</t>
+    <t xml:space="preserve">DB1 duct bank — MH1-3 to MH1-4</t>
   </si>
   <si>
     <t xml:space="preserve">Dimensioned</t>
@@ -617,7 +797,7 @@
     <t xml:space="preserve">B6</t>
   </si>
   <si>
-    <t xml:space="preserve">DB1 — MH1-4 to HH1-3 (future Bldg B connection)</t>
+    <t xml:space="preserve">DB1 duct bank — MH1-4 to HH1-3 (future Bldg B connection)</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 / KN 2</t>
@@ -629,19 +809,22 @@
     <t xml:space="preserve">B7</t>
   </si>
   <si>
-    <t xml:space="preserve">DB1 SUBTOTAL</t>
+    <t xml:space="preserve">DB1 SUBTOTAL — (2) 4" PVC w/ MaxCell</t>
   </si>
   <si>
     <t xml:space="preserve">B8</t>
   </si>
   <si>
-    <t xml:space="preserve">DB2 [(4) 4" PVC 2Hx2W, ea. w/ (1) 4" 3-cell MaxCell] — MH1-2 to MH1-3</t>
+    <t xml:space="preserve">DB2 duct bank — MH1-2 to MH1-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(4) 4" conduits, 2H x 2W</t>
   </si>
   <si>
     <t xml:space="preserve">B9</t>
   </si>
   <si>
-    <t xml:space="preserve">DB2 — MH1-3 to Bldg A entry</t>
+    <t xml:space="preserve">DB2 duct bank — MH1-3 to Bldg A entry</t>
   </si>
   <si>
     <t xml:space="preserve">Plan dim 21'-4 3/4" to building; additional 33'-10 3/4" continues inside Bldg A (building package).</t>
@@ -650,13 +833,19 @@
     <t xml:space="preserve">B10</t>
   </si>
   <si>
-    <t xml:space="preserve">DB2 SUBTOTAL</t>
+    <t xml:space="preserve">DB2 SUBTOTAL — (4) 4" PVC w/ MaxCell</t>
   </si>
   <si>
     <t xml:space="preserve">B11</t>
   </si>
   <si>
-    <t xml:space="preserve">DB3 [(2) 2" 1Hx2W, ea. w/ (1) 2" 3-cell MaxCell innerduct] — HH1-3 to HH1-5</t>
+    <t xml:space="preserve">DB3 duct bank — HH1-3 to HH1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 2" conduits, 1H x 2W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2" PVC duct, ea. w/ (1) 2" 3-cell MaxCell innerduct; encasement assumed (no section)</t>
   </si>
   <si>
     <t xml:space="preserve">72'-x 1/4" diagonal + 29'-2 1/2" segments (partially obscured dim — verify 72' leg).</t>
@@ -665,16 +854,16 @@
     <t xml:space="preserve">B12</t>
   </si>
   <si>
-    <t xml:space="preserve">DB3 — HH1-5 to HH1-6 (east vehicle gate)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">179'-7 1/4" + 17'-8 3/4". NOTE: an overall dim of 508'-8 3/4" is also shown at HH1-6 and does NOT reconcile with the segment sum — RFI/verify.</t>
+    <t xml:space="preserve">DB3 duct bank — HH1-5 to HH1-6 (east vehicle gate)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">179'-7 1/4" + 17'-8 3/4". NOTE: overall dim 508'-8 3/4" also shown at HH1-6 does NOT reconcile — RFI.</t>
   </si>
   <si>
     <t xml:space="preserve">B13</t>
   </si>
   <si>
-    <t xml:space="preserve">DB3 SUBTOTAL</t>
+    <t xml:space="preserve">DB3 SUBTOTAL — (2) 2" PVC w/ MaxCell</t>
   </si>
   <si>
     <t xml:space="preserve">Subtotal B (priced lines)</t>
@@ -683,7 +872,13 @@
     <t xml:space="preserve">C. TRENCH / ENCASEMENT / MISC (quantities driven by duct bank LF above)</t>
   </si>
   <si>
-    <t xml:space="preserve">Trench &amp; backfill for telecom duct banks (30" min cover, warning tape, below 50-yr freeze line, ≥6' below grade under traffic)</t>
+    <t xml:space="preserve">Trench &amp; backfill for telecom duct banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30" min cover; ≥6' deep under traffic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavate, bed, backfill, compact; detectable warning tape; below 50-yr freeze line</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 GN 8/9</t>
@@ -695,7 +890,13 @@
     <t xml:space="preserve">Equals sum of all duct bank segments above.</t>
   </si>
   <si>
-    <t xml:space="preserve">Concrete encasement, DB1 section 16"H x 23"W (2.56 SF)</t>
+    <t xml:space="preserve">Concrete encasement — DB1 runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16" H x 23" W section (2.56 SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi concrete; 4-#4 longitudinal rebar; #3 wire hoops @18" OC; plastic spacers @4' OC</t>
   </si>
   <si>
     <t xml:space="preserve">A8/TSN400</t>
@@ -704,10 +905,13 @@
     <t xml:space="preserve">CY</t>
   </si>
   <si>
-    <t xml:space="preserve">Qty = DB1 LF x 2.56 SF / 27.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concrete encasement, DB2 section 25" x 25" (4.34 SF)</t>
+    <t xml:space="preserve">Qty = DB1 LF x 2.56 SF / 27. Reinforcement may vary w/ soil conditions per structural.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete encasement — DB2 runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25" x 25" section (4.34 SF)</t>
   </si>
   <si>
     <t xml:space="preserve">A13/TSN400</t>
@@ -716,25 +920,37 @@
     <t xml:space="preserve">Qty = DB2 LF x 4.34 SF / 27.</t>
   </si>
   <si>
-    <t xml:space="preserve">Concrete encasement, DB3 section 14" x 8-1/2" (0.83 SF) — encasement detail for DB3 not shown, assumed encased</t>
+    <t xml:space="preserve">Concrete encasement — DB3 runs (assumed encased; no section drawn)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14" x 8-1/2" envelope (0.83 SF)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi concrete (assumed, matching DB1/DB2)</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 sched.</t>
   </si>
   <si>
-    <t xml:space="preserve">Qty = DB3 LF x 0.83 SF / 27. Verify whether DB3 is concrete-encased or direct-buried.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">#6 AWG bonding conductor, power-to-telecom plant bond; bond metallic-sheath cables at each MH</t>
+    <t xml:space="preserve">Qty = DB3 LF x 0.83 SF / 27. Verify concrete-encased vs. direct-buried (RFI-2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bonding conductor, power-to-telecom plant bond; bond metallic-sheath cables at each MH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#6 AWG min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bare Cu bonding conductor per NEC/NESC (IEEE C2); MH bonding ribbon connections</t>
   </si>
   <si>
     <t xml:space="preserve">TSN100 GN 3/12</t>
   </si>
   <si>
-    <t xml:space="preserve">Per NEC/NESC; includes MH bonding ribbon connections.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pull string / mule tape in all conduits &amp; innerduct cells; empty-conduit test rating 200 lb</t>
+    <t xml:space="preserve">Pull string / mule tape in all conduits &amp; innerduct cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polyester mule tape, 1,250 lb (assumed); empty conduits w/ 200-lb test pull string per TSN notes</t>
   </si>
   <si>
     <t xml:space="preserve">TSN gen. notes</t>
@@ -743,18 +959,30 @@
     <t xml:space="preserve">D. OSP CABLING (TSN300 site one-line)</t>
   </si>
   <si>
-    <t xml:space="preserve">12-strand OM4 multimode fiber, OSP — Bldg A to MH/HH system incl. coils for future connection at Bldg B/C and east gate handholes</t>
+    <t xml:space="preserve">OSP fiber — Bldg A to MH/HH system incl. coils for future connection at Bldg B/C and east gate handholes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-strand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OM4 50/125 multimode, OSP-rated (gel-free, assumed), green-dashed runs per TSN300</t>
   </si>
   <si>
     <t xml:space="preserve">TSN300</t>
   </si>
   <si>
-    <t xml:space="preserve">Routes + 20% slack + coils (QC: 'fiber optic cable coiled for future connection' at HH1s). Revise when cable schedule issued.</t>
+    <t xml:space="preserve">Routes + 20% slack + coils (QC: coiled for future connection at HH1s). Revise when cable schedule issued.</t>
   </si>
   <si>
     <t xml:space="preserve">Fiber terminations, LIU/patch panel at Bldg A, testing &amp; documentation</t>
   </si>
   <si>
+    <t xml:space="preserve">12 strands</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LC LIU/patch panel (assumed); OTDR + insertion loss testing, labeling per TIA-606</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSN300; TSN001 matrix</t>
   </si>
   <si>
@@ -764,13 +992,19 @@
     <t xml:space="preserve">D3</t>
   </si>
   <si>
-    <t xml:space="preserve">OSP copper backbone cabling — TBD (QC comment: 'Where is the OSP copper?')</t>
+    <t xml:space="preserve">OSP copper backbone cabling — TBD (QC: 'Where is the OSP copper?')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pair count TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP-rated copper backbone (type/size not shown at 65%)</t>
   </si>
   <si>
     <t xml:space="preserve">TSN300 QC</t>
   </si>
   <si>
-    <t xml:space="preserve">Matrix lists copper backbone as Contractor scope but no copper shown on one-line at 65% — carry allowance / RFI.</t>
+    <t xml:space="preserve">Matrix lists copper backbone as Contractor scope but none shown on one-line — carry allowance / RFI.</t>
   </si>
   <si>
     <t xml:space="preserve">D4</t>
@@ -779,7 +1013,10 @@
     <t xml:space="preserve">ISP fiber &amp; ISP telecom pedestal — BY ISP</t>
   </si>
   <si>
-    <t xml:space="preserve">ISP-furnished/installed per responsibility matrix; contractor provides pathway (DB1 item B1) &amp; coordination.</t>
+    <t xml:space="preserve">Per ISP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP-furnished fiber &amp; pedestal; contractor provides DB1 pathway (item B1)</t>
   </si>
   <si>
     <t xml:space="preserve">TELECOM OSP TOTAL</t>
@@ -791,46 +1028,85 @@
     <t xml:space="preserve">A. FIELD DEVICES — GATES</t>
   </si>
   <si>
-    <t xml:space="preserve">Pedestal-mounted video intercom w/ integrated card reader — welded 316 SS gooseneck pedestal (min 2" sq.), 48" above roadway, concrete footer (frost depth +20" from curb), 1" conduit for signal cables</t>
+    <t xml:space="preserve">Pedestal-mounted video intercom w/ integrated card reader, concrete footer &amp; conduit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48" above roadway; min 2" sq pedestal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welded 316 stainless gooseneck pedestal, heavy wall; PoE video intercom + reader; 1" conduit for signal; footer to frost depth, 20" from curb</t>
   </si>
   <si>
     <t xml:space="preserve">TSY100; A1/TSY101</t>
   </si>
   <si>
-    <t xml:space="preserve">East vehicle gates at HH1-5 &amp; HH1-6. QC: pedestal locations updated per civil; verify vs. updated civil background.</t>
+    <t xml:space="preserve">East vehicle gates at HH1-5 &amp; HH1-6. QC: locations updated per civil — verify against updated background.</t>
   </si>
   <si>
     <t xml:space="preserve">Building-mounted video intercom w/ integrated card reader — vehicle gate at Bldg B</t>
   </si>
   <si>
+    <t xml:space="preserve">Mtg ht 3'-10" AFF (typ per TSY001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall-mount video intercom/reader; 4-11/16" sq 2-device mud-ring box, 2-1/8" deep; (1) 1" C stub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSY100; TSY001 sched.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Building-mounted card reader — pedestrian gate (Bldg C area)</t>
   </si>
   <si>
-    <t xml:space="preserve">QC: shift reader to wall mount at the gate; add OSP-rated ACS cable keynote.</t>
+    <t xml:space="preserve">Mtg ht 3'-6" AFF (typ per TSY001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card reader; 4-11/16" sq 1-device mud-ring box, 2-1/8" deep; (1) 3/4" C stub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QC: shift reader to wall mount at the gate; OSP-rated ACS cable keynote to be added.</t>
   </si>
   <si>
     <t xml:space="preserve">Card reader at personnel swing gate (TSY101 inset, KN 7) — additional to A3?</t>
   </si>
   <si>
+    <t xml:space="preserve">Mtg ht 3'-6" AFF (typ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card reader in WP enclosure (see A8 rough-in)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSY101 inset KN 7-9</t>
   </si>
   <si>
-    <t xml:space="preserve">Inset shows card readers at swing gate (KN 8) &amp; personnel swing gate (KN 9, gates per C-503). VERIFY overlap with A2/A3 building-mounted readers before pricing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle gate operator connection/interface (operator &amp; gate by others — civil C-503) incl. gate command wiring</t>
+    <t xml:space="preserve">Inset shows readers at swing gate (KN 8) &amp; personnel swing gate (KN 9, gates per C-503). VERIFY overlap with A2/A3 before pricing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle gate operator connection/interface (operator &amp; gate by others — civil C-503)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate command wiring, dry-contact/relay interface to operator controller</t>
   </si>
   <si>
     <t xml:space="preserve">TSY101 flow diag.</t>
   </si>
   <si>
-    <t xml:space="preserve">VEH GATE 1/2/3 operators. 120V power JB by electrical (see Site Electrical D1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Vehicle exit loop (saw-cut or preformed) w/ lead-in to gate operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gate position switch (DPS) on sliding gate — magnet, mounting bracket, armored cable, WP single-gang box, 3/4" conduit to handhole</t>
+    <t xml:space="preserve">VEH GATE 1/2/3 operators. 120V power JB by electrical (Site Electrical D1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle exit loop w/ lead-in to gate operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loop size per operator mfr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preformed or saw-cut inductive loop + sealant + lead-in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate position switch (DPS) on sliding gate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magnet on gate + position switch on fence-post bracket; armored cable; WP single-gang box; 3/4" conduit to handhole</t>
   </si>
   <si>
     <t xml:space="preserve">A7/TSY101</t>
@@ -839,10 +1115,16 @@
     <t xml:space="preserve">Assumed one per vehicle gate; verify sliding vs. swing gate count w/ C-503.</t>
   </si>
   <si>
-    <t xml:space="preserve">Access control rough-in at fence gates — card reader WP sheet-metal enclosure, swinging gate lock &amp; bracket, (2) 1" conduits to security equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A13/TSY101</t>
+    <t xml:space="preserve">Access control rough-in at fence gates</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(2) 1" conduits to SEC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WP sheet-metal enclosure for card reader; swinging gate lock &amp; bracket; torx/peg tamper-resistant hardware</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A13/TSY101; GN 18</t>
   </si>
   <si>
     <t xml:space="preserve">Per access control gate rough-in detail (swing/personnel gates).</t>
@@ -854,36 +1136,72 @@
     <t xml:space="preserve">Access control panel ACP1</t>
   </si>
   <si>
+    <t xml:space="preserve">Surface mount, 5'-0" AFF (TSY001 sched.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP w/ enclosure &amp; power supply, Div 28; mount to fire-rated plywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G2/TSY101; TSY001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access control panel ACP2 ('if necessary')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface mount, 5'-0" AFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACP w/ enclosure &amp; power supply, Div 28</t>
+  </si>
+  <si>
     <t xml:space="preserve">G2/TSY101</t>
   </si>
   <si>
-    <t xml:space="preserve">Access control panel ACP2 ('if necessary')</t>
-  </si>
-  <si>
     <t xml:space="preserve">Shown dashed / 'IF NECESSARY' — carry until panel count confirmed.</t>
   </si>
   <si>
-    <t xml:space="preserve">12U equipment rack, COMM 124</t>
+    <t xml:space="preserve">Equipment rack, COMM 124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wall/floor rack per detail</t>
   </si>
   <si>
     <t xml:space="preserve">ACS server + access control software, licensing &amp; commissioning</t>
   </si>
   <si>
+    <t xml:space="preserve">Rack-mount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS server, Div 28 contractor furnished/installed per matrix</t>
+  </si>
+  <si>
     <t xml:space="preserve">G2/TSY101; TSY002</t>
   </si>
   <si>
-    <t xml:space="preserve">Div 28, contractor furnished/installed per matrix.</t>
-  </si>
-  <si>
     <t xml:space="preserve">VIC (video intercom) master station</t>
   </si>
   <si>
+    <t xml:space="preserve">Desktop (TSY001 sched.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video intercom master station w/ (1) copper cable to switch; surface mount to desk</t>
+  </si>
+  <si>
     <t xml:space="preserve">Video intercom system remains contractor scope per TSY002.</t>
   </si>
   <si>
     <t xml:space="preserve">Security network switch — OWNER furnished/installed; coordination only</t>
   </si>
   <si>
+    <t xml:space="preserve">PoE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owner network switch (matrix: owner/owner)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSY002 matrix</t>
   </si>
   <si>
@@ -896,13 +1214,13 @@
     <t xml:space="preserve">Excluded</t>
   </si>
   <si>
-    <t xml:space="preserve">Video surveillance head-end, cameras &amp; VSS cabling struck through on responsibility matrix. Still drawn on G2/TSY101 rack — VERIFY deletion before bid.</t>
+    <t xml:space="preserve">VSS head-end, cameras &amp; cabling struck on matrix but still drawn on G2/TSY101 rack — VERIFY deletion before bid.</t>
   </si>
   <si>
     <t xml:space="preserve">Surge protection devices &amp; associated cabling (head end + field)</t>
   </si>
   <si>
-    <t xml:space="preserve">Div 28 contractor scope.</t>
+    <t xml:space="preserve">SPDs on OSP copper entering building + device circuits, Div 28</t>
   </si>
   <si>
     <t xml:space="preserve">C. CABLING (homeruns via telecom duct bank system to COMM 124)</t>
@@ -911,19 +1229,31 @@
     <t xml:space="preserve">OSP-rated access control cable to each card reader location</t>
   </si>
   <si>
+    <t xml:space="preserve">Composite/multi-conductor per spec 28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP-rated ACS cable (reader/lock/DPS/REX composite assumed)</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSY100 QC notes</t>
   </si>
   <si>
-    <t xml:space="preserve">5 reader locations; homerun lengths estimated along duct routes + slack. QC keynote to be added: '(1) OSP-rated ACS cable to card reader'.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended-reach 4-pair 22 AWG min. copper data cable, PoE rated, to each intercom (3)</t>
+    <t xml:space="preserve">5 reader locations; homerun lengths estimated along duct routes + slack.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended-reach copper data cable to each intercom (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-pair, 22 AWG min</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended-reach PoE-rated OSP copper data cable (per TSY101 riser note &amp; QC keynote)</t>
   </si>
   <si>
     <t xml:space="preserve">TSY101; TSY100 QC</t>
   </si>
   <si>
-    <t xml:space="preserve">(3) cables per riser note. Verify cable length/bandwidth/PoE load/voltage-drop per manufacturer (GN 9). East gate run ±600 LF — confirm extended-reach product suitability.</t>
+    <t xml:space="preserve">(3) cables per riser note. Verify length/bandwidth/PoE load/voltage-drop per mfr (GN 9) — east gate run ±600 LF.</t>
   </si>
   <si>
     <t xml:space="preserve">ACS cables, ACP1/ACP2 to Bldg A doors/monitored devices — BUILDING PACKAGE</t>
@@ -935,6 +1265,9 @@
     <t xml:space="preserve">Testing, labeling, commissioning, software licensing — all site security systems; record drawings</t>
   </si>
   <si>
+    <t xml:space="preserve">Per TSY100 GN 8 &amp; Div 28</t>
+  </si>
+  <si>
     <t xml:space="preserve">TSY002; TSY100 GN 8</t>
   </si>
   <si>
@@ -944,9 +1277,6 @@
     <t xml:space="preserve">Video surveillance cameras, mounting hardware, network cabling, head-end server &amp; storage</t>
   </si>
   <si>
-    <t xml:space="preserve">—</t>
-  </si>
-  <si>
     <t xml:space="preserve">Struck through in red on matrix.</t>
   </si>
   <si>
@@ -986,7 +1316,7 @@
     <t xml:space="preserve">Not available</t>
   </si>
   <si>
-    <t xml:space="preserve">Specifications (Div 26/27/28, 33 71 02), electrical one-line diagram, panel schedules, building 'A' package. Items referencing the one-line are carried as allowances.</t>
+    <t xml:space="preserve">Specifications (Div 26/27/28, 33 71 02), electrical one-line diagram, panel schedules, building 'A' package. Items referencing the one-line are carried as allowances; sizes marked '(assumed)' or 'TBD' pending these documents.</t>
   </si>
   <si>
     <t xml:space="preserve">2. TAKEOFF METHODOLOGY</t>
@@ -1004,6 +1334,12 @@
     <t xml:space="preserve">Work that is clearly required but not yet drawn at 65% (site lighting branch circuits, security homerun cabling, OSP copper). Quantities are order-of-magnitude placeholders — revise at 95%.</t>
   </si>
   <si>
+    <t xml:space="preserve">Sizes &amp; types</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size and Type/Material/Model columns are transcribed from the ES601 luminaire schedule, TSN100 site device &amp; duct bank schedules, TSN400/TSY101/ES601 details, and TSY001 device schedule. Anything not stated on the drawings is marked '(assumed)' or 'TBD'.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pricing</t>
   </si>
   <si>
@@ -1034,7 +1370,7 @@
     <t xml:space="preserve">A3.4</t>
   </si>
   <si>
-    <t xml:space="preserve">Duct banks DB1/DB2 concrete-encased per TSN400 sections; DB3 assumed concrete-encased (no section drawn) — verify.</t>
+    <t xml:space="preserve">Duct banks DB1/DB2 concrete-encased per TSN400 sections; DB3 assumed concrete-encased (no section drawn) — verify. Note the TSN100 duct bank schedule lists envelope dims (DB1 18"x10-1/2", DB2 18"x18", DB3 14"x8-1/2") that differ from the TSN400 encasement sections (23"x16", 25"x25") — encasement CY is computed from the TSN400 sections; see RFI-11.</t>
   </si>
   <si>
     <t xml:space="preserve">A3.5</t>
@@ -1046,13 +1382,13 @@
     <t xml:space="preserve">A3.6</t>
   </si>
   <si>
-    <t xml:space="preserve">Telecom trench: 30" min cover, below 50-yr freeze line, ≥6' below surface where vehicular traffic crosses (TSN100 GN 8/9); max 600' between MH/HH (GN 4); conduit sloped ≥0.4"/ft to MHs.</t>
+    <t xml:space="preserve">Telecom trench: 30" min cover, below 50-yr freeze line, ≥6' below surface where vehicular traffic crosses (TSN100 GN 8/9); max 600' between MH/HH (GN 4); conduit sloped ≥0.4"/ft to MHs; 6"/12" separations from other utilities (GN 6/7).</t>
   </si>
   <si>
     <t xml:space="preserve">A3.7</t>
   </si>
   <si>
-    <t xml:space="preserve">Security homerun cabling routed through the telecom duct bank/MaxCell system to COMM 124 in Bldg A (TSY100 GN); no separate security duct bank carried.</t>
+    <t xml:space="preserve">Security homerun cabling routed through the telecom duct bank/MaxCell system to COMM 124 in Bldg A (TSY100 GN); no separate security duct bank carried. Security pathways in EMT or secured cable tray inside buildings (TSY100 GN 6).</t>
   </si>
   <si>
     <t xml:space="preserve">A3.8</t>
@@ -1064,13 +1400,19 @@
     <t xml:space="preserve">A3.9</t>
   </si>
   <si>
-    <t xml:space="preserve">Generator is existing government-owned; relocation + recertification testing by building electrical contractor (ES101 KN 8). Fuel, pad, and mechanical work excluded.</t>
+    <t xml:space="preserve">Generator is existing government-owned; relocation + recertification testing by building electrical contractor (ES101 KN 8). Fuel, pad, and mechanical work excluded. Rating TBD from building package.</t>
   </si>
   <si>
     <t xml:space="preserve">A3.10</t>
   </si>
   <si>
-    <t xml:space="preserve">Site lighting controls are integral (PIR/dimming) + timeclock in Bldg A lighting control panel (building package); only interface wiring carried.</t>
+    <t xml:space="preserve">Site lighting controls are integral (PIR/dimming) + timeclock in Bldg A lighting control panel (building package); only interface wiring carried. Sequence: on 1 hr before business open, off within 1 hr after close, 10-min timeout, dim to 30%.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumed materials where drawings are silent: PVC Sch 40 for site branch conduits, THWN-2/XHHW-2 Cu conductors, 5/8"x8' Cu-clad ground rods, NEMA 3R/4 exterior enclosures, LC fiber terminations, 1,250-lb mule tape. All flagged '(assumed)' in the Type column.</t>
   </si>
   <si>
     <t xml:space="preserve">4. EXCLUSIONS</t>
@@ -1142,7 +1484,7 @@
     <t xml:space="preserve">RFI-3</t>
   </si>
   <si>
-    <t xml:space="preserve">Confirm EA2 = one or two luminaires per pole (plan symbol vs. schedule).</t>
+    <t xml:space="preserve">Confirm EA2 = one or two luminaires per pole (plan symbol vs. schedule); complete wattage/lumen/CCT columns of luminaire schedule.</t>
   </si>
   <si>
     <t xml:space="preserve">RFI-4</t>
@@ -1160,7 +1502,7 @@
     <t xml:space="preserve">RFI-6</t>
   </si>
   <si>
-    <t xml:space="preserve">Site lighting circuiting, panel source, and photometric plan to be issued (QC) — allowances C10/C11/D2 must be re-quantified at 95%.</t>
+    <t xml:space="preserve">Site lighting circuiting, panel source, and photometric plan to be issued (QC) — allowances C10/C11/D2 must be re-quantified at 95%; confirm conduit/conductor sizes.</t>
   </si>
   <si>
     <t xml:space="preserve">RFI-7</t>
@@ -1172,7 +1514,7 @@
     <t xml:space="preserve">RFI-8</t>
   </si>
   <si>
-    <t xml:space="preserve">OSP copper backbone shown in matrix but absent from TSN300 one-line ('Where is the OSP copper?' QC) — confirm scope.</t>
+    <t xml:space="preserve">OSP copper backbone shown in matrix but absent from TSN300 one-line ('Where is the OSP copper?' QC) — confirm scope, type and pair count.</t>
   </si>
   <si>
     <t xml:space="preserve">RFI-9</t>
@@ -1185,6 +1527,18 @@
   </si>
   <si>
     <t xml:space="preserve">Relocated EA1 pole at generator (fire-truck access conflict, ES101 QC) — location change may affect circuit lengths.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFI-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSN100 duct bank schedule W x H values (DB1 18"x10-1/2", DB2 18"x18", DB3 14"x8-1/2") differ from TSN400 encasement sections (DB1 23"x16", DB2 25"x25") — confirm governing encasement dimensions for concrete quantities.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFI-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirm transformer kVA, generator kW/recertification requirements, and secondary conductor/conduit schedule (one-line, building package).</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1770,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="41">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1545,28 +1899,16 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -1845,12 +2187,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:E29"/>
+  <dimension ref="B2:E31"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="60"/>
   </cols>
@@ -1902,7 +2244,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">'Site Electrical'!H42</f>
+        <f aca="false">'Site Electrical'!J42</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -1917,14 +2259,14 @@
         <v>13</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">'Telecom OSP'!H40</f>
+        <f aca="false">'Telecom OSP'!J40</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="7" t="s">
         <v>15</v>
       </c>
@@ -1932,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">Security!H37</f>
+        <f aca="false">Security!J37</f>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -1995,7 +2337,7 @@
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="22.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="17" t="s">
         <v>28</v>
       </c>
@@ -2005,22 +2347,24 @@
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="17" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="14" t="s">
+      <c r="C20" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
@@ -2028,7 +2372,7 @@
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
@@ -2036,7 +2380,7 @@
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
@@ -2044,7 +2388,7 @@
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -2052,7 +2396,7 @@
     </row>
     <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="14" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
@@ -2060,7 +2404,7 @@
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="14" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
@@ -2068,20 +2412,36 @@
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="14" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
     </row>
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B30" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="15">
     <mergeCell ref="C15:E15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="C17:E17"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
-    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="C20:E20"/>
     <mergeCell ref="B23:E23"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B25:E25"/>
@@ -2089,6 +2449,8 @@
     <mergeCell ref="B27:E27"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2105,62 +2467,70 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>48</v>
+      <c r="K4" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -2170,306 +2540,370 @@
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E6" s="22" t="n">
-        <v>50</v>
-      </c>
-      <c r="F6" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24" t="str">
-        <f aca="false">IF(G6="","",E6*G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="24" t="str">
+        <f aca="false">IF(I6="","",G6*I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E7" s="25" t="n">
+        <v>64</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="str">
-        <f aca="false">IF(G7="","",E7*G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>61</v>
+      <c r="H7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24" t="str">
+        <f aca="false">IF(I7="","",G7*I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="25" t="n">
+        <v>71</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24" t="str">
-        <f aca="false">IF(G8="","",E8*G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24" t="str">
+        <f aca="false">IF(I8="","",G8*I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>80</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="G9" s="25" t="n">
+        <v>150</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24" t="str">
+        <f aca="false">IF(I9="","",G9*I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="21" t="s">
-        <v>70</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>150</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24" t="str">
-        <f aca="false">IF(G9="","",E9*G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>72</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>2</v>
-      </c>
-      <c r="F10" s="21" t="s">
+      <c r="I10" s="23"/>
+      <c r="J10" s="24" t="str">
+        <f aca="false">IF(I10="","",G10*I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24" t="str">
-        <f aca="false">IF(G10="","",E10*G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="22" t="n">
+      <c r="G11" s="22" t="n">
         <v>200</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="str">
-        <f aca="false">IF(G11="","",E11*G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="24" t="str">
+        <f aca="false">IF(I11="","",G11*I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="22" t="n">
+        <v>97</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="22" t="n">
         <v>400</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24" t="str">
-        <f aca="false">IF(G12="","",E12*G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>83</v>
+      <c r="H12" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24" t="str">
+        <f aca="false">IF(I12="","",G12*I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E13" s="25" t="n">
+      <c r="D13" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24" t="str">
-        <f aca="false">IF(G13="","",E13*G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="27" t="s">
-        <v>87</v>
+      <c r="H13" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24" t="str">
+        <f aca="false">IF(I13="","",G13*I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="27" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="C14" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E14" s="25" t="n">
+      <c r="D14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>99</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24" t="str">
-        <f aca="false">IF(G14="","",E14*G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="27" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24" t="str">
+        <f aca="false">IF(I14="","",G14*I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="27" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="21" t="s">
+        <v>111</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="25" t="n">
+      <c r="D15" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24" t="str">
-        <f aca="false">IF(G15="","",E15*G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>94</v>
+      <c r="H15" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24" t="str">
+        <f aca="false">IF(I15="","",G15*I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28"/>
       <c r="B16" s="29" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
       <c r="E16" s="28"/>
       <c r="F16" s="28"/>
       <c r="G16" s="28"/>
-      <c r="H16" s="30" t="n">
-        <f aca="false">SUM(H6:H15)</f>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="30" t="n">
+        <f aca="false">SUM(J6:J15)</f>
         <v>0</v>
       </c>
-      <c r="I16" s="28"/>
+      <c r="K16" s="28"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="19" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B17" s="20"/>
       <c r="C17" s="20"/>
@@ -2479,166 +2913,200 @@
       <c r="G17" s="20"/>
       <c r="H17" s="20"/>
       <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="25" t="n">
+        <v>118</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G18" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="24" t="str">
-        <f aca="false">IF(G18="","",E18*G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24" t="str">
+        <f aca="false">IF(I18="","",G18*I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="25" t="n">
+        <v>124</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="24" t="str">
-        <f aca="false">IF(G19="","",E19*G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24" t="str">
+        <f aca="false">IF(I19="","",G19*I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="21" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="25" t="n">
+        <v>129</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F20" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24" t="str">
-        <f aca="false">IF(G20="","",E20*G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>106</v>
+      <c r="H20" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24" t="str">
+        <f aca="false">IF(I20="","",G20*I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E21" s="22" t="n">
+        <v>134</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="22" t="n">
         <v>30</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24" t="str">
-        <f aca="false">IF(G21="","",E21*G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24" t="str">
+        <f aca="false">IF(I21="","",G21*I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E22" s="22" t="n">
+        <v>140</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G22" s="22" t="n">
         <v>50</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24" t="str">
-        <f aca="false">IF(G22="","",E22*G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>114</v>
+      <c r="H22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="24" t="str">
+        <f aca="false">IF(I22="","",G22*I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="27" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28"/>
       <c r="B23" s="29" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
       <c r="G23" s="28"/>
-      <c r="H23" s="30" t="n">
-        <f aca="false">SUM(H18:H22)</f>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="30" t="n">
+        <f aca="false">SUM(J18:J22)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="28"/>
+      <c r="K23" s="28"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -2648,334 +3116,404 @@
       <c r="G24" s="20"/>
       <c r="H24" s="20"/>
       <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D25" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="25" t="n">
+        <v>147</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="F25" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G25" s="23"/>
-      <c r="H25" s="24" t="str">
-        <f aca="false">IF(G25="","",E25*G25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="8" t="s">
-        <v>120</v>
+      <c r="H25" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="23"/>
+      <c r="J25" s="24" t="str">
+        <f aca="false">IF(I25="","",G25*I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="25" t="n">
+        <v>153</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="25" t="n">
         <v>7</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24" t="str">
-        <f aca="false">IF(G26="","",E26*G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>123</v>
+      <c r="H26" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24" t="str">
+        <f aca="false">IF(I26="","",G26*I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="27" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>125</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="25" t="n">
+        <v>157</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F27" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24" t="str">
-        <f aca="false">IF(G27="","",E27*G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>126</v>
+      <c r="H27" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="24" t="str">
+        <f aca="false">IF(I27="","",G27*I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>128</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="25" t="n">
+        <v>161</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="24" t="str">
-        <f aca="false">IF(G28="","",E28*G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="24" t="str">
+        <f aca="false">IF(I28="","",G28*I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E29" s="25" t="n">
+        <v>166</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>170</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="24" t="str">
-        <f aca="false">IF(G29="","",E29*G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="8" t="s">
-        <v>134</v>
+      <c r="H29" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="24" t="str">
+        <f aca="false">IF(I29="","",G29*I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E30" s="25" t="n">
+        <v>173</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="24" t="str">
-        <f aca="false">IF(G30="","",E30*G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="23"/>
+      <c r="J30" s="24" t="str">
+        <f aca="false">IF(I30="","",G30*I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="8" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>140</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="25" t="n">
+        <v>178</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="25" t="n">
         <v>6</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G31" s="23"/>
-      <c r="H31" s="24" t="str">
-        <f aca="false">IF(G31="","",E31*G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="8" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H31" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24" t="str">
+        <f aca="false">IF(I31="","",G31*I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="8" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="25" t="n">
+        <v>183</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>150</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G32" s="23"/>
-      <c r="H32" s="24" t="str">
-        <f aca="false">IF(G32="","",E32*G32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="8" t="s">
-        <v>144</v>
+      <c r="H32" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24" t="str">
+        <f aca="false">IF(I32="","",G32*I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="27" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>145</v>
+        <v>188</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>147</v>
-      </c>
-      <c r="D33" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24" t="str">
+        <f aca="false">IF(I33="","",G33*I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>194</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>195</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G34" s="22" t="n">
+        <v>2400</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="23"/>
+      <c r="J34" s="24" t="str">
+        <f aca="false">IF(I34="","",G34*I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="27" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>202</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E33" s="25" t="n">
+      <c r="D35" s="7" t="s">
+        <v>203</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G33" s="23"/>
-      <c r="H33" s="24" t="str">
-        <f aca="false">IF(G33="","",E33*G33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>150</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>151</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E34" s="22" t="n">
-        <v>2400</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="24" t="str">
-        <f aca="false">IF(G34="","",E34*G34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="27" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
-        <v>154</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="24" t="str">
-        <f aca="false">IF(G35="","",E35*G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="27" t="s">
-        <v>157</v>
+      <c r="H35" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24" t="str">
+        <f aca="false">IF(I35="","",G35*I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="27" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="28"/>
       <c r="B36" s="29" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="28"/>
       <c r="F36" s="28"/>
       <c r="G36" s="28"/>
-      <c r="H36" s="30" t="n">
-        <f aca="false">SUM(H25:H35)</f>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="30" t="n">
+        <f aca="false">SUM(J25:J35)</f>
         <v>0</v>
       </c>
-      <c r="I36" s="28"/>
+      <c r="K36" s="28"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>159</v>
+        <v>207</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -2985,94 +3523,112 @@
       <c r="G37" s="20"/>
       <c r="H37" s="20"/>
       <c r="I37" s="20"/>
-    </row>
-    <row r="38" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+    </row>
+    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>161</v>
-      </c>
-      <c r="C38" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D38" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" s="25" t="n">
+        <v>209</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G38" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F38" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G38" s="23"/>
-      <c r="H38" s="24" t="str">
-        <f aca="false">IF(G38="","",E38*G38)</f>
-        <v/>
-      </c>
-      <c r="I38" s="27" t="s">
-        <v>163</v>
+      <c r="H38" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I38" s="23"/>
+      <c r="J38" s="24" t="str">
+        <f aca="false">IF(I38="","",G38*I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="27" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>165</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>162</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E39" s="22" t="n">
+        <v>215</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G39" s="22" t="n">
         <v>700</v>
       </c>
-      <c r="F39" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G39" s="23"/>
-      <c r="H39" s="24" t="str">
-        <f aca="false">IF(G39="","",E39*G39)</f>
-        <v/>
-      </c>
-      <c r="I39" s="27" t="s">
-        <v>166</v>
+      <c r="H39" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I39" s="23"/>
+      <c r="J39" s="24" t="str">
+        <f aca="false">IF(I39="","",G39*I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="28"/>
       <c r="B40" s="29" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="28"/>
       <c r="F40" s="28"/>
       <c r="G40" s="28"/>
-      <c r="H40" s="30" t="n">
-        <f aca="false">SUM(H38:H39)</f>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="30" t="n">
+        <f aca="false">SUM(J38:J39)</f>
         <v>0</v>
       </c>
-      <c r="I40" s="28"/>
+      <c r="K40" s="28"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="11"/>
       <c r="B42" s="10" t="s">
-        <v>168</v>
+        <v>220</v>
       </c>
       <c r="C42" s="11"/>
       <c r="D42" s="11"/>
       <c r="E42" s="11"/>
       <c r="F42" s="11"/>
       <c r="G42" s="11"/>
-      <c r="H42" s="12" t="n">
-        <f aca="false">H16+H23+H36+H40</f>
+      <c r="H42" s="11"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="12" t="n">
+        <f aca="false">J16+J23+J36+J40</f>
         <v>0</v>
       </c>
-      <c r="I42" s="11"/>
+      <c r="K42" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3090,62 +3646,70 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>169</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>48</v>
+      <c r="K4" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -3155,110 +3719,132 @@
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>172</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="25" t="n">
+        <v>223</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24" t="str">
-        <f aca="false">IF(G6="","",E6*G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="24" t="str">
+        <f aca="false">IF(I6="","",G6*I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="25" t="n">
+        <v>228</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="25" t="n">
         <v>5</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="str">
-        <f aca="false">IF(G7="","",E7*G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24" t="str">
+        <f aca="false">IF(I7="","",G7*I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>177</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="25" t="n">
+        <v>233</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24" t="str">
-        <f aca="false">IF(G8="","",E8*G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>179</v>
+      <c r="H8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24" t="str">
+        <f aca="false">IF(I8="","",G8*I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>237</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28"/>
       <c r="B9" s="29" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C9" s="28"/>
       <c r="D9" s="28"/>
       <c r="E9" s="28"/>
       <c r="F9" s="28"/>
       <c r="G9" s="28"/>
-      <c r="H9" s="30" t="n">
-        <f aca="false">SUM(H6:H8)</f>
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="30" t="n">
+        <f aca="false">SUM(J6:J8)</f>
         <v>0</v>
       </c>
-      <c r="I9" s="28"/>
+      <c r="K9" s="28"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -3268,366 +3854,436 @@
       <c r="G10" s="20"/>
       <c r="H10" s="20"/>
       <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E11" s="22" t="n">
+        <v>239</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>242</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G11" s="22" t="n">
         <v>355</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="str">
-        <f aca="false">IF(G11="","",E11*G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H11" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="24" t="str">
+        <f aca="false">IF(I11="","",G11*I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E12" s="22" t="n">
+        <v>244</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="22" t="n">
         <v>220</v>
       </c>
-      <c r="F12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24" t="str">
-        <f aca="false">IF(G12="","",E12*G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24" t="str">
+        <f aca="false">IF(I12="","",G12*I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="22" t="n">
+        <v>247</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G13" s="22" t="n">
         <v>165</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24" t="str">
-        <f aca="false">IF(G13="","",E13*G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H13" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24" t="str">
+        <f aca="false">IF(I13="","",G13*I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="C14" s="21" t="s">
-        <v>191</v>
-      </c>
-      <c r="D14" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="22" t="n">
+        <v>250</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E14" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="F14" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="22" t="n">
         <v>90</v>
       </c>
-      <c r="F14" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14" s="23"/>
-      <c r="H14" s="24" t="str">
-        <f aca="false">IF(G14="","",E14*G14)</f>
-        <v/>
-      </c>
-      <c r="I14" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H14" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I14" s="23"/>
+      <c r="J14" s="24" t="str">
+        <f aca="false">IF(I14="","",G14*I14)</f>
+        <v/>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>111</v>
+        <v>139</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E15" s="31" t="n">
+        <v>253</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G15" s="31" t="n">
         <v>123.1</v>
       </c>
-      <c r="F15" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15" s="23"/>
-      <c r="H15" s="24" t="str">
-        <f aca="false">IF(G15="","",E15*G15)</f>
-        <v/>
-      </c>
-      <c r="I15" s="8" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H15" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I15" s="23"/>
+      <c r="J15" s="24" t="str">
+        <f aca="false">IF(I15="","",G15*I15)</f>
+        <v/>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>196</v>
+        <v>256</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>198</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E16" s="31" t="n">
+        <v>257</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>258</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G16" s="31" t="n">
         <v>13.7</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="24" t="str">
-        <f aca="false">IF(G16="","",E16*G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>199</v>
+      <c r="H16" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24" t="str">
+        <f aca="false">IF(I16="","",G16*I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>200</v>
-      </c>
-      <c r="B17" s="33" t="s">
-        <v>201</v>
-      </c>
-      <c r="C17" s="32"/>
-      <c r="D17" s="32"/>
-      <c r="E17" s="34" t="n">
-        <f aca="false">SUM(E11:E16)</f>
+        <v>260</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>261</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="33" t="n">
+        <f aca="false">SUM(G11:G16)</f>
         <v>966.8</v>
       </c>
-      <c r="F17" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17" s="35"/>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H17" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>202</v>
+        <v>262</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D18" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E18" s="22" t="n">
+        <v>263</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G18" s="22" t="n">
         <v>120</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="24" t="str">
-        <f aca="false">IF(G18="","",E18*G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H18" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24" t="str">
+        <f aca="false">IF(I18="","",G18*I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>204</v>
+        <v>265</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E19" s="31" t="n">
+        <v>266</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G19" s="31" t="n">
         <v>21.4</v>
       </c>
-      <c r="F19" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="24" t="str">
-        <f aca="false">IF(G19="","",E19*G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>206</v>
+      <c r="H19" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24" t="str">
+        <f aca="false">IF(I19="","",G19*I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>267</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>207</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>208</v>
-      </c>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="34" t="n">
-        <f aca="false">SUM(E18:E19)</f>
+        <v>268</v>
+      </c>
+      <c r="B20" s="29" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="28"/>
+      <c r="D20" s="28"/>
+      <c r="E20" s="28"/>
+      <c r="F20" s="28"/>
+      <c r="G20" s="33" t="n">
+        <f aca="false">SUM(G18:G19)</f>
         <v>141.4</v>
       </c>
-      <c r="F20" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20" s="35"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37"/>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H20" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="28"/>
+      <c r="J20" s="28"/>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>209</v>
+        <v>270</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E21" s="31" t="n">
+        <v>271</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G21" s="31" t="n">
         <v>101.5</v>
       </c>
-      <c r="F21" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24" t="str">
-        <f aca="false">IF(G21="","",E21*G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24" t="str">
+        <f aca="false">IF(I21="","",G21*I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="27" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>212</v>
+        <v>275</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>185</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="E22" s="31" t="n">
+        <v>276</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>245</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>254</v>
+      </c>
+      <c r="G22" s="31" t="n">
         <v>197.3</v>
       </c>
-      <c r="F22" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22" s="23"/>
-      <c r="H22" s="24" t="str">
-        <f aca="false">IF(G22="","",E22*G22)</f>
-        <v/>
-      </c>
-      <c r="I22" s="27" t="s">
-        <v>214</v>
+      <c r="H22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="23"/>
+      <c r="J22" s="24" t="str">
+        <f aca="false">IF(I22="","",G22*I22)</f>
+        <v/>
+      </c>
+      <c r="K22" s="27" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="34" t="n">
-        <f aca="false">SUM(E21:E22)</f>
+        <v>278</v>
+      </c>
+      <c r="B23" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="C23" s="28"/>
+      <c r="D23" s="28"/>
+      <c r="E23" s="28"/>
+      <c r="F23" s="28"/>
+      <c r="G23" s="33" t="n">
+        <f aca="false">SUM(G21:G22)</f>
         <v>298.8</v>
       </c>
-      <c r="F23" s="32" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23" s="35"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="37"/>
+      <c r="H23" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
+      <c r="K23" s="28"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>217</v>
+        <v>280</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="30" t="n">
-        <f aca="false">SUM(H11:H23)</f>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="30" t="n">
+        <f aca="false">SUM(J11:J23)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="28"/>
+      <c r="K24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -3637,196 +4293,234 @@
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>220</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="25" t="n">
-        <f aca="false">SUM(E11:E16)+SUM(E18:E19)+SUM(E21:E22)</f>
+        <v>282</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G26" s="25" t="n">
+        <f aca="false">SUM(G11:G16)+SUM(G18:G19)+SUM(G21:G22)</f>
         <v>1407</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="38" t="str">
-        <f aca="false">IF(G26="","",E26*G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="8" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H26" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="35" t="str">
+        <f aca="false">IF(I26="","",G26*I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>223</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>224</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E27" s="31" t="n">
-        <f aca="false">ROUND(SUM(E11:E16)*2.56/27,1)</f>
+        <v>288</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>291</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G27" s="31" t="n">
+        <f aca="false">ROUND(SUM(G11:G16)*2.56/27,1)</f>
         <v>91.7</v>
       </c>
-      <c r="F27" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="38" t="str">
-        <f aca="false">IF(G27="","",E27*G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="8" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H27" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="35" t="str">
+        <f aca="false">IF(I27="","",G27*I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>228</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E28" s="31" t="n">
-        <f aca="false">ROUND(SUM(E18:E19)*4.34/27,1)</f>
+        <v>294</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>290</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>296</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G28" s="31" t="n">
+        <f aca="false">ROUND(SUM(G18:G19)*4.34/27,1)</f>
         <v>22.7</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="G28" s="23"/>
-      <c r="H28" s="38" t="str">
-        <f aca="false">IF(G28="","",E28*G28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="8" t="s">
-        <v>229</v>
+      <c r="H28" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="I28" s="23"/>
+      <c r="J28" s="35" t="str">
+        <f aca="false">IF(I28="","",G28*I28)</f>
+        <v/>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="E29" s="31" t="n">
-        <f aca="false">ROUND(SUM(E21:E22)*0.83/27,1)</f>
+        <v>298</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>301</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <f aca="false">ROUND(SUM(G21:G22)*0.83/27,1)</f>
         <v>9.2</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>225</v>
-      </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="38" t="str">
-        <f aca="false">IF(G29="","",E29*G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="27" t="s">
-        <v>232</v>
+      <c r="H29" s="21" t="s">
+        <v>292</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="35" t="str">
+        <f aca="false">IF(I29="","",G29*I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="27" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>233</v>
-      </c>
-      <c r="C30" s="21" t="s">
-        <v>234</v>
-      </c>
-      <c r="D30" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E30" s="22" t="n">
+        <v>303</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G30" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F30" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G30" s="23"/>
-      <c r="H30" s="24" t="str">
-        <f aca="false">IF(G30="","",E30*G30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="8" t="s">
-        <v>235</v>
-      </c>
+      <c r="H30" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I30" s="23"/>
+      <c r="J30" s="24" t="str">
+        <f aca="false">IF(I30="","",G30*I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="8"/>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>236</v>
-      </c>
-      <c r="C31" s="21" t="s">
-        <v>237</v>
-      </c>
-      <c r="D31" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E31" s="22" t="n">
+        <v>307</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G31" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G31" s="23"/>
-      <c r="H31" s="24" t="str">
-        <f aca="false">IF(G31="","",E31*G31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="8"/>
+      <c r="H31" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24" t="str">
+        <f aca="false">IF(I31="","",G31*I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="8"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="28"/>
       <c r="B32" s="29" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="C32" s="28"/>
       <c r="D32" s="28"/>
       <c r="E32" s="28"/>
       <c r="F32" s="28"/>
       <c r="G32" s="28"/>
-      <c r="H32" s="30" t="n">
-        <f aca="false">SUM(H26:H31)</f>
+      <c r="H32" s="28"/>
+      <c r="I32" s="28"/>
+      <c r="J32" s="30" t="n">
+        <f aca="false">SUM(J26:J31)</f>
         <v>0</v>
       </c>
-      <c r="I32" s="28"/>
+      <c r="K32" s="28"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>238</v>
+        <v>310</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -3836,150 +4530,178 @@
       <c r="G33" s="20"/>
       <c r="H33" s="20"/>
       <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>239</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="E34" s="22" t="n">
+        <v>311</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G34" s="22" t="n">
         <v>1600</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G34" s="23"/>
-      <c r="H34" s="24" t="str">
-        <f aca="false">IF(G34="","",E34*G34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="27" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I34" s="23"/>
+      <c r="J34" s="24" t="str">
+        <f aca="false">IF(I34="","",G34*I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="27" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>242</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E35" s="22" t="n">
+        <v>316</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G35" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G35" s="23"/>
-      <c r="H35" s="24" t="str">
-        <f aca="false">IF(G35="","",E35*G35)</f>
-        <v/>
-      </c>
-      <c r="I35" s="8" t="s">
-        <v>244</v>
+      <c r="H35" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I35" s="23"/>
+      <c r="J35" s="24" t="str">
+        <f aca="false">IF(I35="","",G35*I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="8" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>245</v>
+        <v>321</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>247</v>
-      </c>
-      <c r="D36" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E36" s="22" t="n">
+        <v>322</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>324</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G36" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G36" s="23"/>
-      <c r="H36" s="24" t="str">
-        <f aca="false">IF(G36="","",E36*G36)</f>
-        <v/>
-      </c>
-      <c r="I36" s="27" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H36" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24" t="str">
+        <f aca="false">IF(I36="","",G36*I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>250</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>243</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E37" s="25" t="n">
+        <v>328</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>329</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>330</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G37" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F37" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G37" s="23"/>
-      <c r="H37" s="24" t="str">
-        <f aca="false">IF(G37="","",E37*G37)</f>
-        <v/>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>251</v>
-      </c>
+      <c r="H37" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24" t="str">
+        <f aca="false">IF(I37="","",G37*I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="8"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="28"/>
       <c r="B38" s="29" t="s">
-        <v>167</v>
+        <v>219</v>
       </c>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
       <c r="G38" s="28"/>
-      <c r="H38" s="30" t="n">
-        <f aca="false">SUM(H34:H37)</f>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="30" t="n">
+        <f aca="false">SUM(J34:J37)</f>
         <v>0</v>
       </c>
-      <c r="I38" s="28"/>
+      <c r="K38" s="28"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11"/>
       <c r="B40" s="10" t="s">
-        <v>252</v>
+        <v>331</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
       <c r="E40" s="11"/>
       <c r="F40" s="11"/>
       <c r="G40" s="11"/>
-      <c r="H40" s="12" t="n">
-        <f aca="false">H9+H24+H32+H38</f>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12" t="n">
+        <f aca="false">J9+J24+J32+J38</f>
         <v>0</v>
       </c>
-      <c r="I40" s="11"/>
+      <c r="K40" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3997,62 +4719,70 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="9"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>253</v>
+        <v>332</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="J4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>48</v>
+      <c r="K4" s="6" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>254</v>
+        <v>333</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -4062,246 +4792,298 @@
       <c r="G5" s="20"/>
       <c r="H5" s="20"/>
       <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
     </row>
     <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>255</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>256</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="25" t="n">
+        <v>334</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>335</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>336</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6" s="23"/>
-      <c r="H6" s="24" t="str">
-        <f aca="false">IF(G6="","",E6*G6)</f>
-        <v/>
-      </c>
-      <c r="I6" s="27" t="s">
-        <v>257</v>
+      <c r="H6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="23"/>
+      <c r="J6" s="24" t="str">
+        <f aca="false">IF(I6="","",G6*I6)</f>
+        <v/>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>258</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="25" t="n">
+        <v>339</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="23"/>
-      <c r="H7" s="24" t="str">
-        <f aca="false">IF(G7="","",E7*G7)</f>
-        <v/>
-      </c>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="23"/>
+      <c r="J7" s="24" t="str">
+        <f aca="false">IF(I7="","",G7*I7)</f>
+        <v/>
+      </c>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>259</v>
-      </c>
-      <c r="C8" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="25" t="n">
+        <v>343</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>345</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G8" s="23"/>
-      <c r="H8" s="24" t="str">
-        <f aca="false">IF(G8="","",E8*G8)</f>
-        <v/>
-      </c>
-      <c r="I8" s="27" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="23"/>
+      <c r="J8" s="24" t="str">
+        <f aca="false">IF(I8="","",G8*I8)</f>
+        <v/>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>261</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>262</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="25" t="n">
+        <v>347</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>348</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>349</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="24" t="str">
-        <f aca="false">IF(G9="","",E9*G9)</f>
-        <v/>
-      </c>
-      <c r="I9" s="27" t="s">
-        <v>263</v>
+      <c r="H9" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="23"/>
+      <c r="J9" s="24" t="str">
+        <f aca="false">IF(I9="","",G9*I9)</f>
+        <v/>
+      </c>
+      <c r="K9" s="27" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>264</v>
-      </c>
-      <c r="C10" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D10" s="21" t="s">
+        <v>352</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E10" s="25" t="n">
+      <c r="D10" s="7" t="s">
+        <v>353</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G10" s="23"/>
-      <c r="H10" s="24" t="str">
-        <f aca="false">IF(G10="","",E10*G10)</f>
-        <v/>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H10" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="23"/>
+      <c r="J10" s="24" t="str">
+        <f aca="false">IF(I10="","",G10*I10)</f>
+        <v/>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
+        <v>91</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>356</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="F11" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>267</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D11" s="21" t="s">
+      <c r="G11" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="23"/>
+      <c r="J11" s="24" t="str">
+        <f aca="false">IF(I11="","",G11*I11)</f>
+        <v/>
+      </c>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>359</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="25" t="n">
+      <c r="D12" s="7" t="s">
+        <v>360</v>
+      </c>
+      <c r="E12" s="21" t="s">
+        <v>361</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="F11" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G11" s="23"/>
-      <c r="H11" s="24" t="str">
-        <f aca="false">IF(G11="","",E11*G11)</f>
-        <v/>
-      </c>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>268</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>269</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12" s="25" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="23"/>
-      <c r="H12" s="24" t="str">
-        <f aca="false">IF(G12="","",E12*G12)</f>
-        <v/>
-      </c>
-      <c r="I12" s="27" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H12" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="23"/>
+      <c r="J12" s="24" t="str">
+        <f aca="false">IF(I12="","",G12*I12)</f>
+        <v/>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="21" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>271</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>272</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E13" s="25" t="n">
+        <v>363</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>365</v>
+      </c>
+      <c r="E13" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="F13" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G13" s="23"/>
-      <c r="H13" s="24" t="str">
-        <f aca="false">IF(G13="","",E13*G13)</f>
-        <v/>
-      </c>
-      <c r="I13" s="8" t="s">
-        <v>273</v>
+      <c r="H13" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I13" s="23"/>
+      <c r="J13" s="24" t="str">
+        <f aca="false">IF(I13="","",G13*I13)</f>
+        <v/>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>367</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28"/>
       <c r="B14" s="29" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
       <c r="F14" s="28"/>
       <c r="G14" s="28"/>
-      <c r="H14" s="30" t="n">
-        <f aca="false">SUM(H6:H13)</f>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="30" t="n">
+        <f aca="false">SUM(J6:J13)</f>
         <v>0</v>
       </c>
-      <c r="I14" s="28"/>
+      <c r="K14" s="28"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>274</v>
+        <v>368</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -4311,241 +5093,289 @@
       <c r="G15" s="20"/>
       <c r="H15" s="20"/>
       <c r="I15" s="20"/>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>97</v>
+        <v>117</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E16" s="25" t="n">
+        <v>369</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>370</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="E16" s="21" t="s">
+        <v>372</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F16" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="23"/>
-      <c r="H16" s="24" t="str">
-        <f aca="false">IF(G16="","",E16*G16)</f>
-        <v/>
-      </c>
-      <c r="I16" s="8"/>
+      <c r="H16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="23"/>
+      <c r="J16" s="24" t="str">
+        <f aca="false">IF(I16="","",G16*I16)</f>
+        <v/>
+      </c>
+      <c r="K16" s="8"/>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="25" t="n">
+        <v>373</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>374</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>375</v>
+      </c>
+      <c r="E17" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F17" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G17" s="23"/>
-      <c r="H17" s="24" t="str">
-        <f aca="false">IF(G17="","",E17*G17)</f>
-        <v/>
-      </c>
-      <c r="I17" s="27" t="s">
-        <v>278</v>
+      <c r="H17" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="23"/>
+      <c r="J17" s="24" t="str">
+        <f aca="false">IF(I17="","",G17*I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="27" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>279</v>
-      </c>
-      <c r="C18" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D18" s="21" t="s">
+        <v>378</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>379</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>380</v>
+      </c>
+      <c r="E18" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F18" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="23"/>
+      <c r="J18" s="24" t="str">
+        <f aca="false">IF(I18="","",G18*I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="8"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>133</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>381</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>382</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>383</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>384</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="23"/>
+      <c r="J19" s="24" t="str">
+        <f aca="false">IF(I19="","",G19*I19)</f>
+        <v/>
+      </c>
+      <c r="K19" s="8"/>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>139</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>387</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="23"/>
+      <c r="J20" s="24" t="str">
+        <f aca="false">IF(I20="","",G20*I20)</f>
+        <v/>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>389</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>392</v>
+      </c>
+      <c r="F21" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G21" s="25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I21" s="23"/>
+      <c r="J21" s="24" t="str">
+        <f aca="false">IF(I21="","",G21*I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="8"/>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>260</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>393</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E18" s="25" t="n">
+      <c r="D22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F22" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I22" s="36"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="27" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>397</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G23" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F18" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G18" s="23"/>
-      <c r="H18" s="24" t="str">
-        <f aca="false">IF(G18="","",E18*G18)</f>
-        <v/>
-      </c>
-      <c r="I18" s="8"/>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>280</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="D19" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G19" s="23"/>
-      <c r="H19" s="24" t="str">
-        <f aca="false">IF(G19="","",E19*G19)</f>
-        <v/>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="C20" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="D20" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="23"/>
-      <c r="H20" s="24" t="str">
-        <f aca="false">IF(G20="","",E20*G20)</f>
-        <v/>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E21" s="25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="23"/>
-      <c r="H21" s="24" t="str">
-        <f aca="false">IF(G21="","",E21*G21)</f>
-        <v/>
-      </c>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
-        <v>200</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>287</v>
-      </c>
-      <c r="C22" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D22" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E22" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="39"/>
-      <c r="H22" s="38"/>
-      <c r="I22" s="27" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
-        <v>202</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>291</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E23" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G23" s="23"/>
-      <c r="H23" s="24" t="str">
-        <f aca="false">IF(G23="","",E23*G23)</f>
-        <v/>
-      </c>
-      <c r="I23" s="8" t="s">
-        <v>292</v>
-      </c>
+      <c r="H23" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="24" t="str">
+        <f aca="false">IF(I23="","",G23*I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="8"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
       <c r="E24" s="28"/>
       <c r="F24" s="28"/>
       <c r="G24" s="28"/>
-      <c r="H24" s="30" t="n">
-        <f aca="false">SUM(H16:H23)</f>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="30" t="n">
+        <f aca="false">SUM(J16:J23)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="28"/>
+      <c r="K24" s="28"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>293</v>
+        <v>399</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -4555,133 +5385,161 @@
       <c r="G25" s="20"/>
       <c r="H25" s="20"/>
       <c r="I25" s="20"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>294</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>295</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" s="22" t="n">
+        <v>400</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>401</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>402</v>
+      </c>
+      <c r="E26" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G26" s="22" t="n">
         <v>1800</v>
       </c>
-      <c r="F26" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26" s="23"/>
-      <c r="H26" s="24" t="str">
-        <f aca="false">IF(G26="","",E26*G26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="27" t="s">
-        <v>296</v>
+      <c r="H26" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="23"/>
+      <c r="J26" s="24" t="str">
+        <f aca="false">IF(I26="","",G26*I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="27" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>121</v>
+        <v>152</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>297</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E27" s="22" t="n">
+        <v>405</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>407</v>
+      </c>
+      <c r="E27" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="F27" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G27" s="22" t="n">
         <v>1400</v>
       </c>
-      <c r="F27" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" s="23"/>
-      <c r="H27" s="24" t="str">
-        <f aca="false">IF(G27="","",E27*G27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="27" t="s">
-        <v>299</v>
+      <c r="H27" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="23"/>
+      <c r="J27" s="24" t="str">
+        <f aca="false">IF(I27="","",G27*I27)</f>
+        <v/>
+      </c>
+      <c r="K27" s="27" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>124</v>
+        <v>156</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="C28" s="21" t="s">
-        <v>276</v>
-      </c>
-      <c r="D28" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="E28" s="25" t="n">
+        <v>410</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="21" t="s">
+        <v>376</v>
+      </c>
+      <c r="F28" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="G28" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G28" s="39"/>
-      <c r="H28" s="38"/>
-      <c r="I28" s="8" t="s">
-        <v>301</v>
+      <c r="H28" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="36"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="8" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>127</v>
+        <v>160</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>302</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="D29" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="E29" s="22" t="n">
+        <v>412</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="E29" s="21" t="s">
+        <v>414</v>
+      </c>
+      <c r="F29" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="G29" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="F29" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="G29" s="23"/>
-      <c r="H29" s="24" t="str">
-        <f aca="false">IF(G29="","",E29*G29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="8"/>
+      <c r="H29" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I29" s="23"/>
+      <c r="J29" s="24" t="str">
+        <f aca="false">IF(I29="","",G29*I29)</f>
+        <v/>
+      </c>
+      <c r="K29" s="8"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28"/>
       <c r="B30" s="29" t="s">
-        <v>158</v>
+        <v>206</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
       <c r="E30" s="28"/>
       <c r="F30" s="28"/>
       <c r="G30" s="28"/>
-      <c r="H30" s="30" t="n">
-        <f aca="false">SUM(H26:H29)</f>
+      <c r="H30" s="28"/>
+      <c r="I30" s="28"/>
+      <c r="J30" s="30" t="n">
+        <f aca="false">SUM(J26:J29)</f>
         <v>0</v>
       </c>
-      <c r="I30" s="28"/>
+      <c r="K30" s="28"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>304</v>
+        <v>415</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -4691,122 +5549,150 @@
       <c r="G31" s="20"/>
       <c r="H31" s="20"/>
       <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>160</v>
+        <v>208</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>305</v>
-      </c>
-      <c r="C32" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D32" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E32" s="25" t="n">
+        <v>416</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G32" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="G32" s="39"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="27" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H32" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I32" s="36"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>164</v>
+        <v>214</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>308</v>
-      </c>
-      <c r="C33" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E33" s="25" t="n">
+        <v>418</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G33" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="G33" s="39"/>
-      <c r="H33" s="38"/>
-      <c r="I33" s="27" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H33" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I33" s="36"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="27" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>245</v>
+        <v>321</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>309</v>
-      </c>
-      <c r="C34" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D34" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E34" s="25" t="n">
+        <v>419</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F34" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G34" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="G34" s="39"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="27" t="s">
-        <v>310</v>
+      <c r="H34" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I34" s="36"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="27" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>249</v>
+        <v>327</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>311</v>
-      </c>
-      <c r="C35" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="E35" s="25" t="n">
+        <v>421</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="21" t="s">
+        <v>394</v>
+      </c>
+      <c r="F35" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="G35" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="21" t="s">
-        <v>306</v>
-      </c>
-      <c r="G35" s="39"/>
-      <c r="H35" s="38"/>
-      <c r="I35" s="27" t="s">
-        <v>307</v>
+      <c r="H35" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I35" s="36"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="27" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11"/>
       <c r="B37" s="10" t="s">
-        <v>312</v>
+        <v>422</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
       <c r="E37" s="11"/>
       <c r="F37" s="11"/>
       <c r="G37" s="11"/>
-      <c r="H37" s="12" t="n">
-        <f aca="false">H14+H24+H30</f>
+      <c r="H37" s="11"/>
+      <c r="I37" s="11"/>
+      <c r="J37" s="12" t="n">
+        <f aca="false">J14+J24+J30</f>
         <v>0</v>
       </c>
-      <c r="I37" s="11"/>
+      <c r="K37" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4824,7 +5710,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C48"/>
+  <dimension ref="B2:C52"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -4833,326 +5719,358 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="40" t="s">
-        <v>313</v>
+      <c r="B2" s="37" t="s">
+        <v>423</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="41" t="s">
-        <v>314</v>
-      </c>
-      <c r="C4" s="42"/>
+      <c r="B4" s="38" t="s">
+        <v>424</v>
+      </c>
+      <c r="C4" s="39"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="43" t="s">
-        <v>315</v>
+      <c r="B5" s="40" t="s">
+        <v>425</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>316</v>
+        <v>426</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="43" t="s">
-        <v>317</v>
+      <c r="B6" s="40" t="s">
+        <v>427</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>318</v>
+        <v>428</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="43" t="s">
-        <v>319</v>
+      <c r="B7" s="40" t="s">
+        <v>429</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>320</v>
+        <v>430</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>321</v>
-      </c>
-      <c r="C9" s="42"/>
+      <c r="B9" s="38" t="s">
+        <v>431</v>
+      </c>
+      <c r="C9" s="39"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="43" t="s">
-        <v>65</v>
+      <c r="B10" s="40" t="s">
+        <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>322</v>
+        <v>432</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="43" t="s">
-        <v>194</v>
+      <c r="B11" s="40" t="s">
+        <v>254</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>323</v>
+        <v>433</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="43" t="s">
-        <v>53</v>
+      <c r="B12" s="40" t="s">
+        <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>324</v>
+        <v>434</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="43" t="s">
-        <v>152</v>
+      <c r="B13" s="40" t="s">
+        <v>199</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="43" t="s">
-        <v>326</v>
+        <v>435</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="40" t="s">
+        <v>436</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="41" t="s">
-        <v>328</v>
-      </c>
-      <c r="C16" s="42"/>
-    </row>
-    <row r="17" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="43" t="s">
-        <v>329</v>
-      </c>
-      <c r="C17" s="8" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="43" t="s">
-        <v>331</v>
+        <v>437</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="40" t="s">
+        <v>438</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="38" t="s">
+        <v>440</v>
+      </c>
+      <c r="C17" s="39"/>
+    </row>
+    <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B18" s="40" t="s">
+        <v>441</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>332</v>
+        <v>442</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="s">
-        <v>333</v>
+      <c r="B19" s="40" t="s">
+        <v>443</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>334</v>
+        <v>444</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="s">
-        <v>335</v>
+      <c r="B20" s="40" t="s">
+        <v>445</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="s">
-        <v>337</v>
+        <v>446</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="40" t="s">
+        <v>447</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>338</v>
+        <v>448</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="s">
-        <v>339</v>
+      <c r="B22" s="40" t="s">
+        <v>449</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>340</v>
+        <v>450</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="s">
-        <v>341</v>
+      <c r="B23" s="40" t="s">
+        <v>451</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>342</v>
+        <v>452</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="s">
-        <v>343</v>
+      <c r="B24" s="40" t="s">
+        <v>453</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>344</v>
+        <v>454</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="s">
-        <v>345</v>
+      <c r="B25" s="40" t="s">
+        <v>455</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>346</v>
+        <v>456</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="s">
-        <v>347</v>
+      <c r="B26" s="40" t="s">
+        <v>457</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="41" t="s">
-        <v>349</v>
-      </c>
-      <c r="C28" s="42"/>
-    </row>
-    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="43" t="s">
-        <v>350</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="43" t="s">
-        <v>352</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="43" t="s">
-        <v>354</v>
+        <v>458</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B27" s="40" t="s">
+        <v>459</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B28" s="40" t="s">
+        <v>461</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="38" t="s">
+        <v>463</v>
+      </c>
+      <c r="C30" s="39"/>
+    </row>
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B31" s="40" t="s">
+        <v>464</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>355</v>
+        <v>465</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="43" t="s">
-        <v>356</v>
+      <c r="B32" s="40" t="s">
+        <v>466</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="43" t="s">
-        <v>358</v>
+        <v>467</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B33" s="40" t="s">
+        <v>468</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>359</v>
+        <v>469</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="43" t="s">
-        <v>360</v>
+      <c r="B34" s="40" t="s">
+        <v>470</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>361</v>
+        <v>471</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="43" t="s">
-        <v>362</v>
+      <c r="B35" s="40" t="s">
+        <v>472</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>363</v>
+        <v>473</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="43" t="s">
-        <v>364</v>
+      <c r="B36" s="40" t="s">
+        <v>474</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="41" t="s">
-        <v>366</v>
-      </c>
-      <c r="C38" s="42"/>
-    </row>
-    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="43" t="s">
-        <v>367</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="43" t="s">
-        <v>369</v>
-      </c>
-      <c r="C40" s="8" t="s">
-        <v>370</v>
-      </c>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B37" s="40" t="s">
+        <v>476</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="40" t="s">
+        <v>478</v>
+      </c>
+      <c r="C38" s="8" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="38" t="s">
+        <v>480</v>
+      </c>
+      <c r="C40" s="39"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="43" t="s">
-        <v>371</v>
+      <c r="B41" s="40" t="s">
+        <v>481</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>372</v>
+        <v>482</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="43" t="s">
-        <v>373</v>
+      <c r="B42" s="40" t="s">
+        <v>483</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>374</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="43" t="s">
-        <v>375</v>
+      <c r="B43" s="40" t="s">
+        <v>485</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>376</v>
+        <v>486</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="43" t="s">
-        <v>377</v>
+      <c r="B44" s="40" t="s">
+        <v>487</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>378</v>
+        <v>488</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="43" t="s">
-        <v>379</v>
+      <c r="B45" s="40" t="s">
+        <v>489</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>380</v>
+        <v>490</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="43" t="s">
-        <v>381</v>
+      <c r="B46" s="40" t="s">
+        <v>491</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>382</v>
+        <v>492</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="43" t="s">
-        <v>383</v>
+      <c r="B47" s="40" t="s">
+        <v>493</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>384</v>
+        <v>494</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="43" t="s">
-        <v>385</v>
+      <c r="B48" s="40" t="s">
+        <v>495</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>386</v>
+        <v>496</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="40" t="s">
+        <v>497</v>
+      </c>
+      <c r="C49" s="8" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="40" t="s">
+        <v>499</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="40" t="s">
+        <v>501</v>
+      </c>
+      <c r="C51" s="8" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="40" t="s">
+        <v>503</v>
+      </c>
+      <c r="C52" s="8" t="s">
+        <v>504</v>
       </c>
     </row>
   </sheetData>

--- a/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
+++ b/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
@@ -12,7 +12,8 @@
     <sheet name="Site Electrical" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Telecom OSP" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Security" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Assumptions" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Materials &amp; Makes" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="505">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="699">
   <si>
     <t xml:space="preserve">DETAILED QUANTITY TAKEOFF — EXTERIOR ELECTRICAL &amp; COMMUNICATIONS</t>
   </si>
@@ -545,16 +546,16 @@
     <t xml:space="preserve">C6</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EB1 — exterior LED bollard, at grade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">277V; 3000K, 80 CRI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Luminis RADB-LED-P1-30K-SYM-PIR-BTT-BCF-HXX-DDXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6 bollards along Bldg A south walk; integral PIR.</t>
+    <t xml:space="preserve">Fixture EB1 — exterior LED bollard (RADEAN), at grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-1/4" dia x 41-1/2" H; 277V; 3000K, 80 CRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADB-LED-P1-30K-SYM-PIR-BTT-BCF-HXX-DDXX (schedule lists 'Luminis'; RADB is a Lithonia/Acuity RADEAN model — see RFI-13)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 bollards along Bldg A south walk; integral PIR, symmetric distribution.</t>
   </si>
   <si>
     <t xml:space="preserve">C7</t>
@@ -578,13 +579,13 @@
     <t xml:space="preserve">C8</t>
   </si>
   <si>
-    <t xml:space="preserve">Fixture EF1 — exterior flagpole light, truck (trunnion) mounted</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Remote-driver LED; 3000K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eagle Mountain SG-3K-EHS-M-XX</t>
+    <t xml:space="preserve">Fixture EF1 — exterior flagpole downlight, truck mounted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size M (flags to 15'x25'); 3000K; remote driver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eagle Mountain Flag &amp; Flagpole 'StarGazer' SG-3K-EHS-M-XX (external-halyard stationary truck, dark-sky downlight)</t>
   </si>
   <si>
     <t xml:space="preserve">3 at flagpoles NW of Bldg A. Schedule voltage column shows 0V at 65% — driver remote (see C9).</t>
@@ -1295,6 +1296,555 @@
     <t xml:space="preserve">SECURITY TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">MATERIALS, MAKES &amp; MODELS — PROCUREMENT LIST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Specified' = named on the 65% drawings. 'Basis-of-design (suggested)' = drawings silent — a common product meeting the drawn requirements, offered for pricing only; Div 26/27/28 specs govern. Qty cells link live to the takeoff tabs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cat.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size / Rating</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Model / Part No.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spec Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIGHTING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area luminaire EA1 (Type 3, backlight control, house-side shield)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35' pole mt; 277V; 3000K/80CRI; P3 pkg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithonia Lighting (Acuity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSX1-LED-P3-30K-80CRI-BLC3-MVOLT-XXXX-PIR-SPD20KV-HS-EGSR-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Specified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D-Series Size 1. Wattage/lumen columns blank on 65% schedule — per fixture submittal. XXXX = distribution/finish fields to complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area luminaire EA2 (Type 5 wide)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSX1-LED-P3-30K-80CRI-T5W-MVOLT-XXXX-PIR-SPD20KV-EGSR-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan symbol shows twin heads/pole — RFI-3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Area luminaire EA3 (short-throw T1S, house-side shield)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DSX1-LED-P3-30K-80CRI-T1S-MVOLT-XXXX-PIR-SPD20KV-HS-EGSR-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Light pole, round straight steel or aluminum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35'-0 nominal; drilled for D-Series arm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valmont / RSA / Lithonia SSS (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per luminaire mfr pole selector, EPA per wind load</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pole make/finish NOT scheduled at 65% — coordinate w/ luminaire order; anchor bolts per mfr (2/ES601).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LED bollard EB1 (RADEAN)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8-1/4" dia x 41-1/2" H; 277V; 3000K/80CRI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lithonia Lighting (Acuity) — schedule says 'Luminis'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADB-LED-P1-30K-SYM-PIR-BTT-BCF-HXX-DDXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RADB is Lithonia's RADEAN bollard (Luminis is a sister Acuity brand) — RFI-13 to correct schedule mfr.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flagpole downlight EF1 (StarGazer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Size M (flags to 15'x25'); 3000K; LED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eagle Mountain Flag &amp; Flagpole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SG-3K-EHS-M-XX (external halyard, stationary truck)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dark-sky downlight; remote drivers in buried WP box (ES101 KN 10).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WP enclosure for EF1 remote drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burial/landscape rated, NEMA 4/6P (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBD (per driver mfr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify enclosure &amp; driver model w/ Eagle Mountain submittal.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SERVICE &amp; POWER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pad-mount transformer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">480/277V 3-ph; kVA TBD by utility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xcel Energy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">By Others</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XE furnished/installed; pad &amp; grounding by GC/EC.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meter housing + CT cabinet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per XE metering standard; NEMA 3R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milbank / B-Line (or per XE approved list)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per XE metering spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BOD (suggested)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EC furnishes/installs housing; XE sets meter (ES101 KN 4).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exterior JB for gate operator power</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Min 4-11/16" sq (NEC 314); NEMA 3R/4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hoffman / Wiegmann (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Galvanized steel, gasketed, stamped</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per ES101 KN 7; 2#10+1#10G, 3/4"C, 120V.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ground rods &amp; bonding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5/8" x 8' (assumed); #6 bare Cu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ERICO / Harger (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cu-clad rod + exothermic or irreversible compression</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rod size not on drawings — confirm Div 26 spec.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TELECOM OSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom maintenance hole MH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8'-0" x 96" x 96"; base 9,275 lb / top 2,100 lb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Oldcastle / Jensen Precast (or regional precaster)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'4260' base + top deck per H1/TSN400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'4260' designation from detail — confirm precaster &amp; traffic rating of cover.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom handhole HH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hubbell/Quazite or Armorcast (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polymer concrete box + slip-resistant bolted cover, ANSI Tier (non-deliberate traffic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOT vehicle-traffic rated per A1/TSN400 — keep out of pavement.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct bank conduit, 4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4" PVC Type DB/EB (concrete-encased)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantex / JM Eagle (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB-60/DB-120 PVC duct</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduit-feet: DB1 LF x2 + DB2 LF x4 (live formula).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct bank conduit, 2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2" PVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sch 40/DB PVC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB3 LF x 2 conduits (live formula).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabric innerduct, 4" 3-cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4", 3-cell, w/ pull tapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxCell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxCell 4" 3-cell (MXE4 series)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'MaxCell' named on TSN100 duct bank schedule — one per conduit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabric innerduct, 2" 3-cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2", 3-cell, w/ pull tapes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxCell 2" 3-cell (MXE2 series)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One per DB3 conduit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP fiber, 12-strand OM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12F OM4 50/125 MM, OSP gel-free</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corning / OFS (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e.g. Corning ALTOS 012TU4-T4790D20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type on TSN300 is generic '12-STRAND OM4 FIBER' — exact cable per Div 27 spec.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber termination hardware @ Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12F LC (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corning CCH / Panduit (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LIU/patch panel + pigtails/splice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OTDR + IL testing per TIA; labeling per TIA-606.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Detectable warning tape &amp; mule tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6" tape @12" above duct; 1,250-lb tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Presco / Neptco (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"CAUTION BURIED TELECOM" + WP1250 mule tape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tape LF = trench LF (live).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SECURITY (Div 28 — models per spec; BOD offered where drawings silent)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video intercom door/pedestal station w/ integrated reader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PoE; vandal/weather resistant; flush or pedestal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aiphone (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IX Series 2 (e.g. IX-DVM) + reader module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Matches 'VIC' video intercom system &amp; extended-reach PoE copper architecture (TSY101).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Video intercom master station</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop, video</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IX-MV7-* master</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desktop mount per TSY001 schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gooseneck pedestal, 316 SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">48" above roadway; min 2" sq heavy wall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedestal PRO (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">316 SS gooseneck w/ template L-bolts x4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Welded 316 SS required by A1/TSY101; footer to frost +20" from curb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card readers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mullion/single-gang; 3'-6" AFF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HID (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Signo 20 / 20K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reader tech (prox/SEOS/PIV) per DOE requirements — confirm; boxes per TSY001 schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Access control panels ACP1/ACP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Surface mt 5'-0" AFF on fire-rated plywood</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LenelS2 / Software House / Mercury-based (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Div 28 spec &amp; DOE standard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Head-end platform not named on drawings — owner standard governs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate position switch (DPS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Industrial gate switch w/ armored lead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sentrol/Edwards 2500-series (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">e.g. 2507A w/ magnet &amp; bracket</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per A7/TSY101: magnet on gate, switch on fence post, WP 1-gang box, 3/4"C to HH.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle exit loops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preformed loop size per operator mfr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EMX / Reno A&amp;E (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preformed loop + matching detector in operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate operators (36' cantilever slide gates per C-502/C-503) by others.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended-reach PoE copper data cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-pair, 22 AWG min, OSP-rated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paige (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GameChanger PD2201EX (OSP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Named performance (extended-reach, 22AWG, PoE) on TSY101/QC — GameChanger is the common BOD; verify E gate run length vs. mfr limit.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP access control composite cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reader/lock/DPS/REX composite, OSP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Windy City Wire / West Penn (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per Div 28 spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment rack + SPDs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12U rack; SPDs on OSP copper &amp; device circuits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Middle Atlantic / CPI; DITEK (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12U wall rack; DTK series SPD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rack per G2/TSY101; SPD line item Security B8.</t>
+  </si>
+  <si>
     <t xml:space="preserve">ASSUMPTIONS, CLARIFICATIONS &amp; EXCLUSIONS</t>
   </si>
   <si>
@@ -1539,6 +2089,39 @@
   </si>
   <si>
     <t xml:space="preserve">Confirm transformer kVA, generator kW/recertification requirements, and secondary conductor/conduit schedule (one-line, building package).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFI-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES601 luminaire schedule lists EB1 manufacturer as 'Luminis', but model RADB-LED is Lithonia Lighting's RADEAN bollard (both Acuity brands) — confirm intended manufacturer/model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RFI-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complete the 'XXXX' placeholder fields in the DSX1 catalog strings (finish/options) and the blank wattage/lumen/CCT columns of the luminaire schedule.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6. MATERIALS &amp; MAKES TAB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Method</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The 'Materials &amp; Makes' tab consolidates every product into a procurement list. 'Specified' items are named on the drawings (Lithonia DSX1 series, RADB/RADEAN bollard, Eagle Mountain StarGazer SG-EHS, MaxCell innerduct, '4260' precast MH). Where drawings are silent, a clearly-marked basis-of-design (BOD) suggestion is offered for pricing only — Div 26/27/28 specifications and DOE/owner standards govern final selection.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacturer identities verified against current product literature: DSX1 = Lithonia D-Series Size 1 area luminaire (Acuity); RADB = Lithonia RADEAN bollard, 8-1/4" dia x 41-1/2" H (schedule's 'Luminis' appears to be an error — RFI-13); SG-3K-EHS-M = Eagle Mountain Flag &amp; Flagpole 'StarGazer' dark-sky flagpole downlight, external-halyard stationary truck, size M for flags to 15'x25'.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty cells on the Materials tab are live formulas linked to the takeoff tabs (green), including conduit-feet roll-ups (duct bank LF x conduits per bank). Changing a takeoff quantity updates the procurement list automatically.</t>
   </si>
 </sst>
 </file>
@@ -1677,7 +2260,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1711,13 +2294,19 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9E2F3"/>
-        <bgColor rgb="FFBDD7EE"/>
+        <bgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -1770,7 +2359,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="44">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1919,6 +2508,18 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1980,7 +2581,7 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
       <rgbColor rgb="FFFF99CC"/>
@@ -3289,11 +3890,11 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="B30" s="26" t="s">
         <v>173</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -3319,7 +3920,7 @@
         <f aca="false">IF(I30="","",G30*I30)</f>
         <v/>
       </c>
-      <c r="K30" s="8" t="s">
+      <c r="K30" s="27" t="s">
         <v>176</v>
       </c>
     </row>
@@ -3357,7 +3958,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
         <v>183</v>
       </c>
@@ -5710,7 +6311,1020 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C52"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>425</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="19" t="s">
+        <v>430</v>
+      </c>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G6" s="37" t="n">
+        <f aca="false">'Site Electrical'!G25</f>
+        <v>9</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G7" s="37" t="n">
+        <f aca="false">'Site Electrical'!G26</f>
+        <v>7</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G8" s="37" t="n">
+        <f aca="false">'Site Electrical'!G27</f>
+        <v>2</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>446</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="F9" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>18</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G10" s="37" t="n">
+        <f aca="false">'Site Electrical'!G30</f>
+        <v>6</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G11" s="37" t="n">
+        <f aca="false">'Site Electrical'!G32</f>
+        <v>3</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="F12" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="G12" s="37" t="n">
+        <f aca="false">'Site Electrical'!G33</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="19" t="s">
+        <v>469</v>
+      </c>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20"/>
+      <c r="I13" s="20"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="F14" s="34" t="s">
+        <v>474</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>479</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="F15" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G15" s="37" t="n">
+        <f aca="false">'Site Electrical'!G20</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
+        <v>483</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>484</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="F16" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G16" s="37" t="n">
+        <f aca="false">'Site Electrical'!G38</f>
+        <v>3</v>
+      </c>
+      <c r="H16" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
+        <v>489</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="F17" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G17" s="37" t="n">
+        <f aca="false">'Site Electrical'!G29</f>
+        <v>18</v>
+      </c>
+      <c r="H17" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="B18" s="20"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="F18" s="20"/>
+      <c r="G18" s="20"/>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20"/>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="21" t="s">
+        <v>496</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>499</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="F19" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="G19" s="37" t="n">
+        <f aca="false">'Telecom OSP'!G6</f>
+        <v>4</v>
+      </c>
+      <c r="H19" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
+        <v>502</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>504</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="F20" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G20" s="37" t="n">
+        <f aca="false">'Telecom OSP'!G7</f>
+        <v>5</v>
+      </c>
+      <c r="H20" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="8" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
+        <v>507</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>509</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="F21" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G21" s="37" t="n">
+        <f aca="false">ROUND('Telecom OSP'!G17*2+'Telecom OSP'!G20*4,0)</f>
+        <v>2499</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="8" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
+        <v>513</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>514</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F22" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G22" s="37" t="n">
+        <f aca="false">ROUND('Telecom OSP'!G23*2,0)</f>
+        <v>598</v>
+      </c>
+      <c r="H22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="8" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
+        <v>518</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>519</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G23" s="37" t="n">
+        <f aca="false">ROUND('Telecom OSP'!G17*2+'Telecom OSP'!G20*4,0)</f>
+        <v>2499</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="8" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
+        <v>524</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>526</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>527</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="G24" s="37" t="n">
+        <f aca="false">ROUND('Telecom OSP'!G23*2,0)</f>
+        <v>598</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="8" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
+        <v>529</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>533</v>
+      </c>
+      <c r="F25" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G25" s="37" t="n">
+        <f aca="false">'Telecom OSP'!G34</f>
+        <v>1600</v>
+      </c>
+      <c r="H25" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="8" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
+        <v>535</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>538</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G26" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I26" s="8" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
+        <v>541</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>543</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="F27" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G27" s="37" t="n">
+        <f aca="false">'Telecom OSP'!G26</f>
+        <v>1407</v>
+      </c>
+      <c r="H27" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="8" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="B28" s="20"/>
+      <c r="C28" s="20"/>
+      <c r="D28" s="20"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
+      <c r="G28" s="20"/>
+      <c r="H28" s="20"/>
+      <c r="I28" s="20"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
+        <v>548</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G29" s="21" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I29" s="8" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G30" s="37" t="n">
+        <f aca="false">Security!G20</f>
+        <v>1</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I30" s="8" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>559</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>563</v>
+      </c>
+      <c r="F31" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G31" s="37" t="n">
+        <f aca="false">Security!G6</f>
+        <v>2</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I31" s="8" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>565</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="F32" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G32" s="37" t="n">
+        <f aca="false">Security!G8+Security!G9</f>
+        <v>2</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="8" t="s">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>571</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>572</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>573</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>574</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>575</v>
+      </c>
+      <c r="F33" s="38" t="s">
+        <v>450</v>
+      </c>
+      <c r="G33" s="37" t="n">
+        <f aca="false">Security!G16+Security!G17</f>
+        <v>2</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="8" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
+        <v>577</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>578</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>579</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="E34" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="F34" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G34" s="37" t="n">
+        <f aca="false">Security!G12</f>
+        <v>3</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>584</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="F35" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G35" s="37" t="n">
+        <f aca="false">Security!G11</f>
+        <v>3</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="F36" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G36" s="37" t="n">
+        <f aca="false">Security!G27</f>
+        <v>1400</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I36" s="8" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>595</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>597</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="F37" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G37" s="37" t="n">
+        <f aca="false">Security!G26</f>
+        <v>1800</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I37" s="8"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>600</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>602</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="F38" s="39" t="s">
+        <v>481</v>
+      </c>
+      <c r="G38" s="37" t="n">
+        <f aca="false">Security!G18</f>
+        <v>1</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I38" s="8" t="s">
+        <v>605</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:C59"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -5719,358 +7333,404 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="37" t="s">
-        <v>423</v>
+      <c r="B2" s="40" t="s">
+        <v>606</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="38" t="s">
-        <v>424</v>
-      </c>
-      <c r="C4" s="39"/>
+      <c r="B4" s="41" t="s">
+        <v>607</v>
+      </c>
+      <c r="C4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="40" t="s">
-        <v>425</v>
+      <c r="B5" s="43" t="s">
+        <v>608</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>426</v>
+        <v>609</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="40" t="s">
-        <v>427</v>
+      <c r="B6" s="43" t="s">
+        <v>610</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>428</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="40" t="s">
-        <v>429</v>
+      <c r="B7" s="43" t="s">
+        <v>612</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>430</v>
+        <v>613</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="38" t="s">
-        <v>431</v>
-      </c>
-      <c r="C9" s="39"/>
+      <c r="B9" s="41" t="s">
+        <v>614</v>
+      </c>
+      <c r="C9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="40" t="s">
+      <c r="B10" s="43" t="s">
         <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>432</v>
+        <v>615</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="40" t="s">
+      <c r="B11" s="43" t="s">
         <v>254</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>433</v>
+        <v>616</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="40" t="s">
+      <c r="B12" s="43" t="s">
         <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>434</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="40" t="s">
+      <c r="B13" s="43" t="s">
         <v>199</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>435</v>
+        <v>618</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="40" t="s">
-        <v>436</v>
+      <c r="B14" s="43" t="s">
+        <v>619</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>437</v>
+        <v>620</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="40" t="s">
-        <v>438</v>
+      <c r="B15" s="43" t="s">
+        <v>621</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>439</v>
+        <v>622</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="38" t="s">
-        <v>440</v>
-      </c>
-      <c r="C17" s="39"/>
+      <c r="B17" s="41" t="s">
+        <v>623</v>
+      </c>
+      <c r="C17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="40" t="s">
-        <v>441</v>
+      <c r="B18" s="43" t="s">
+        <v>624</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>442</v>
+        <v>625</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="40" t="s">
-        <v>443</v>
+      <c r="B19" s="43" t="s">
+        <v>626</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>444</v>
+        <v>627</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="40" t="s">
-        <v>445</v>
+      <c r="B20" s="43" t="s">
+        <v>628</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>446</v>
+        <v>629</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="40" t="s">
-        <v>447</v>
+      <c r="B21" s="43" t="s">
+        <v>630</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>448</v>
+        <v>631</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="40" t="s">
-        <v>449</v>
+      <c r="B22" s="43" t="s">
+        <v>632</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>450</v>
+        <v>633</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="40" t="s">
-        <v>451</v>
+      <c r="B23" s="43" t="s">
+        <v>634</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>452</v>
+        <v>635</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="40" t="s">
-        <v>453</v>
+      <c r="B24" s="43" t="s">
+        <v>636</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>454</v>
+        <v>637</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="40" t="s">
-        <v>455</v>
+      <c r="B25" s="43" t="s">
+        <v>638</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>456</v>
+        <v>639</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="40" t="s">
-        <v>457</v>
+      <c r="B26" s="43" t="s">
+        <v>640</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>458</v>
+        <v>641</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="40" t="s">
-        <v>459</v>
+      <c r="B27" s="43" t="s">
+        <v>642</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>460</v>
+        <v>643</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="40" t="s">
-        <v>461</v>
+      <c r="B28" s="43" t="s">
+        <v>644</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>462</v>
+        <v>645</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="38" t="s">
-        <v>463</v>
-      </c>
-      <c r="C30" s="39"/>
+      <c r="B30" s="41" t="s">
+        <v>646</v>
+      </c>
+      <c r="C30" s="42"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="40" t="s">
-        <v>464</v>
+      <c r="B31" s="43" t="s">
+        <v>647</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>465</v>
+        <v>648</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="40" t="s">
-        <v>466</v>
+      <c r="B32" s="43" t="s">
+        <v>649</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>467</v>
+        <v>650</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="40" t="s">
-        <v>468</v>
+      <c r="B33" s="43" t="s">
+        <v>651</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>469</v>
+        <v>652</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="40" t="s">
-        <v>470</v>
+      <c r="B34" s="43" t="s">
+        <v>653</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>471</v>
+        <v>654</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="40" t="s">
-        <v>472</v>
+      <c r="B35" s="43" t="s">
+        <v>655</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>473</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="40" t="s">
-        <v>474</v>
+      <c r="B36" s="43" t="s">
+        <v>657</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>475</v>
+        <v>658</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="40" t="s">
-        <v>476</v>
+      <c r="B37" s="43" t="s">
+        <v>659</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>477</v>
+        <v>660</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="40" t="s">
-        <v>478</v>
+      <c r="B38" s="43" t="s">
+        <v>661</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>479</v>
+        <v>662</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="38" t="s">
-        <v>480</v>
-      </c>
-      <c r="C40" s="39"/>
+      <c r="B40" s="41" t="s">
+        <v>663</v>
+      </c>
+      <c r="C40" s="42"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="40" t="s">
-        <v>481</v>
+      <c r="B41" s="43" t="s">
+        <v>664</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>482</v>
+        <v>665</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="40" t="s">
-        <v>483</v>
+      <c r="B42" s="43" t="s">
+        <v>666</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>484</v>
+        <v>667</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="40" t="s">
-        <v>485</v>
+      <c r="B43" s="43" t="s">
+        <v>668</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>486</v>
+        <v>669</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="40" t="s">
-        <v>487</v>
+      <c r="B44" s="43" t="s">
+        <v>670</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>488</v>
+        <v>671</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="40" t="s">
-        <v>489</v>
+      <c r="B45" s="43" t="s">
+        <v>672</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>490</v>
+        <v>673</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="40" t="s">
-        <v>491</v>
+      <c r="B46" s="43" t="s">
+        <v>674</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>492</v>
+        <v>675</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="40" t="s">
-        <v>493</v>
+      <c r="B47" s="43" t="s">
+        <v>676</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>494</v>
+        <v>677</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="40" t="s">
-        <v>495</v>
+      <c r="B48" s="43" t="s">
+        <v>678</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>496</v>
+        <v>679</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="40" t="s">
-        <v>497</v>
+      <c r="B49" s="43" t="s">
+        <v>680</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>498</v>
+        <v>681</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="40" t="s">
-        <v>499</v>
+      <c r="B50" s="43" t="s">
+        <v>682</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>500</v>
+        <v>683</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="40" t="s">
-        <v>501</v>
+      <c r="B51" s="43" t="s">
+        <v>684</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>502</v>
+        <v>685</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="40" t="s">
-        <v>503</v>
+      <c r="B52" s="43" t="s">
+        <v>686</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>504</v>
+        <v>687</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B53" s="43" t="s">
+        <v>688</v>
+      </c>
+      <c r="C53" s="8" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B54" s="43" t="s">
+        <v>690</v>
+      </c>
+      <c r="C54" s="8" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="41" t="s">
+        <v>692</v>
+      </c>
+      <c r="C56" s="42"/>
+    </row>
+    <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B57" s="43" t="s">
+        <v>693</v>
+      </c>
+      <c r="C57" s="8" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="43" t="s">
+        <v>695</v>
+      </c>
+      <c r="C58" s="8" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B59" s="43" t="s">
+        <v>697</v>
+      </c>
+      <c r="C59" s="8" t="s">
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
+++ b/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1055" uniqueCount="699">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="771">
   <si>
     <t xml:space="preserve">DETAILED QUANTITY TAKEOFF — EXTERIOR ELECTRICAL &amp; COMMUNICATIONS</t>
   </si>
@@ -459,6 +459,27 @@
     <t xml:space="preserve">Refer to one-line for conduit count. Field coordinate exact routing &amp; stub-up locations prior to rough-in (KN 6).</t>
   </si>
   <si>
+    <t xml:space="preserve">B6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid-tight flex (LFMC) whips, connectors &amp; termination fittings at generator, ATS &amp; service equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sizes to match B4/B5 conduits (TBD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LFMC + steel LT connectors; myers hubs/bonding bushings at enclosures</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES101 KN 5/6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Equipment connection fittings not shown at 65% — carried as LS until one-line issues conduit schedule.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Subtotal B</t>
   </si>
   <si>
@@ -624,9 +645,6 @@
     <t xml:space="preserve">ES101</t>
   </si>
   <si>
-    <t xml:space="preserve">Allowance</t>
-  </si>
-  <si>
     <t xml:space="preserve">No homeruns/circuit routing drawn at 65%; photometric plan to be added per QC. Allowance = pole-to-pole loop + homeruns; revise at 95%.</t>
   </si>
   <si>
@@ -645,6 +663,24 @@
     <t xml:space="preserve">Carry site interface/controls wiring allowance.</t>
   </si>
   <si>
+    <t xml:space="preserve">C12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long-radius 90° sweeps + bell ends at pole &amp; bollard base conduit stub-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1" (to match C10 circuit conduit)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC LR sweeps, min radius per NEC; bell end each stub</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2/ES601, 3/ES601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Details say 'conduit, quantity as required' — carried 2 sweeps/pole base (36) + 1/bollard (6). Firm up with circuiting at 95%.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Subtotal C</t>
   </si>
   <si>
@@ -684,6 +720,39 @@
     <t xml:space="preserve">Conductors/size per KN 7; conduit material &amp; source panel not indicated at 65%. Allowance for 3 runs.</t>
   </si>
   <si>
+    <t xml:space="preserve">D3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sweeps, LBs &amp; terminations at gate power JBs, DPS boxes &amp; pedestal risers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4" – 1"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC/steel LR sweeps, LB conduit bodies, TA adapters, bushings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ES101 KN 7; A7,A1/TSY101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 per JB (6) + 1 per DPS box (3) + riser sweep per pedestal/intercom location (3) + spares (2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LFMC whip + connectors, JB to each gate operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4" x 6' (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Liquid-tight flexible metal conduit w/ steel LT connectors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final connection to operator per operator mfr; verify w/ shop drawings.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Subtotal D</t>
   </si>
   <si>
@@ -795,9 +864,6 @@
     <t xml:space="preserve">Plan dim 123'-1".</t>
   </si>
   <si>
-    <t xml:space="preserve">B6</t>
-  </si>
-  <si>
     <t xml:space="preserve">DB1 duct bank — MH1-4 to HH1-3 (future Bldg B connection)</t>
   </si>
   <si>
@@ -957,6 +1023,75 @@
     <t xml:space="preserve">TSN gen. notes</t>
   </si>
   <si>
+    <t xml:space="preserve">Duct terminators / bell-end wall entries at MH &amp; HH structures — 4" conduits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator/end bell at structure knockout, grouted &amp; bonded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1/TSN400; TSN100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counted from route topology: MH1-1(4), MH1-2(10), MH1-3(10), MH1-4(4), HH1-2(2), HH1-3(2), HH1-4(2). NOTE — NO 90° elbows in duct runs and NO underground tees: turns/branches occur INSIDE structures via wall knockouts (H1/TSN400 note 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct terminators / bell-end wall entries at HH structures — 2" conduits</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator/end bell at structure knockout</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSN100 (DB3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-3(2), HH1-5(4 — in &amp; out), HH1-6(2).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long-radius 90° riser sweeps — Bldg A entry &amp; ISP pedestal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4"; radius ≥10x dia (per TSY GN 17 practice)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiberglass or RGS LR elbows recommended at cable pulls (PVC burns through)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSN100/TSN300</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A DB2 riser (4) + ISP pedestal riser (2). Gate pedestal risers carried on Site Electrical D3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansion/deflection fittings where conduits enter Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansion-deflection couplings (OZ Gedney AX/DX type or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSN GN 24 (analog)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom GN requires sliding/offsetting fittings at expansion crossings — assumed at the 4 DB2 building-entry conduits; verify structural joint locations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct plugs &amp; MaxCell cell plugs — vacant conduits/cells at every termination</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4" &amp; 2" duplex/simplex plugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackmoon/Tyco duct plugs + MaxCell cell plugs (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Most of the 3-cell fabric cells are vacant at turnover (fiber occupies 1 cell on select routes) — seal all.</t>
+  </si>
+  <si>
     <t xml:space="preserve">D. OSP CABLING (TSN300 site one-line)</t>
   </si>
   <si>
@@ -990,9 +1125,6 @@
     <t xml:space="preserve">Contractor per responsibility matrix (Div 27).</t>
   </si>
   <si>
-    <t xml:space="preserve">D3</t>
-  </si>
-  <si>
     <t xml:space="preserve">OSP copper backbone cabling — TBD (QC: 'Where is the OSP copper?')</t>
   </si>
   <si>
@@ -1008,9 +1140,6 @@
     <t xml:space="preserve">Matrix lists copper backbone as Contractor scope but none shown on one-line — carry allowance / RFI.</t>
   </si>
   <si>
-    <t xml:space="preserve">D4</t>
-  </si>
-  <si>
     <t xml:space="preserve">ISP fiber &amp; ISP telecom pedestal — BY ISP</t>
   </si>
   <si>
@@ -1368,7 +1497,7 @@
     <t xml:space="preserve">Light pole, round straight steel or aluminum</t>
   </si>
   <si>
-    <t xml:space="preserve">35'-0 nominal; drilled for D-Series arm</t>
+    <t xml:space="preserve">35'-0" nominal; drilled for D-Series arm</t>
   </si>
   <si>
     <t xml:space="preserve">Valmont / RSA / Lithonia SSS (or equal)</t>
@@ -1512,6 +1641,39 @@
     <t xml:space="preserve">Rod size not on drawings — confirm Div 26 spec.</t>
   </si>
   <si>
+    <t xml:space="preserve">P5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LFMC whips &amp; LT connectors — gate operators, generator/ATS equipment connections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4" (gates); service sizes TBD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Southwire / AFC (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LFMC + steel liquid-tight connectors, bonding bushings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate operator whips counted (D4); generator/ATS whips in LS item B6.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduit sweeps, LBs, bell ends — site power &amp; lighting stub-ups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cantex / Killark (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC/steel LR sweeps, LB conduit bodies, bell ends</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pole/bollard base sweeps (C12) + gate JB/DPS/pedestal fittings (D3). No UG tees — splices at boxes/handholes only.</t>
+  </si>
+  <si>
     <t xml:space="preserve">TELECOM OSP</t>
   </si>
   <si>
@@ -1666,6 +1828,60 @@
   </si>
   <si>
     <t xml:space="preserve">Tape LF = trench LF (live).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct terminators / bell ends at MH &amp; HH wall entries</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(34) 4" + (8) 2"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underground Devices / Cantex (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terminator/end bell at structure knockouts, grouted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counted from route topology. NO 90° elbows in duct runs &amp; NO UG tees — all turns/branches inside structures (H1/TSN400 note 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long-radius 90° riser sweeps + expansion fittings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4"; LR ≥10x dia; OZ AX/DX at bldg entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Champion Fiberglass / OZ-Gedney (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiberglass or RGS LR elbows at pulls; expansion-deflection at Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A riser (4) + ISP pedestal (2) + 4 expansion fittings.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct plugs &amp; MaxCell cell plugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4"/2" simplex-duplex + fabric cell plugs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jackmoon (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seal every vacant conduit &amp; innerduct cell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Takeoff line Telecom C11.</t>
   </si>
   <si>
     <t xml:space="preserve">SECURITY (Div 28 — models per spec; BOD offered where drawings silent)</t>
@@ -2845,7 +3061,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">'Site Electrical'!J42</f>
+        <f aca="false">'Site Electrical'!J46</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -2860,7 +3076,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">'Telecom OSP'!J40</f>
+        <f aca="false">'Telecom OSP'!J45</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -3068,7 +3284,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -3687,94 +3903,94 @@
         <v>143</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="28"/>
-      <c r="B23" s="29" t="s">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="30" t="n">
-        <f aca="false">SUM(J18:J22)</f>
+      <c r="B23" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="E23" s="21" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I23" s="23"/>
+      <c r="J23" s="24" t="str">
+        <f aca="false">IF(I23="","",G23*I23)</f>
+        <v/>
+      </c>
+      <c r="K23" s="27" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="28"/>
+      <c r="B24" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="C24" s="28"/>
+      <c r="D24" s="28"/>
+      <c r="E24" s="28"/>
+      <c r="F24" s="28"/>
+      <c r="G24" s="28"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="30" t="n">
+        <f aca="false">SUM(J18:J23)</f>
         <v>0</v>
       </c>
-      <c r="K23" s="28"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>145</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
-        <v>146</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>150</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="25" t="n">
-        <v>9</v>
-      </c>
-      <c r="H25" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="23"/>
-      <c r="J25" s="24" t="str">
-        <f aca="false">IF(I25="","",G25*I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="8" t="s">
-        <v>151</v>
-      </c>
+      <c r="K24" s="28"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
+        <v>152</v>
+      </c>
+      <c r="B25" s="20"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
+      <c r="G25" s="20"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="26" t="s">
         <v>153</v>
       </c>
+      <c r="B26" s="7" t="s">
+        <v>154</v>
+      </c>
       <c r="C26" s="7" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F26" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="25" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>69</v>
@@ -3784,31 +4000,31 @@
         <f aca="false">IF(I26="","",G26*I26)</f>
         <v/>
       </c>
-      <c r="K26" s="27" t="s">
-        <v>155</v>
+      <c r="K26" s="8" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>156</v>
-      </c>
-      <c r="B27" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="E27" s="21" t="s">
         <v>157</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>150</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>69</v>
@@ -3818,31 +4034,31 @@
         <f aca="false">IF(I27="","",G27*I27)</f>
         <v/>
       </c>
-      <c r="K27" s="8" t="s">
-        <v>159</v>
+      <c r="K27" s="27" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G28" s="25" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="H28" s="21" t="s">
         <v>69</v>
@@ -3853,24 +4069,24 @@
         <v/>
       </c>
       <c r="K28" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>166</v>
-      </c>
-      <c r="B29" s="26" t="s">
         <v>167</v>
       </c>
+      <c r="B29" s="7" t="s">
+        <v>168</v>
+      </c>
       <c r="C29" s="7" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>76</v>
@@ -3886,31 +4102,31 @@
         <f aca="false">IF(I29="","",G29*I29)</f>
         <v/>
       </c>
-      <c r="K29" s="27" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K29" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>150</v>
+        <v>177</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G30" s="25" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>69</v>
@@ -3921,24 +4137,24 @@
         <v/>
       </c>
       <c r="K30" s="27" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>177</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>178</v>
+        <v>179</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>180</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>181</v>
+        <v>157</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>76</v>
@@ -3954,31 +4170,31 @@
         <f aca="false">IF(I31="","",G31*I31)</f>
         <v/>
       </c>
-      <c r="K31" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K31" s="27" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>183</v>
-      </c>
-      <c r="B32" s="26" t="s">
         <v>184</v>
       </c>
+      <c r="B32" s="7" t="s">
+        <v>185</v>
+      </c>
       <c r="C32" s="7" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>150</v>
+        <v>188</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G32" s="25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H32" s="21" t="s">
         <v>69</v>
@@ -3988,31 +4204,31 @@
         <f aca="false">IF(I32="","",G32*I32)</f>
         <v/>
       </c>
-      <c r="K32" s="27" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="K32" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>188</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>189</v>
+        <v>190</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>191</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>76</v>
       </c>
       <c r="G33" s="25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H33" s="21" t="s">
         <v>69</v>
@@ -4022,41 +4238,41 @@
         <f aca="false">IF(I33="","",G33*I33)</f>
         <v/>
       </c>
-      <c r="K33" s="8" t="s">
-        <v>193</v>
+      <c r="K33" s="27" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>194</v>
-      </c>
-      <c r="B34" s="26" t="s">
         <v>195</v>
       </c>
+      <c r="B34" s="7" t="s">
+        <v>196</v>
+      </c>
       <c r="C34" s="7" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>2400</v>
+        <v>76</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>1</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I34" s="23"/>
       <c r="J34" s="24" t="str">
         <f aca="false">IF(I34="","",G34*I34)</f>
         <v/>
       </c>
-      <c r="K34" s="27" t="s">
+      <c r="K34" s="8" t="s">
         <v>200</v>
       </c>
     </row>
@@ -4068,22 +4284,22 @@
         <v>202</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>65</v>
+        <v>203</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>1</v>
+        <v>2400</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I35" s="23"/>
       <c r="J35" s="24" t="str">
@@ -4091,145 +4307,281 @@
         <v/>
       </c>
       <c r="K35" s="27" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="28"/>
-      <c r="B36" s="29" t="s">
         <v>206</v>
       </c>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="30" t="n">
-        <f aca="false">SUM(J25:J35)</f>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>208</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G36" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H36" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I36" s="23"/>
+      <c r="J36" s="24" t="str">
+        <f aca="false">IF(I36="","",G36*I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G37" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24" t="str">
+        <f aca="false">IF(I37="","",G37*I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="28"/>
+      <c r="B38" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C38" s="28"/>
+      <c r="D38" s="28"/>
+      <c r="E38" s="28"/>
+      <c r="F38" s="28"/>
+      <c r="G38" s="28"/>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28"/>
+      <c r="J38" s="30" t="n">
+        <f aca="false">SUM(J26:J37)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="28"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>207</v>
-      </c>
-      <c r="B37" s="20"/>
-      <c r="C37" s="20"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
-      <c r="F37" s="20"/>
-      <c r="G37" s="20"/>
-      <c r="H37" s="20"/>
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-    </row>
-    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>209</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="E38" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="F38" s="21" t="s">
+      <c r="K38" s="28"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
+        <v>219</v>
+      </c>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="20"/>
+      <c r="E39" s="20"/>
+      <c r="F39" s="20"/>
+      <c r="G39" s="20"/>
+      <c r="H39" s="20"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+    </row>
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>221</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>223</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F40" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="G38" s="25" t="n">
+      <c r="G40" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H40" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I38" s="23"/>
-      <c r="J38" s="24" t="str">
-        <f aca="false">IF(I38="","",G38*I38)</f>
+      <c r="I40" s="23"/>
+      <c r="J40" s="24" t="str">
+        <f aca="false">IF(I40="","",G40*I40)</f>
         <v/>
       </c>
-      <c r="K38" s="27" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>215</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>216</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>217</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>212</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>199</v>
-      </c>
-      <c r="G39" s="22" t="n">
+      <c r="K40" s="27" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G41" s="22" t="n">
         <v>700</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H41" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I39" s="23"/>
-      <c r="J39" s="24" t="str">
-        <f aca="false">IF(I39="","",G39*I39)</f>
+      <c r="I41" s="23"/>
+      <c r="J41" s="24" t="str">
+        <f aca="false">IF(I41="","",G41*I41)</f>
         <v/>
       </c>
-      <c r="K39" s="27" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="28"/>
-      <c r="B40" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="30" t="n">
-        <f aca="false">SUM(J38:J39)</f>
+      <c r="K41" s="27" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>232</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>235</v>
+      </c>
+      <c r="F42" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G42" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I42" s="23"/>
+      <c r="J42" s="24" t="str">
+        <f aca="false">IF(I42="","",G42*I42)</f>
+        <v/>
+      </c>
+      <c r="K42" s="27" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>238</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>240</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>224</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G43" s="25" t="n">
+        <v>3</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I43" s="23"/>
+      <c r="J43" s="24" t="str">
+        <f aca="false">IF(I43="","",G43*I43)</f>
+        <v/>
+      </c>
+      <c r="K43" s="8" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="28"/>
+      <c r="B44" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28"/>
+      <c r="H44" s="28"/>
+      <c r="I44" s="28"/>
+      <c r="J44" s="30" t="n">
+        <f aca="false">SUM(J40:J43)</f>
         <v>0</v>
       </c>
-      <c r="K40" s="28"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11"/>
-      <c r="B42" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="12" t="n">
-        <f aca="false">J16+J23+J36+J40</f>
+      <c r="K44" s="28"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="11"/>
+      <c r="B46" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="11"/>
+      <c r="G46" s="11"/>
+      <c r="H46" s="11"/>
+      <c r="I46" s="11"/>
+      <c r="J46" s="12" t="n">
+        <f aca="false">J16+J24+J38+J44</f>
         <v>0</v>
       </c>
-      <c r="K42" s="11"/>
+      <c r="K46" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -4247,7 +4599,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -4265,7 +4617,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4310,7 +4662,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -4328,16 +4680,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>76</v>
@@ -4354,7 +4706,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="s">
-        <v>227</v>
+        <v>250</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4362,16 +4714,16 @@
         <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>228</v>
+        <v>251</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>229</v>
+        <v>252</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>230</v>
+        <v>253</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>231</v>
+        <v>254</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>76</v>
@@ -4388,7 +4740,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="s">
-        <v>232</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4396,16 +4748,16 @@
         <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>233</v>
+        <v>256</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>234</v>
+        <v>257</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>235</v>
+        <v>258</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>236</v>
+        <v>259</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>76</v>
@@ -4422,7 +4774,7 @@
         <v/>
       </c>
       <c r="K8" s="27" t="s">
-        <v>237</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4445,7 +4797,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>238</v>
+        <v>261</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -4463,16 +4815,16 @@
         <v>117</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>239</v>
+        <v>262</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>242</v>
+        <v>265</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>60</v>
@@ -4489,7 +4841,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="s">
-        <v>243</v>
+        <v>266</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4497,16 +4849,16 @@
         <v>123</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>244</v>
+        <v>267</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>60</v>
@@ -4523,7 +4875,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4531,16 +4883,16 @@
         <v>128</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>247</v>
+        <v>270</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>60</v>
@@ -4557,7 +4909,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="s">
-        <v>249</v>
+        <v>272</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4565,16 +4917,16 @@
         <v>133</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>60</v>
@@ -4591,7 +4943,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="s">
-        <v>252</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4599,19 +4951,19 @@
         <v>139</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>253</v>
+        <v>276</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G15" s="31" t="n">
         <v>123.1</v>
@@ -4625,27 +4977,27 @@
         <v/>
       </c>
       <c r="K15" s="8" t="s">
-        <v>255</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>240</v>
+        <v>263</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>241</v>
+        <v>264</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>258</v>
+        <v>280</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G16" s="31" t="n">
         <v>13.7</v>
@@ -4659,15 +5011,15 @@
         <v/>
       </c>
       <c r="K16" s="8" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="32" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>261</v>
+        <v>283</v>
       </c>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
@@ -4686,19 +5038,19 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>263</v>
+        <v>285</v>
       </c>
       <c r="C18" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D18" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="D18" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="E18" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>60</v>
@@ -4715,27 +5067,27 @@
         <v/>
       </c>
       <c r="K18" s="8" t="s">
-        <v>246</v>
+        <v>269</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>265</v>
+        <v>287</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>266</v>
+        <v>288</v>
       </c>
       <c r="C19" s="7" t="s">
+        <v>286</v>
+      </c>
+      <c r="D19" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="D19" s="7" t="s">
-        <v>241</v>
-      </c>
       <c r="E19" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G19" s="31" t="n">
         <v>21.4</v>
@@ -4749,15 +5101,15 @@
         <v/>
       </c>
       <c r="K19" s="8" t="s">
-        <v>267</v>
+        <v>289</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="32" t="s">
-        <v>268</v>
+        <v>290</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>269</v>
+        <v>291</v>
       </c>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
@@ -4776,22 +5128,22 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>270</v>
+        <v>292</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>271</v>
+        <v>293</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G21" s="31" t="n">
         <v>101.5</v>
@@ -4805,27 +5157,27 @@
         <v/>
       </c>
       <c r="K21" s="27" t="s">
-        <v>274</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>276</v>
+        <v>298</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>245</v>
+        <v>268</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="G22" s="31" t="n">
         <v>197.3</v>
@@ -4839,15 +5191,15 @@
         <v/>
       </c>
       <c r="K22" s="27" t="s">
-        <v>277</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="32" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>279</v>
+        <v>301</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
@@ -4867,7 +5219,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
@@ -4884,7 +5236,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -4899,22 +5251,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>283</v>
+        <v>305</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">SUM(G11:G16)+SUM(G18:G19)+SUM(G21:G22)</f>
@@ -4929,34 +5281,34 @@
         <v/>
       </c>
       <c r="K26" s="8" t="s">
-        <v>287</v>
+        <v>309</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>291</v>
+        <v>313</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G27" s="31" t="n">
         <f aca="false">ROUND(SUM(G11:G16)*2.56/27,1)</f>
         <v>91.7</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I27" s="23"/>
       <c r="J27" s="35" t="str">
@@ -4964,34 +5316,34 @@
         <v/>
       </c>
       <c r="K27" s="8" t="s">
-        <v>293</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>294</v>
+        <v>316</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>295</v>
+        <v>317</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>290</v>
+        <v>312</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>296</v>
+        <v>318</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G28" s="31" t="n">
         <f aca="false">ROUND(SUM(G18:G19)*4.34/27,1)</f>
         <v>22.7</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I28" s="23"/>
       <c r="J28" s="35" t="str">
@@ -4999,34 +5351,34 @@
         <v/>
       </c>
       <c r="K28" s="8" t="s">
-        <v>297</v>
+        <v>319</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>298</v>
+        <v>320</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>299</v>
+        <v>321</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="G29" s="31" t="n">
         <f aca="false">ROUND(SUM(G21:G22)*0.83/27,1)</f>
         <v>9.2</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>292</v>
+        <v>314</v>
       </c>
       <c r="I29" s="23"/>
       <c r="J29" s="35" t="str">
@@ -5034,27 +5386,27 @@
         <v/>
       </c>
       <c r="K29" s="27" t="s">
-        <v>302</v>
+        <v>324</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>303</v>
+        <v>325</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>304</v>
+        <v>326</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>305</v>
+        <v>327</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>306</v>
+        <v>328</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G30" s="22" t="n">
         <v>1</v>
@@ -5071,22 +5423,22 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>307</v>
+        <v>329</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>308</v>
+        <v>330</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>309</v>
+        <v>331</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G31" s="22" t="n">
         <v>1</v>
@@ -5101,125 +5453,160 @@
       </c>
       <c r="K31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="28"/>
-      <c r="B32" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="30" t="n">
-        <f aca="false">SUM(J26:J31)</f>
-        <v>0</v>
-      </c>
-      <c r="K32" s="28"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="B33" s="20"/>
-      <c r="C33" s="20"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
-      <c r="F33" s="20"/>
-      <c r="G33" s="20"/>
-      <c r="H33" s="20"/>
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>332</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>333</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>335</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G32" s="25" t="n">
+        <v>34</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24" t="str">
+        <f aca="false">IF(I32="","",G32*I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="8" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>338</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="E33" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="F33" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G33" s="25" t="n">
+        <v>8</v>
+      </c>
+      <c r="H33" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I33" s="23"/>
+      <c r="J33" s="24" t="str">
+        <f aca="false">IF(I33="","",G33*I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="8" t="s">
+        <v>341</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>208</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>311</v>
+        <v>195</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>342</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>312</v>
+        <v>343</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>314</v>
+        <v>345</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G34" s="22" t="n">
-        <v>1600</v>
+        <v>76</v>
+      </c>
+      <c r="G34" s="25" t="n">
+        <v>6</v>
       </c>
       <c r="H34" s="21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I34" s="23"/>
       <c r="J34" s="24" t="str">
         <f aca="false">IF(I34="","",G34*I34)</f>
         <v/>
       </c>
-      <c r="K34" s="27" t="s">
-        <v>315</v>
+      <c r="K34" s="8" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>316</v>
+        <v>201</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>347</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>318</v>
+        <v>348</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H35" s="21" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="I35" s="23"/>
       <c r="J35" s="24" t="str">
         <f aca="false">IF(I35="","",G35*I35)</f>
         <v/>
       </c>
-      <c r="K35" s="8" t="s">
-        <v>320</v>
+      <c r="K35" s="27" t="s">
+        <v>350</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>321</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>322</v>
+        <v>207</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>351</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G36" s="22" t="n">
         <v>1</v>
@@ -5232,77 +5619,212 @@
         <f aca="false">IF(I36="","",G36*I36)</f>
         <v/>
       </c>
-      <c r="K36" s="27" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>329</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>330</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>319</v>
-      </c>
-      <c r="F37" s="21" t="s">
+      <c r="K36" s="8" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="28"/>
+      <c r="B37" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="28"/>
+      <c r="F37" s="28"/>
+      <c r="G37" s="28"/>
+      <c r="H37" s="28"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="30" t="n">
+        <f aca="false">SUM(J26:J36)</f>
+        <v>0</v>
+      </c>
+      <c r="K37" s="28"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="s">
+        <v>355</v>
+      </c>
+      <c r="B38" s="20"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
+      <c r="F38" s="20"/>
+      <c r="G38" s="20"/>
+      <c r="H38" s="20"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>356</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>357</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>358</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F39" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="22" t="n">
+        <v>1600</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I39" s="23"/>
+      <c r="J39" s="24" t="str">
+        <f aca="false">IF(I39="","",G39*I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="27" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F40" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G40" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I40" s="23"/>
+      <c r="J40" s="24" t="str">
+        <f aca="false">IF(I40="","",G40*I40)</f>
+        <v/>
+      </c>
+      <c r="K40" s="8" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>367</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>368</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>369</v>
+      </c>
+      <c r="F41" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G41" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I41" s="23"/>
+      <c r="J41" s="24" t="str">
+        <f aca="false">IF(I41="","",G41*I41)</f>
+        <v/>
+      </c>
+      <c r="K41" s="27" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>371</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>372</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>373</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="F42" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G37" s="25" t="n">
+      <c r="G42" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H42" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="I37" s="23"/>
-      <c r="J37" s="24" t="str">
-        <f aca="false">IF(I37="","",G37*I37)</f>
+      <c r="I42" s="23"/>
+      <c r="J42" s="24" t="str">
+        <f aca="false">IF(I42="","",G42*I42)</f>
         <v/>
       </c>
-      <c r="K37" s="8"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="28"/>
-      <c r="B38" s="29" t="s">
-        <v>219</v>
-      </c>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="28"/>
-      <c r="I38" s="28"/>
-      <c r="J38" s="30" t="n">
-        <f aca="false">SUM(J34:J37)</f>
+      <c r="K42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="28"/>
+      <c r="B43" s="29" t="s">
+        <v>242</v>
+      </c>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
+      <c r="F43" s="28"/>
+      <c r="G43" s="28"/>
+      <c r="H43" s="28"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="30" t="n">
+        <f aca="false">SUM(J39:J42)</f>
         <v>0</v>
       </c>
-      <c r="K38" s="28"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="11"/>
-      <c r="B40" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="11"/>
-      <c r="G40" s="11"/>
-      <c r="H40" s="11"/>
-      <c r="I40" s="11"/>
-      <c r="J40" s="12" t="n">
-        <f aca="false">J9+J24+J32+J38</f>
+      <c r="K43" s="28"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11"/>
+      <c r="B45" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="12" t="n">
+        <f aca="false">J9+J24+J37+J43</f>
         <v>0</v>
       </c>
-      <c r="K40" s="11"/>
+      <c r="K45" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5338,7 +5860,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>332</v>
+        <v>375</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5383,7 +5905,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>333</v>
+        <v>376</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -5401,16 +5923,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>334</v>
+        <v>377</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>335</v>
+        <v>378</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>336</v>
+        <v>379</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>337</v>
+        <v>380</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>76</v>
@@ -5427,7 +5949,7 @@
         <v/>
       </c>
       <c r="K6" s="27" t="s">
-        <v>338</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5435,16 +5957,16 @@
         <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>339</v>
+        <v>382</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>340</v>
+        <v>383</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>341</v>
+        <v>384</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>76</v>
@@ -5467,16 +5989,16 @@
         <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>343</v>
+        <v>386</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>344</v>
+        <v>387</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>345</v>
+        <v>388</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>76</v>
@@ -5493,7 +6015,7 @@
         <v/>
       </c>
       <c r="K8" s="27" t="s">
-        <v>346</v>
+        <v>389</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5501,16 +6023,16 @@
         <v>79</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>347</v>
+        <v>390</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>348</v>
+        <v>391</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>349</v>
+        <v>392</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>76</v>
@@ -5527,7 +6049,7 @@
         <v/>
       </c>
       <c r="K9" s="27" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5535,16 +6057,16 @@
         <v>85</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>352</v>
+        <v>395</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>353</v>
+        <v>396</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>76</v>
@@ -5561,7 +6083,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="s">
-        <v>355</v>
+        <v>398</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5569,16 +6091,16 @@
         <v>91</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>357</v>
+        <v>400</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>358</v>
+        <v>401</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>76</v>
@@ -5601,16 +6123,16 @@
         <v>96</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>359</v>
+        <v>402</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>360</v>
+        <v>403</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>361</v>
+        <v>404</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>76</v>
@@ -5627,7 +6149,7 @@
         <v/>
       </c>
       <c r="K12" s="27" t="s">
-        <v>362</v>
+        <v>405</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5635,16 +6157,16 @@
         <v>101</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>363</v>
+        <v>406</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>364</v>
+        <v>407</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>365</v>
+        <v>408</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>366</v>
+        <v>409</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>76</v>
@@ -5661,7 +6183,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="s">
-        <v>367</v>
+        <v>410</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5684,7 +6206,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>368</v>
+        <v>411</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -5702,16 +6224,16 @@
         <v>117</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>369</v>
+        <v>412</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>370</v>
+        <v>413</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>371</v>
+        <v>414</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>372</v>
+        <v>415</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>76</v>
@@ -5734,16 +6256,16 @@
         <v>123</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>373</v>
+        <v>416</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>374</v>
+        <v>417</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>375</v>
+        <v>418</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>76</v>
@@ -5760,7 +6282,7 @@
         <v/>
       </c>
       <c r="K17" s="27" t="s">
-        <v>377</v>
+        <v>420</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5768,16 +6290,16 @@
         <v>128</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>378</v>
+        <v>421</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>379</v>
+        <v>422</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>380</v>
+        <v>423</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>76</v>
@@ -5800,16 +6322,16 @@
         <v>133</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>381</v>
+        <v>424</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>382</v>
+        <v>425</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>383</v>
+        <v>426</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>384</v>
+        <v>427</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>76</v>
@@ -5832,16 +6354,16 @@
         <v>139</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>385</v>
+        <v>428</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>386</v>
+        <v>429</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>387</v>
+        <v>430</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>76</v>
@@ -5858,24 +6380,24 @@
         <v/>
       </c>
       <c r="K20" s="8" t="s">
-        <v>388</v>
+        <v>431</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>256</v>
+        <v>144</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>389</v>
+        <v>432</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>390</v>
+        <v>433</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>391</v>
+        <v>434</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>392</v>
+        <v>435</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>68</v>
@@ -5895,10 +6417,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>260</v>
+        <v>282</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>393</v>
+        <v>436</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>65</v>
@@ -5907,10 +6429,10 @@
         <v>65</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>0</v>
@@ -5921,27 +6443,27 @@
       <c r="I22" s="36"/>
       <c r="J22" s="35"/>
       <c r="K22" s="27" t="s">
-        <v>396</v>
+        <v>439</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>398</v>
+        <v>441</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F23" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G23" s="22" t="n">
         <v>1</v>
@@ -5959,7 +6481,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
@@ -5976,7 +6498,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>399</v>
+        <v>442</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -5991,22 +6513,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>400</v>
+        <v>443</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>401</v>
+        <v>444</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>402</v>
+        <v>445</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G26" s="22" t="n">
         <v>1800</v>
@@ -6020,27 +6542,27 @@
         <v/>
       </c>
       <c r="K26" s="27" t="s">
-        <v>404</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>405</v>
+        <v>448</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>406</v>
+        <v>449</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>407</v>
+        <v>450</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>408</v>
+        <v>451</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G27" s="22" t="n">
         <v>1400</v>
@@ -6054,15 +6576,15 @@
         <v/>
       </c>
       <c r="K27" s="27" t="s">
-        <v>409</v>
+        <v>452</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>410</v>
+        <v>453</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>65</v>
@@ -6071,7 +6593,7 @@
         <v>65</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>376</v>
+        <v>419</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>68</v>
@@ -6085,27 +6607,27 @@
       <c r="I28" s="36"/>
       <c r="J28" s="35"/>
       <c r="K28" s="8" t="s">
-        <v>411</v>
+        <v>454</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>412</v>
+        <v>455</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>413</v>
+        <v>456</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>414</v>
+        <v>457</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="G29" s="22" t="n">
         <v>1</v>
@@ -6123,7 +6645,7 @@
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="28"/>
       <c r="B30" s="29" t="s">
-        <v>206</v>
+        <v>218</v>
       </c>
       <c r="C30" s="28"/>
       <c r="D30" s="28"/>
@@ -6140,7 +6662,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>415</v>
+        <v>458</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20"/>
@@ -6155,10 +6677,10 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>416</v>
+        <v>459</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>65</v>
@@ -6167,10 +6689,10 @@
         <v>65</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F32" s="21" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="G32" s="25" t="n">
         <v>0</v>
@@ -6181,15 +6703,15 @@
       <c r="I32" s="36"/>
       <c r="J32" s="35"/>
       <c r="K32" s="27" t="s">
-        <v>417</v>
+        <v>460</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="21" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B33" s="26" t="s">
-        <v>418</v>
+        <v>461</v>
       </c>
       <c r="C33" s="7" t="s">
         <v>65</v>
@@ -6198,10 +6720,10 @@
         <v>65</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F33" s="21" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="G33" s="25" t="n">
         <v>0</v>
@@ -6212,15 +6734,15 @@
       <c r="I33" s="36"/>
       <c r="J33" s="35"/>
       <c r="K33" s="27" t="s">
-        <v>417</v>
+        <v>460</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>321</v>
+        <v>231</v>
       </c>
       <c r="B34" s="26" t="s">
-        <v>419</v>
+        <v>462</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>65</v>
@@ -6229,10 +6751,10 @@
         <v>65</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F34" s="21" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="G34" s="25" t="n">
         <v>0</v>
@@ -6243,15 +6765,15 @@
       <c r="I34" s="36"/>
       <c r="J34" s="35"/>
       <c r="K34" s="27" t="s">
-        <v>420</v>
+        <v>463</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>327</v>
+        <v>237</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>421</v>
+        <v>464</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>65</v>
@@ -6260,10 +6782,10 @@
         <v>65</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>394</v>
+        <v>437</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>395</v>
+        <v>438</v>
       </c>
       <c r="G35" s="25" t="n">
         <v>0</v>
@@ -6274,13 +6796,13 @@
       <c r="I35" s="36"/>
       <c r="J35" s="35"/>
       <c r="K35" s="27" t="s">
-        <v>417</v>
+        <v>460</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11"/>
       <c r="B37" s="10" t="s">
-        <v>422</v>
+        <v>465</v>
       </c>
       <c r="C37" s="11"/>
       <c r="D37" s="11"/>
@@ -6311,7 +6833,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6327,32 +6849,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>423</v>
+        <v>466</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>424</v>
+        <v>467</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>425</v>
+        <v>468</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>426</v>
+        <v>469</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>427</v>
+        <v>470</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>428</v>
+        <v>471</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>429</v>
+        <v>472</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>50</v>
@@ -6366,7 +6888,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>430</v>
+        <v>473</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -6379,85 +6901,85 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>431</v>
+        <v>474</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>432</v>
+        <v>475</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>435</v>
+        <v>478</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G6" s="37" t="n">
-        <f aca="false">'Site Electrical'!G25</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C1",'Site Electrical'!A:A,0))</f>
         <v>9</v>
       </c>
       <c r="H6" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>437</v>
+        <v>480</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>438</v>
+        <v>481</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>439</v>
+        <v>482</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>440</v>
+        <v>483</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G7" s="37" t="n">
-        <f aca="false">'Site Electrical'!G26</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C2",'Site Electrical'!A:A,0))</f>
         <v>7</v>
       </c>
       <c r="H7" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>441</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>442</v>
+        <v>485</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>443</v>
+        <v>486</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>433</v>
+        <v>476</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>434</v>
+        <v>477</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G8" s="37" t="n">
-        <f aca="false">'Site Electrical'!G27</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C3",'Site Electrical'!A:A,0))</f>
         <v>2</v>
       </c>
       <c r="H8" s="21" t="s">
@@ -6467,126 +6989,127 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>445</v>
+        <v>488</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>446</v>
+        <v>489</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>447</v>
+        <v>490</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>448</v>
+        <v>491</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>449</v>
+        <v>492</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="G9" s="21" t="n">
+        <v>493</v>
+      </c>
+      <c r="G9" s="37" t="n">
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C4",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
       <c r="H9" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>451</v>
+        <v>494</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>452</v>
+        <v>495</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>453</v>
+        <v>496</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>454</v>
+        <v>497</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>455</v>
+        <v>498</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>456</v>
+        <v>499</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G10" s="37" t="n">
-        <f aca="false">'Site Electrical'!G30</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C6",'Site Electrical'!A:A,0))</f>
         <v>6</v>
       </c>
       <c r="H10" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>457</v>
+        <v>500</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>458</v>
+        <v>501</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>459</v>
+        <v>502</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>460</v>
+        <v>503</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>461</v>
+        <v>504</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>462</v>
+        <v>505</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>436</v>
+        <v>479</v>
       </c>
       <c r="G11" s="37" t="n">
-        <f aca="false">'Site Electrical'!G32</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C8",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
       <c r="H11" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>463</v>
+        <v>506</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>464</v>
+        <v>507</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>465</v>
+        <v>508</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>466</v>
+        <v>509</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>467</v>
+        <v>510</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>450</v>
+        <v>493</v>
       </c>
       <c r="G12" s="37" t="n">
-        <f aca="false">'Site Electrical'!G33</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C9",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
       <c r="H12" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>468</v>
+        <v>511</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>469</v>
+        <v>512</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -6599,22 +7122,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>470</v>
+        <v>513</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>471</v>
+        <v>514</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>472</v>
+        <v>515</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>473</v>
+        <v>516</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>474</v>
+        <v>517</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>1</v>
@@ -6623,689 +7146,838 @@
         <v>69</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>475</v>
+        <v>518</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>476</v>
+        <v>519</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>477</v>
+        <v>520</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>478</v>
+        <v>521</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>479</v>
+        <v>522</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>480</v>
+        <v>523</v>
       </c>
       <c r="F15" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G15" s="37" t="n">
-        <f aca="false">'Site Electrical'!G20</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("B3",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
       <c r="H15" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>482</v>
+        <v>525</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>483</v>
+        <v>526</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>484</v>
+        <v>527</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>485</v>
+        <v>528</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>486</v>
+        <v>529</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>487</v>
+        <v>530</v>
       </c>
       <c r="F16" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G16" s="37" t="n">
-        <f aca="false">'Site Electrical'!G38</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D1",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
       <c r="H16" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>488</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>489</v>
+        <v>532</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>490</v>
+        <v>533</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>491</v>
+        <v>534</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>492</v>
+        <v>535</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>493</v>
+        <v>536</v>
       </c>
       <c r="F17" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G17" s="37" t="n">
-        <f aca="false">'Site Electrical'!G29</f>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C5",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
       <c r="H17" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="19" t="s">
-        <v>495</v>
-      </c>
-      <c r="B18" s="20"/>
-      <c r="C18" s="20"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="20"/>
-      <c r="G18" s="20"/>
-      <c r="H18" s="20"/>
-      <c r="I18" s="20"/>
+        <v>537</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
+        <v>538</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="F18" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G18" s="37" t="n">
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D4",'Site Electrical'!A:A,0))</f>
+        <v>3</v>
+      </c>
+      <c r="H18" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>543</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>496</v>
+        <v>544</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>497</v>
+        <v>545</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>498</v>
+        <v>233</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>499</v>
+        <v>546</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="F19" s="38" t="s">
-        <v>450</v>
+        <v>547</v>
+      </c>
+      <c r="F19" s="39" t="s">
+        <v>524</v>
       </c>
       <c r="G19" s="37" t="n">
-        <f aca="false">'Telecom OSP'!G6</f>
-        <v>4</v>
+        <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C12",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("D3",'Site Electrical'!A:A,0))</f>
+        <v>56</v>
       </c>
       <c r="H19" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
-        <v>502</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>503</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>234</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>504</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="F20" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="G20" s="37" t="n">
-        <f aca="false">'Telecom OSP'!G7</f>
-        <v>5</v>
-      </c>
-      <c r="H20" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I20" s="8" t="s">
-        <v>506</v>
-      </c>
+        <v>548</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
+        <v>549</v>
+      </c>
+      <c r="B20" s="20"/>
+      <c r="C20" s="20"/>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20"/>
+      <c r="F20" s="20"/>
+      <c r="G20" s="20"/>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20"/>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>507</v>
+        <v>550</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>508</v>
+        <v>551</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>509</v>
+        <v>552</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>510</v>
+        <v>553</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="F21" s="39" t="s">
-        <v>481</v>
+        <v>554</v>
+      </c>
+      <c r="F21" s="38" t="s">
+        <v>493</v>
       </c>
       <c r="G21" s="37" t="n">
-        <f aca="false">ROUND('Telecom OSP'!G17*2+'Telecom OSP'!G20*4,0)</f>
-        <v>2499</v>
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A1",'Telecom OSP'!A:A,0))</f>
+        <v>4</v>
       </c>
       <c r="H21" s="21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>513</v>
+        <v>556</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>514</v>
+        <v>557</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>515</v>
+        <v>257</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>510</v>
+        <v>558</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>516</v>
+        <v>559</v>
       </c>
       <c r="F22" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G22" s="37" t="n">
-        <f aca="false">ROUND('Telecom OSP'!G23*2,0)</f>
-        <v>598</v>
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A2",'Telecom OSP'!A:A,0))</f>
+        <v>5</v>
       </c>
       <c r="H22" s="21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>518</v>
+        <v>561</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>519</v>
+        <v>562</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>520</v>
+        <v>563</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>521</v>
+        <v>564</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>436</v>
+        <v>565</v>
+      </c>
+      <c r="F23" s="39" t="s">
+        <v>524</v>
       </c>
       <c r="G23" s="37" t="n">
-        <f aca="false">ROUND('Telecom OSP'!G17*2+'Telecom OSP'!G20*4,0)</f>
+        <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
         <v>2499</v>
       </c>
       <c r="H23" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>523</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
+        <v>567</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>568</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>569</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="E24" s="7" t="s">
+        <v>570</v>
+      </c>
+      <c r="F24" s="39" t="s">
         <v>524</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>436</v>
-      </c>
       <c r="G24" s="37" t="n">
-        <f aca="false">ROUND('Telecom OSP'!G23*2,0)</f>
+        <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
         <v>598</v>
       </c>
       <c r="H24" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>529</v>
+        <v>572</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>530</v>
+        <v>573</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>531</v>
+        <v>574</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>533</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>481</v>
+        <v>576</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>479</v>
       </c>
       <c r="G25" s="37" t="n">
-        <f aca="false">'Telecom OSP'!G34</f>
-        <v>1600</v>
+        <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
+        <v>2499</v>
       </c>
       <c r="H25" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>534</v>
+        <v>577</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>535</v>
+        <v>578</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>536</v>
+        <v>579</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>537</v>
+        <v>580</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>538</v>
+        <v>575</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <v>1</v>
+        <v>581</v>
+      </c>
+      <c r="F26" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="G26" s="37" t="n">
+        <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
+        <v>598</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>77</v>
+        <v>61</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>541</v>
+        <v>583</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>543</v>
+        <v>585</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>544</v>
+        <v>586</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>545</v>
+        <v>587</v>
       </c>
       <c r="F27" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G27" s="37" t="n">
-        <f aca="false">'Telecom OSP'!G26</f>
-        <v>1407</v>
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("D1",'Telecom OSP'!A:A,0))</f>
+        <v>1600</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>546</v>
+        <v>588</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>547</v>
-      </c>
-      <c r="B28" s="20"/>
-      <c r="C28" s="20"/>
-      <c r="D28" s="20"/>
-      <c r="E28" s="20"/>
-      <c r="F28" s="20"/>
-      <c r="G28" s="20"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
+        <v>589</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>590</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>591</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>592</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G28" s="21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I28" s="8" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>548</v>
+        <v>595</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>549</v>
+        <v>596</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>550</v>
+        <v>597</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>551</v>
+        <v>598</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>552</v>
+        <v>599</v>
       </c>
       <c r="F29" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="G29" s="21" t="n">
-        <v>3</v>
+        <v>524</v>
+      </c>
+      <c r="G29" s="37" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C1",'Telecom OSP'!A:A,0))</f>
+        <v>1407</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>554</v>
+        <v>601</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>555</v>
+        <v>602</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>556</v>
+        <v>603</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>551</v>
+        <v>604</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>557</v>
+        <v>605</v>
       </c>
       <c r="F30" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G30" s="37" t="n">
-        <f aca="false">Security!G20</f>
-        <v>1</v>
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C7",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C8",'Telecom OSP'!A:A,0))</f>
+        <v>42</v>
       </c>
       <c r="H30" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>558</v>
+        <v>606</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>559</v>
+        <v>607</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>560</v>
+        <v>608</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>561</v>
+        <v>609</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>562</v>
+        <v>610</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>563</v>
+        <v>611</v>
       </c>
       <c r="F31" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G31" s="37" t="n">
-        <f aca="false">Security!G6</f>
-        <v>2</v>
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C10",'Telecom OSP'!A:A,0))</f>
+        <v>10</v>
       </c>
       <c r="H31" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>565</v>
+        <v>613</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>566</v>
+        <v>614</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>567</v>
+        <v>615</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>568</v>
+        <v>616</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>569</v>
+        <v>617</v>
       </c>
       <c r="F32" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="G32" s="37" t="n">
-        <f aca="false">Security!G8+Security!G9</f>
-        <v>2</v>
+        <v>524</v>
+      </c>
+      <c r="G32" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="H32" s="21" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
-        <v>571</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>572</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>573</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>574</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>575</v>
-      </c>
-      <c r="F33" s="38" t="s">
-        <v>450</v>
-      </c>
-      <c r="G33" s="37" t="n">
-        <f aca="false">Security!G16+Security!G17</f>
-        <v>2</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="I33" s="8" t="s">
-        <v>576</v>
-      </c>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="19" t="s">
+        <v>619</v>
+      </c>
+      <c r="B33" s="20"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
+      <c r="G33" s="20"/>
+      <c r="H33" s="20"/>
+      <c r="I33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>577</v>
+        <v>620</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="F34" s="39" t="s">
-        <v>481</v>
-      </c>
-      <c r="G34" s="37" t="n">
-        <f aca="false">Security!G12</f>
+        <v>524</v>
+      </c>
+      <c r="G34" s="21" t="n">
         <v>3</v>
       </c>
       <c r="H34" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>582</v>
+        <v>625</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>583</v>
+        <v>626</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>584</v>
+        <v>627</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>585</v>
+        <v>628</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>586</v>
+        <v>623</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>587</v>
+        <v>629</v>
       </c>
       <c r="F35" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G35" s="37" t="n">
-        <f aca="false">Security!G11</f>
-        <v>3</v>
+        <f aca="false">INDEX(Security!G:G,MATCH("B5",Security!A:A,0))</f>
+        <v>1</v>
       </c>
       <c r="H35" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>588</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>589</v>
+        <v>631</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>590</v>
+        <v>632</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>591</v>
+        <v>633</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>592</v>
+        <v>634</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>593</v>
+        <v>635</v>
       </c>
       <c r="F36" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G36" s="37" t="n">
-        <f aca="false">Security!G27</f>
-        <v>1400</v>
+        <f aca="false">INDEX(Security!G:G,MATCH("A1",Security!A:A,0))</f>
+        <v>2</v>
       </c>
       <c r="H36" s="21" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>595</v>
+        <v>637</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>596</v>
+        <v>638</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>597</v>
+        <v>639</v>
       </c>
       <c r="D37" s="7" t="s">
-        <v>598</v>
+        <v>640</v>
       </c>
       <c r="E37" s="7" t="s">
-        <v>599</v>
+        <v>641</v>
       </c>
       <c r="F37" s="39" t="s">
-        <v>481</v>
+        <v>524</v>
       </c>
       <c r="G37" s="37" t="n">
-        <f aca="false">Security!G26</f>
-        <v>1800</v>
+        <f aca="false">INDEX(Security!G:G,MATCH("A3",Security!A:A,0))+INDEX(Security!G:G,MATCH("A4",Security!A:A,0))</f>
+        <v>2</v>
       </c>
       <c r="H37" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="I37" s="8"/>
+        <v>69</v>
+      </c>
+      <c r="I37" s="8" t="s">
+        <v>642</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>600</v>
+        <v>643</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>601</v>
+        <v>644</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>602</v>
+        <v>645</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>603</v>
+        <v>646</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="F38" s="39" t="s">
-        <v>481</v>
+        <v>647</v>
+      </c>
+      <c r="F38" s="38" t="s">
+        <v>493</v>
       </c>
       <c r="G38" s="37" t="n">
-        <f aca="false">Security!G18</f>
-        <v>1</v>
+        <f aca="false">INDEX(Security!G:G,MATCH("B1",Security!A:A,0))+INDEX(Security!G:G,MATCH("B2",Security!A:A,0))</f>
+        <v>2</v>
       </c>
       <c r="H38" s="21" t="s">
         <v>69</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>605</v>
+        <v>648</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>649</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>650</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>651</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>652</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>653</v>
+      </c>
+      <c r="F39" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G39" s="37" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("A7",Security!A:A,0))</f>
+        <v>3</v>
+      </c>
+      <c r="H39" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I39" s="8" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>655</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>656</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>657</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>658</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>659</v>
+      </c>
+      <c r="F40" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G40" s="37" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("A6",Security!A:A,0))</f>
+        <v>3</v>
+      </c>
+      <c r="H40" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I40" s="8" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>661</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>662</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>663</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>664</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>665</v>
+      </c>
+      <c r="F41" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G41" s="37" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("C2",Security!A:A,0))</f>
+        <v>1400</v>
+      </c>
+      <c r="H41" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I41" s="8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>667</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>668</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>669</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>670</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>671</v>
+      </c>
+      <c r="F42" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G42" s="37" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("C1",Security!A:A,0))</f>
+        <v>1800</v>
+      </c>
+      <c r="H42" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I42" s="8"/>
+    </row>
+    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>672</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>673</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>674</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>675</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>676</v>
+      </c>
+      <c r="F43" s="39" t="s">
+        <v>524</v>
+      </c>
+      <c r="G43" s="37" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("B3",Security!A:A,0))</f>
+        <v>1</v>
+      </c>
+      <c r="H43" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="I43" s="8" t="s">
+        <v>677</v>
       </c>
     </row>
   </sheetData>
@@ -7334,42 +8006,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="40" t="s">
-        <v>606</v>
+        <v>678</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="41" t="s">
-        <v>607</v>
+        <v>679</v>
       </c>
       <c r="C4" s="42"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="43" t="s">
-        <v>608</v>
+        <v>680</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>609</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="43" t="s">
-        <v>610</v>
+        <v>682</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>611</v>
+        <v>683</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="43" t="s">
-        <v>612</v>
+        <v>684</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>613</v>
+        <v>685</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="41" t="s">
-        <v>614</v>
+        <v>686</v>
       </c>
       <c r="C9" s="42"/>
     </row>
@@ -7378,15 +8050,15 @@
         <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>615</v>
+        <v>687</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="43" t="s">
-        <v>254</v>
+        <v>277</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>616</v>
+        <v>688</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7394,343 +8066,343 @@
         <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>617</v>
+        <v>689</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="43" t="s">
-        <v>199</v>
+        <v>149</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>618</v>
+        <v>690</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="43" t="s">
-        <v>619</v>
+        <v>691</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>620</v>
+        <v>692</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="43" t="s">
-        <v>621</v>
+        <v>693</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>622</v>
+        <v>694</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="41" t="s">
-        <v>623</v>
+        <v>695</v>
       </c>
       <c r="C17" s="42"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="43" t="s">
-        <v>624</v>
+        <v>696</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>625</v>
+        <v>697</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="43" t="s">
-        <v>626</v>
+        <v>698</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>627</v>
+        <v>699</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="43" t="s">
-        <v>628</v>
+        <v>700</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>629</v>
+        <v>701</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="43" t="s">
-        <v>630</v>
+        <v>702</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>631</v>
+        <v>703</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="43" t="s">
-        <v>632</v>
+        <v>704</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>633</v>
+        <v>705</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="43" t="s">
-        <v>634</v>
+        <v>706</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>635</v>
+        <v>707</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="43" t="s">
-        <v>636</v>
+        <v>708</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>637</v>
+        <v>709</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="43" t="s">
-        <v>638</v>
+        <v>710</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>639</v>
+        <v>711</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="43" t="s">
-        <v>640</v>
+        <v>712</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>641</v>
+        <v>713</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="43" t="s">
-        <v>642</v>
+        <v>714</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>643</v>
+        <v>715</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="43" t="s">
-        <v>644</v>
+        <v>716</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>645</v>
+        <v>717</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="41" t="s">
-        <v>646</v>
+        <v>718</v>
       </c>
       <c r="C30" s="42"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="43" t="s">
-        <v>647</v>
+        <v>719</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>648</v>
+        <v>720</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="43" t="s">
-        <v>649</v>
+        <v>721</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>650</v>
+        <v>722</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="43" t="s">
-        <v>651</v>
+        <v>723</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>652</v>
+        <v>724</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="43" t="s">
-        <v>653</v>
+        <v>725</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>654</v>
+        <v>726</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="43" t="s">
-        <v>655</v>
+        <v>727</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>656</v>
+        <v>728</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="43" t="s">
-        <v>657</v>
+        <v>729</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>658</v>
+        <v>730</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="43" t="s">
-        <v>659</v>
+        <v>731</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>660</v>
+        <v>732</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="43" t="s">
-        <v>661</v>
+        <v>733</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>662</v>
+        <v>734</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="41" t="s">
-        <v>663</v>
+        <v>735</v>
       </c>
       <c r="C40" s="42"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B41" s="43" t="s">
-        <v>664</v>
+        <v>736</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>665</v>
+        <v>737</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="43" t="s">
-        <v>666</v>
+        <v>738</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>667</v>
+        <v>739</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="43" t="s">
-        <v>668</v>
+        <v>740</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>669</v>
+        <v>741</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="43" t="s">
-        <v>670</v>
+        <v>742</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>671</v>
+        <v>743</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="43" t="s">
-        <v>672</v>
+        <v>744</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>673</v>
+        <v>745</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="43" t="s">
-        <v>674</v>
+        <v>746</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>675</v>
+        <v>747</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="43" t="s">
-        <v>676</v>
+        <v>748</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>677</v>
+        <v>749</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="43" t="s">
-        <v>678</v>
+        <v>750</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>679</v>
+        <v>751</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="43" t="s">
-        <v>680</v>
+        <v>752</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>681</v>
+        <v>753</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="43" t="s">
-        <v>682</v>
+        <v>754</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>683</v>
+        <v>755</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="43" t="s">
-        <v>684</v>
+        <v>756</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>685</v>
+        <v>757</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="43" t="s">
-        <v>686</v>
+        <v>758</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>687</v>
+        <v>759</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="43" t="s">
-        <v>688</v>
+        <v>760</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>689</v>
+        <v>761</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="43" t="s">
-        <v>690</v>
+        <v>762</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>691</v>
+        <v>763</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="41" t="s">
-        <v>692</v>
+        <v>764</v>
       </c>
       <c r="C56" s="42"/>
     </row>
     <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B57" s="43" t="s">
-        <v>693</v>
+        <v>765</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>694</v>
+        <v>766</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="43" t="s">
-        <v>695</v>
+        <v>767</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>696</v>
+        <v>768</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="43" t="s">
-        <v>697</v>
+        <v>769</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>698</v>
+        <v>770</v>
       </c>
     </row>
   </sheetData>

--- a/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
+++ b/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
@@ -12,8 +12,9 @@
     <sheet name="Site Electrical" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Telecom OSP" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Security" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Materials &amp; Makes" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Cable Schedule" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Materials &amp; Makes" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Assumptions" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1167" uniqueCount="771">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="893">
   <si>
     <t xml:space="preserve">DETAILED QUANTITY TAKEOFF — EXTERIOR ELECTRICAL &amp; COMMUNICATIONS</t>
   </si>
@@ -1095,7 +1096,7 @@
     <t xml:space="preserve">D. OSP CABLING (TSN300 site one-line)</t>
   </si>
   <si>
-    <t xml:space="preserve">OSP fiber — Bldg A to MH/HH system incl. coils for future connection at Bldg B/C and east gate handholes</t>
+    <t xml:space="preserve">OSP fiber — Bldg A to MH/HH system incl. coils for future connection at Bldg B/C and east gate handholes (3 runs)</t>
   </si>
   <si>
     <t xml:space="preserve">12-strand</t>
@@ -1104,10 +1105,10 @@
     <t xml:space="preserve">OM4 50/125 multimode, OSP-rated (gel-free, assumed), green-dashed runs per TSN300</t>
   </si>
   <si>
-    <t xml:space="preserve">TSN300</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Routes + 20% slack + coils (QC: coiled for future connection at HH1s). Revise when cable schedule issued.</t>
+    <t xml:space="preserve">TSN300; Cable Schedule F1-F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-by-run buildup on Cable Schedule tab (segments + coil + interior + slack). QC: fiber coiled for future connection at HH1s.</t>
   </si>
   <si>
     <t xml:space="preserve">Fiber terminations, LIU/patch panel at Bldg A, testing &amp; documentation</t>
@@ -1356,22 +1357,22 @@
     <t xml:space="preserve">C. CABLING (homeruns via telecom duct bank system to COMM 124)</t>
   </si>
   <si>
-    <t xml:space="preserve">OSP-rated access control cable to each card reader location</t>
+    <t xml:space="preserve">OSP-rated access control cable to each card reader location (5 runs)</t>
   </si>
   <si>
     <t xml:space="preserve">Composite/multi-conductor per spec 28</t>
   </si>
   <si>
-    <t xml:space="preserve">OSP-rated ACS cable (reader/lock/DPS/REX composite assumed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSY100 QC notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 reader locations; homerun lengths estimated along duct routes + slack.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extended-reach copper data cable to each intercom (3)</t>
+    <t xml:space="preserve">OSP-rated ACS cable (reader/lock/REX composite assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSY100 QC; Cable Schedule R1-R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run-by-run buildup on Cable Schedule tab (path lengths live from TSN100 segments + interior &amp; slack inputs).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended-reach copper data cable to each intercom (3 runs)</t>
   </si>
   <si>
     <t xml:space="preserve">4-pair, 22 AWG min</t>
@@ -1380,10 +1381,10 @@
     <t xml:space="preserve">Extended-reach PoE-rated OSP copper data cable (per TSY101 riser note &amp; QC keynote)</t>
   </si>
   <si>
-    <t xml:space="preserve">TSY101; TSY100 QC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">(3) cables per riser note. Verify length/bandwidth/PoE load/voltage-drop per mfr (GN 9) — east gate run ±600 LF.</t>
+    <t xml:space="preserve">TSY101; Cable Schedule R3-R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify length/bandwidth/PoE load/voltage-drop per mfr (GN 9) — east gate run ±560 LF vs. extended-reach limit.</t>
   </si>
   <si>
     <t xml:space="preserve">ACS cables, ACP1/ACP2 to Bldg A doors/monitored devices — BUILDING PACKAGE</t>
@@ -1401,6 +1402,51 @@
     <t xml:space="preserve">TSY002; TSY100 GN 8</t>
   </si>
   <si>
+    <t xml:space="preserve">Gate position switch (DPS) monitoring cable to head end (3 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-cond shielded OSP (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP-rated supervision pair per DPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A7/TSY101; Cable Schedule R3-R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes DPS monitored at ACP (not in operator) — verify signal path; if landed in operator, delete this line.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device conduit stubs &amp; risers — 1"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1" (7 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC/RGS stub-ups: pedestal risers (2), bldg intercom stub (1), gate rough-ins (2)x1" x2 gates (4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1,A13/TSY101; TSY001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itemized on Cable Schedule Table C. Conduit described in device rows A1/A2/A8 is PRICED HERE ONLY — do not double-count.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device conduit stubs — 3/4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4" (5 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PVC/RGS: reader stubs (2), DPS box-to-handhole (3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A7/TSY101; TSY001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Itemized on Cable Schedule Table C; lengths assumed (heights/routing not dimensioned).</t>
+  </si>
+  <si>
     <t xml:space="preserve">D. EXCLUSIONS (struck from TSY002 responsibility matrix at 65% — VERIFY)</t>
   </si>
   <si>
@@ -1425,6 +1471,309 @@
     <t xml:space="preserve">SECURITY TOTAL</t>
   </si>
   <si>
+    <t xml:space="preserve">CABLE &amp; CONDUIT SCHEDULE — SECURITY &amp; COMMUNICATIONS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run lengths are LIVE: each path sums the TSN100 duct bank segments (Telecom OSP tab) + interior allowance, times (1 + slack). Adjust the yellow inputs and every cable total, takeoff line and procurement quantity follows.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPUTS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interior allowance, duct bank entry to COMM 124 rack (per run)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMM 124 location within Bldg A not shown in site set — verify.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slack / service loops / vertical rises</t>
+  </si>
+  <si>
+    <t xml:space="preserve">%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber coil at each future-connection handhole</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE A — SECURITY CABLE RUNS (homeruns to COMM 124, Bldg A)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Device / location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Path (via structures)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site path LF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Run LF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedestrian gate card reader @ Bldg C (HH1-2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-2 &gt; MH1-2 &gt; MH1-3 &gt; Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Swing gate card reader (TSY101 inset — path assumed as R1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify vs. RFI-4 (possible overlap w/ R1 reader).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle gate 1 — Bldg B intercom/reader (HH1-4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-4 &gt; MH1-2 &gt; MH1-3 &gt; Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle gate 2 — pedestal @ HH1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-5 &gt; HH1-3 &gt; MH1-4 &gt; MH1-3 &gt; Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vehicle gate 3 — pedestal @ HH1-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-6 &gt; HH1-5 &gt; HH1-3 &gt; MH1-4 &gt; MH1-3 &gt; Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-ACS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACS cable total (5 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-DATA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extended-reach data total (3 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-DPS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS monitoring total (3 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE B — COMM FIBER RUNS (12-strand OM4, TSN300)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">From &gt; To</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; HH1-2 (coil for future Bldg C)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; MH1-3 &gt; MH1-2 &gt; HH1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; HH1-4 (coil for future Bldg B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; MH1-3 &gt; MH1-2 &gt; HH1-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; HH1-6 (coil, east gates)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg A &gt; MH1-3 &gt; MH1-4 &gt; HH1-3 &gt; HH1-5 &gt; HH1-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-FIBER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OM4 fiber total (3 runs incl. coils)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(info)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP fiber, pedestal &gt; Bldg A — BY ISP (pathway only in contract)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP ped &gt; MH1-1 &gt; MH1-2 &gt; MH1-3 &gt; Bldg A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE C — DEVICE CONDUIT STUBS &amp; RISERS (security field devices; lengths assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ref</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conduit run</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Runs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF ea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LF tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pedestal riser, signal (A1/TSY101 detail — '1" conduit for signal cables')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bldg B intercom/reader stub to accessible ceiling (TSY001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gate rough-in, (2) 1" conduits to SEC x 2 gates (A13/TSY101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Card reader stub (ped. &amp; swing gates, TSY001)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3/4"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS WP box to handhole (A7/TSY101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-C1IN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 1" device conduit (7 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOT-C34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 3/4" device conduit (5 runs)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TABLE D — DUCT BANK SEGMENT OCCUPANCY (cables riding each segment — info for pulling &amp; cell assignment)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seg.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct bank segment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cables</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-3 &gt; Bldg A entry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heaviest segment — 14 cables in 12 cells; multiple LV cables per fabric cell is normal, but assign cells deliberately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-2 &gt; MH1-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-3 &gt; MH1-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-4 &gt; HH1-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-3 &gt; HH1-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HH1-5 &gt; HH1-6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-2 &gt; HH1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-2 &gt; HH1-4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-1 &gt; MH1-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISP fiber only (by ISP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH1-1 &gt; ISP pedestal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOTE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cells = conduits x 3 MaxCell cells. Counts are pass-through cables per this schedule's runs; ISP fiber (B1/B2/B8/B9) is pulled by ISP. No cables in vacant cells — plug per Telecom C11.</t>
+  </si>
+  <si>
     <t xml:space="preserve">MATERIALS, MAKES &amp; MODELS — PROCUREMENT LIST</t>
   </si>
   <si>
@@ -2059,6 +2408,24 @@
   </si>
   <si>
     <t xml:space="preserve">Rack per G2/TSY101; SPD line item Security B8.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPS monitoring cable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2-cond shielded, OSP-rated (assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Belden / West Penn (or equal)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSP supervision pair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 runs per Cable Schedule; delete if DPS lands in gate operator instead of ACP.</t>
   </si>
   <si>
     <t xml:space="preserve">ASSUMPTIONS, CLARIFICATIONS &amp; EXCLUSIONS</t>
@@ -2344,14 +2711,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="7">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="#,##0"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
     <numFmt numFmtId="168" formatCode="#,##0.0"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2461,9 +2830,14 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FF1F4E79"/>
+      <i val="true"/>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2471,6 +2845,14 @@
     <font>
       <b val="true"/>
       <sz val="9"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="14"/>
+      <color rgb="FF1F4E79"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2575,7 +2957,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="59">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2720,12 +3102,72 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="15" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2736,7 +3178,7 @@
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2748,7 +3190,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3091,7 +3533,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="9" t="n">
-        <f aca="false">Security!J37</f>
+        <f aca="false">Security!J40</f>
         <v>0</v>
       </c>
       <c r="E11" s="8" t="s">
@@ -5673,10 +6115,11 @@
         <v>359</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39" s="22" t="n">
-        <v>1600</v>
+        <v>308</v>
+      </c>
+      <c r="G39" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-FIBER",'Cable Schedule'!A:A,0))</f>
+        <v>1425</v>
       </c>
       <c r="H39" s="21" t="s">
         <v>61</v>
@@ -5842,7 +6285,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K40"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6440,7 +6883,7 @@
       <c r="H22" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I22" s="36"/>
+      <c r="I22" s="37"/>
       <c r="J22" s="35"/>
       <c r="K22" s="27" t="s">
         <v>439</v>
@@ -6528,10 +6971,11 @@
         <v>446</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="G26" s="22" t="n">
-        <v>1800</v>
+        <v>308</v>
+      </c>
+      <c r="G26" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-ACS",'Cable Schedule'!A:A,0))</f>
+        <v>1993</v>
       </c>
       <c r="H26" s="21" t="s">
         <v>61</v>
@@ -6562,10 +7006,11 @@
         <v>451</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="G27" s="22" t="n">
-        <v>1400</v>
+        <v>308</v>
+      </c>
+      <c r="G27" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-DATA",'Cable Schedule'!A:A,0))</f>
+        <v>1209</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>61</v>
@@ -6604,7 +7049,7 @@
       <c r="H28" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="I28" s="36"/>
+      <c r="I28" s="37"/>
       <c r="J28" s="35"/>
       <c r="K28" s="8" t="s">
         <v>454</v>
@@ -6642,138 +7087,150 @@
       </c>
       <c r="K29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="28"/>
-      <c r="B30" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="30" t="n">
-        <f aca="false">SUM(J26:J29)</f>
-        <v>0</v>
-      </c>
-      <c r="K30" s="28"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="B30" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="B31" s="20"/>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
+      <c r="C30" s="7" t="s">
+        <v>459</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="E30" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="F30" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="G30" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-DPS",'Cable Schedule'!A:A,0))</f>
+        <v>1209</v>
+      </c>
+      <c r="H30" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I30" s="23"/>
+      <c r="J30" s="24" t="str">
+        <f aca="false">IF(I30="","",G30*I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="27" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>463</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="E31" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G31" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-C1IN",'Cable Schedule'!A:A,0))</f>
+        <v>140</v>
+      </c>
+      <c r="H31" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I31" s="23"/>
+      <c r="J31" s="24" t="str">
+        <f aca="false">IF(I31="","",G31*I31)</f>
+        <v/>
+      </c>
+      <c r="K31" s="27" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>468</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>469</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G32" s="36" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-C34",'Cable Schedule'!A:A,0))</f>
+        <v>85</v>
+      </c>
+      <c r="H32" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I32" s="23"/>
+      <c r="J32" s="24" t="str">
+        <f aca="false">IF(I32="","",G32*I32)</f>
+        <v/>
+      </c>
+      <c r="K32" s="27" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="28"/>
+      <c r="B33" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="30" t="n">
+        <f aca="false">SUM(J26:J32)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="28"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
+        <v>473</v>
+      </c>
+      <c r="B34" s="20"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+    </row>
+    <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="B32" s="26" t="s">
-        <v>459</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="G32" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="I32" s="36"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>461</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="G33" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="I33" s="36"/>
-      <c r="J33" s="35"/>
-      <c r="K33" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>462</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="F34" s="21" t="s">
-        <v>438</v>
-      </c>
-      <c r="G34" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="I34" s="36"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="27" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
-        <v>237</v>
-      </c>
       <c r="B35" s="26" t="s">
-        <v>464</v>
+        <v>474</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>65</v>
@@ -6793,29 +7250,122 @@
       <c r="H35" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="I35" s="36"/>
+      <c r="I35" s="37"/>
       <c r="J35" s="35"/>
       <c r="K35" s="27" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11"/>
-      <c r="B37" s="10" t="s">
-        <v>465</v>
-      </c>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="12" t="n">
-        <f aca="false">J14+J24+J30</f>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>476</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="F36" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="G36" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="K37" s="11"/>
+      <c r="H36" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I36" s="37"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>477</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="G37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I37" s="37"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="27" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>237</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>479</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="G38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="I38" s="37"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="27" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="11"/>
+      <c r="B40" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="C40" s="11"/>
+      <c r="D40" s="11"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="11"/>
+      <c r="G40" s="11"/>
+      <c r="H40" s="11"/>
+      <c r="I40" s="11"/>
+      <c r="J40" s="12" t="n">
+        <f aca="false">J14+J24+J33</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6833,7 +7383,1024 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:J51"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="6" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="18" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="C5" s="38" t="n">
+        <v>50</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="C6" s="40" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="C7" s="38" t="n">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="5" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>491</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>494</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="41" t="s">
+        <v>498</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D11" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>306.4</v>
+      </c>
+      <c r="E11" s="43" t="n">
+        <f aca="false">ROUND((D11+$C$5)*(1+$C$6),0)</f>
+        <v>392</v>
+      </c>
+      <c r="F11" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="44"/>
+      <c r="J11" s="44"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="41" t="s">
+        <v>501</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="D12" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>306.4</v>
+      </c>
+      <c r="E12" s="43" t="n">
+        <f aca="false">ROUND((D12+$C$5)*(1+$C$6),0)</f>
+        <v>392</v>
+      </c>
+      <c r="F12" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="44"/>
+      <c r="J12" s="45" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="41" t="s">
+        <v>504</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>505</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>506</v>
+      </c>
+      <c r="D13" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B4",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>231.4</v>
+      </c>
+      <c r="E13" s="43" t="n">
+        <f aca="false">ROUND((D13+$C$5)*(1+$C$6),0)</f>
+        <v>310</v>
+      </c>
+      <c r="F13" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G13" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="41" t="s">
+        <v>507</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>508</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="D14" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>259.7</v>
+      </c>
+      <c r="E14" s="43" t="n">
+        <f aca="false">ROUND((D14+$C$5)*(1+$C$6),0)</f>
+        <v>341</v>
+      </c>
+      <c r="F14" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="41" t="s">
+        <v>510</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>511</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>512</v>
+      </c>
+      <c r="D15" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B12",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>457</v>
+      </c>
+      <c r="E15" s="43" t="n">
+        <f aca="false">ROUND((D15+$C$5)*(1+$C$6),0)</f>
+        <v>558</v>
+      </c>
+      <c r="F15" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G15" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="44"/>
+      <c r="J15" s="44"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="s">
+        <v>513</v>
+      </c>
+      <c r="B16" s="29" t="s">
+        <v>514</v>
+      </c>
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="46" t="n">
+        <f aca="false">SUMPRODUCT(E11:E15,F11:F15)</f>
+        <v>1993</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="s">
+        <v>515</v>
+      </c>
+      <c r="B17" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="46" t="n">
+        <f aca="false">SUMPRODUCT(E11:E15,G11:G15)</f>
+        <v>1209</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="s">
+        <v>517</v>
+      </c>
+      <c r="B18" s="29" t="s">
+        <v>518</v>
+      </c>
+      <c r="C18" s="28"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="46" t="n">
+        <f aca="false">SUMPRODUCT(E11:E15,H11:H15)</f>
+        <v>1209</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="28"/>
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="6" t="s">
+        <v>490</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>520</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>492</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>493</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="41" t="s">
+        <v>521</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>523</v>
+      </c>
+      <c r="D22" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))</f>
+        <v>306.4</v>
+      </c>
+      <c r="E22" s="43" t="n">
+        <f aca="false">ROUND((D22+$C$7+$C$5)*(1+$C$6),0)</f>
+        <v>447</v>
+      </c>
+      <c r="F22" s="44"/>
+      <c r="G22" s="44"/>
+      <c r="H22" s="44"/>
+      <c r="I22" s="44"/>
+      <c r="J22" s="44"/>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="41" t="s">
+        <v>524</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="D23" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B4",'Telecom OSP'!A:A,0))</f>
+        <v>231.4</v>
+      </c>
+      <c r="E23" s="43" t="n">
+        <f aca="false">ROUND((D23+$C$7+$C$5)*(1+$C$6),0)</f>
+        <v>365</v>
+      </c>
+      <c r="F23" s="44"/>
+      <c r="G23" s="44"/>
+      <c r="H23" s="44"/>
+      <c r="I23" s="44"/>
+      <c r="J23" s="44"/>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="41" t="s">
+        <v>527</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D24" s="42" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B12",'Telecom OSP'!A:A,0))</f>
+        <v>457</v>
+      </c>
+      <c r="E24" s="43" t="n">
+        <f aca="false">ROUND((D24+$C$7+$C$5)*(1+$C$6),0)</f>
+        <v>613</v>
+      </c>
+      <c r="F24" s="44"/>
+      <c r="G24" s="44"/>
+      <c r="H24" s="44"/>
+      <c r="I24" s="44"/>
+      <c r="J24" s="44"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="29" t="s">
+        <v>530</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>531</v>
+      </c>
+      <c r="C25" s="28"/>
+      <c r="D25" s="28"/>
+      <c r="E25" s="46" t="n">
+        <f aca="false">SUM(E22:E24)</f>
+        <v>1425</v>
+      </c>
+      <c r="F25" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="G25" s="28"/>
+      <c r="H25" s="28"/>
+      <c r="I25" s="28"/>
+      <c r="J25" s="28"/>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="D26" s="48" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B1",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B2",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
+        <v>716.4</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="5" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="6" t="s">
+        <v>536</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>538</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>539</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="41" t="s">
+        <v>541</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>542</v>
+      </c>
+      <c r="C30" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="D30" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="41" t="n">
+        <v>10</v>
+      </c>
+      <c r="F30" s="43" t="n">
+        <f aca="false">D30*E30</f>
+        <v>20</v>
+      </c>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="44"/>
+      <c r="J30" s="44"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="41" t="s">
+        <v>544</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="C31" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="D31" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F31" s="43" t="n">
+        <f aca="false">D31*E31</f>
+        <v>20</v>
+      </c>
+      <c r="G31" s="44"/>
+      <c r="H31" s="44"/>
+      <c r="I31" s="44"/>
+      <c r="J31" s="44"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="41" t="s">
+        <v>546</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="C32" s="41" t="s">
+        <v>543</v>
+      </c>
+      <c r="D32" s="41" t="n">
+        <v>4</v>
+      </c>
+      <c r="E32" s="41" t="n">
+        <v>25</v>
+      </c>
+      <c r="F32" s="43" t="n">
+        <f aca="false">D32*E32</f>
+        <v>100</v>
+      </c>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="44"/>
+      <c r="J32" s="44"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="41" t="s">
+        <v>548</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>549</v>
+      </c>
+      <c r="C33" s="41" t="s">
+        <v>550</v>
+      </c>
+      <c r="D33" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" s="41" t="n">
+        <v>20</v>
+      </c>
+      <c r="F33" s="43" t="n">
+        <f aca="false">D33*E33</f>
+        <v>40</v>
+      </c>
+      <c r="G33" s="44"/>
+      <c r="H33" s="44"/>
+      <c r="I33" s="44"/>
+      <c r="J33" s="44"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="41" t="s">
+        <v>551</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>552</v>
+      </c>
+      <c r="C34" s="41" t="s">
+        <v>550</v>
+      </c>
+      <c r="D34" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" s="41" t="n">
+        <v>15</v>
+      </c>
+      <c r="F34" s="43" t="n">
+        <f aca="false">D34*E34</f>
+        <v>45</v>
+      </c>
+      <c r="G34" s="44"/>
+      <c r="H34" s="44"/>
+      <c r="I34" s="44"/>
+      <c r="J34" s="44"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="29" t="s">
+        <v>553</v>
+      </c>
+      <c r="B35" s="29" t="s">
+        <v>554</v>
+      </c>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="46" t="n">
+        <f aca="false">SUMPRODUCT((C30:C34="1""")*F30:F34)</f>
+        <v>140</v>
+      </c>
+      <c r="F35" s="28"/>
+      <c r="G35" s="28"/>
+      <c r="H35" s="28"/>
+      <c r="I35" s="28"/>
+      <c r="J35" s="28"/>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="29" t="s">
+        <v>555</v>
+      </c>
+      <c r="B36" s="29" t="s">
+        <v>556</v>
+      </c>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="46" t="n">
+        <f aca="false">SUMPRODUCT((C30:C34="3/4""")*F30:F34)</f>
+        <v>85</v>
+      </c>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28"/>
+      <c r="H36" s="28"/>
+      <c r="I36" s="28"/>
+      <c r="J36" s="28"/>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="5" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>558</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>559</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>560</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>496</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>497</v>
+      </c>
+      <c r="G39" s="6" t="s">
+        <v>561</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>562</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>563</v>
+      </c>
+      <c r="J39" s="6" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="41" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="C40" s="41" t="s">
+        <v>566</v>
+      </c>
+      <c r="D40" s="41" t="n">
+        <v>5</v>
+      </c>
+      <c r="E40" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="F40" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="G40" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="H40" s="49" t="n">
+        <f aca="false">SUM(D40:G40)</f>
+        <v>14</v>
+      </c>
+      <c r="I40" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="J40" s="50" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="41" t="s">
+        <v>284</v>
+      </c>
+      <c r="B41" s="8" t="s">
+        <v>568</v>
+      </c>
+      <c r="C41" s="41" t="s">
+        <v>566</v>
+      </c>
+      <c r="D41" s="41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F41" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G41" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="49" t="n">
+        <f aca="false">SUM(D41:G41)</f>
+        <v>7</v>
+      </c>
+      <c r="I41" s="41" t="n">
+        <v>12</v>
+      </c>
+      <c r="J41" s="50"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="41" t="s">
+        <v>139</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>569</v>
+      </c>
+      <c r="C42" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D42" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E42" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G42" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="49" t="n">
+        <f aca="false">SUM(D42:G42)</f>
+        <v>7</v>
+      </c>
+      <c r="I42" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J42" s="50"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="41" t="s">
+        <v>144</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>571</v>
+      </c>
+      <c r="C43" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D43" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E43" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G43" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H43" s="49" t="n">
+        <f aca="false">SUM(D43:G43)</f>
+        <v>7</v>
+      </c>
+      <c r="I43" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J43" s="50"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="41" t="s">
+        <v>292</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>572</v>
+      </c>
+      <c r="C44" s="41" t="s">
+        <v>573</v>
+      </c>
+      <c r="D44" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E44" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="G44" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H44" s="49" t="n">
+        <f aca="false">SUM(D44:G44)</f>
+        <v>7</v>
+      </c>
+      <c r="I44" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J44" s="50"/>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="41" t="s">
+        <v>297</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>574</v>
+      </c>
+      <c r="C45" s="41" t="s">
+        <v>573</v>
+      </c>
+      <c r="D45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="49" t="n">
+        <f aca="false">SUM(D45:G45)</f>
+        <v>4</v>
+      </c>
+      <c r="I45" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J45" s="50"/>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B46" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="C46" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D46" s="41" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="49" t="n">
+        <f aca="false">SUM(D46:G46)</f>
+        <v>3</v>
+      </c>
+      <c r="I46" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J46" s="50"/>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B47" s="8" t="s">
+        <v>576</v>
+      </c>
+      <c r="C47" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="F47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="G47" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="49" t="n">
+        <f aca="false">SUM(D47:G47)</f>
+        <v>4</v>
+      </c>
+      <c r="I47" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="50"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="41" t="s">
+        <v>123</v>
+      </c>
+      <c r="B48" s="8" t="s">
+        <v>577</v>
+      </c>
+      <c r="C48" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D48" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="49" t="n">
+        <f aca="false">SUM(D48:G48)</f>
+        <v>0</v>
+      </c>
+      <c r="I48" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J48" s="50" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="B49" s="8" t="s">
+        <v>579</v>
+      </c>
+      <c r="C49" s="41" t="s">
+        <v>570</v>
+      </c>
+      <c r="D49" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="49" t="n">
+        <f aca="false">SUM(D49:G49)</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="41" t="n">
+        <v>6</v>
+      </c>
+      <c r="J49" s="50" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="51" t="s">
+        <v>580</v>
+      </c>
+      <c r="B51" s="52" t="s">
+        <v>581</v>
+      </c>
+      <c r="C51" s="52"/>
+      <c r="D51" s="52"/>
+      <c r="E51" s="52"/>
+      <c r="F51" s="52"/>
+      <c r="G51" s="52"/>
+      <c r="H51" s="52"/>
+      <c r="I51" s="52"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B51:I51"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -6849,32 +8416,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>466</v>
+        <v>582</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>467</v>
+        <v>583</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>468</v>
+        <v>584</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>469</v>
+        <v>585</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>470</v>
+        <v>586</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>471</v>
+        <v>587</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>472</v>
+        <v>588</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>50</v>
@@ -6888,7 +8455,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>473</v>
+        <v>589</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -6901,24 +8468,24 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>474</v>
+        <v>590</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>475</v>
+        <v>591</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>478</v>
+        <v>594</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G6" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G6" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C1",'Site Electrical'!A:A,0))</f>
         <v>9</v>
       </c>
@@ -6926,29 +8493,29 @@
         <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>480</v>
+        <v>596</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>481</v>
+        <v>597</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>482</v>
+        <v>598</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>483</v>
+        <v>599</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G7" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G7" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C2",'Site Electrical'!A:A,0))</f>
         <v>7</v>
       </c>
@@ -6956,29 +8523,29 @@
         <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>484</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>485</v>
+        <v>601</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>486</v>
+        <v>602</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>476</v>
+        <v>592</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>477</v>
+        <v>593</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>487</v>
+        <v>603</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G8" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G8" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C3",'Site Electrical'!A:A,0))</f>
         <v>2</v>
       </c>
@@ -6989,24 +8556,24 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>488</v>
+        <v>604</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>489</v>
+        <v>605</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>490</v>
+        <v>606</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>491</v>
+        <v>607</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="G9" s="37" t="n">
+        <v>608</v>
+      </c>
+      <c r="F9" s="53" t="s">
+        <v>609</v>
+      </c>
+      <c r="G9" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C4",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
@@ -7014,29 +8581,29 @@
         <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>494</v>
+        <v>610</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>495</v>
+        <v>611</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>496</v>
+        <v>612</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>497</v>
+        <v>613</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>498</v>
+        <v>614</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>499</v>
+        <v>615</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G10" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G10" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C6",'Site Electrical'!A:A,0))</f>
         <v>6</v>
       </c>
@@ -7044,29 +8611,29 @@
         <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>500</v>
+        <v>616</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>501</v>
+        <v>617</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>502</v>
+        <v>618</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>503</v>
+        <v>619</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>504</v>
+        <v>620</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>505</v>
+        <v>621</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G11" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G11" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C8",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -7074,29 +8641,29 @@
         <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>506</v>
+        <v>622</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>507</v>
+        <v>623</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>508</v>
+        <v>624</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>509</v>
+        <v>625</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>510</v>
+        <v>626</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F12" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="G12" s="37" t="n">
+      <c r="F12" s="53" t="s">
+        <v>609</v>
+      </c>
+      <c r="G12" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C9",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
@@ -7104,12 +8671,12 @@
         <v>69</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>511</v>
+        <v>627</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>512</v>
+        <v>628</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -7122,22 +8689,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>513</v>
+        <v>629</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>514</v>
+        <v>630</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>515</v>
+        <v>631</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>516</v>
+        <v>632</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>81</v>
       </c>
       <c r="F14" s="34" t="s">
-        <v>517</v>
+        <v>633</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>1</v>
@@ -7146,29 +8713,29 @@
         <v>69</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>518</v>
+        <v>634</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>519</v>
+        <v>635</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>520</v>
+        <v>636</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>521</v>
+        <v>637</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>522</v>
+        <v>638</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>523</v>
-      </c>
-      <c r="F15" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G15" s="37" t="n">
+        <v>639</v>
+      </c>
+      <c r="F15" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G15" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("B3",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
@@ -7176,29 +8743,29 @@
         <v>69</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>525</v>
+        <v>641</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>526</v>
+        <v>642</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>527</v>
+        <v>643</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>528</v>
+        <v>644</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>529</v>
+        <v>645</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>530</v>
-      </c>
-      <c r="F16" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G16" s="37" t="n">
+        <v>646</v>
+      </c>
+      <c r="F16" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G16" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D1",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -7206,29 +8773,29 @@
         <v>69</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>531</v>
+        <v>647</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>532</v>
+        <v>648</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>533</v>
+        <v>649</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>534</v>
+        <v>650</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>535</v>
+        <v>651</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="F17" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G17" s="37" t="n">
+        <v>652</v>
+      </c>
+      <c r="F17" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G17" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C5",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
@@ -7236,29 +8803,29 @@
         <v>69</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>537</v>
+        <v>653</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>538</v>
+        <v>654</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>539</v>
+        <v>655</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>540</v>
+        <v>656</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>541</v>
+        <v>657</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>542</v>
-      </c>
-      <c r="F18" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G18" s="37" t="n">
+        <v>658</v>
+      </c>
+      <c r="F18" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G18" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D4",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -7266,29 +8833,29 @@
         <v>69</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>543</v>
+        <v>659</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>544</v>
+        <v>660</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>545</v>
+        <v>661</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>233</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>546</v>
+        <v>662</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>547</v>
-      </c>
-      <c r="F19" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G19" s="37" t="n">
+        <v>663</v>
+      </c>
+      <c r="F19" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G19" s="36" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C12",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("D3",'Site Electrical'!A:A,0))</f>
         <v>56</v>
       </c>
@@ -7296,12 +8863,12 @@
         <v>69</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>548</v>
+        <v>664</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>549</v>
+        <v>665</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -7314,24 +8881,24 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>550</v>
+        <v>666</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>551</v>
+        <v>667</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>552</v>
+        <v>668</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>553</v>
+        <v>669</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="F21" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="G21" s="37" t="n">
+        <v>670</v>
+      </c>
+      <c r="F21" s="53" t="s">
+        <v>609</v>
+      </c>
+      <c r="G21" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A1",'Telecom OSP'!A:A,0))</f>
         <v>4</v>
       </c>
@@ -7339,29 +8906,29 @@
         <v>69</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>555</v>
+        <v>671</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>556</v>
+        <v>672</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>557</v>
+        <v>673</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>257</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>558</v>
+        <v>674</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G22" s="37" t="n">
+        <v>675</v>
+      </c>
+      <c r="F22" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G22" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A2",'Telecom OSP'!A:A,0))</f>
         <v>5</v>
       </c>
@@ -7369,29 +8936,29 @@
         <v>69</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>560</v>
+        <v>676</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>561</v>
+        <v>677</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>562</v>
+        <v>678</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>563</v>
+        <v>679</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>564</v>
+        <v>680</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G23" s="37" t="n">
+        <v>681</v>
+      </c>
+      <c r="F23" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G23" s="36" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
         <v>2499</v>
       </c>
@@ -7399,29 +8966,29 @@
         <v>61</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>566</v>
+        <v>682</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>567</v>
+        <v>683</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>568</v>
+        <v>684</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>569</v>
+        <v>685</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>564</v>
+        <v>680</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="F24" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G24" s="37" t="n">
+        <v>686</v>
+      </c>
+      <c r="F24" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G24" s="36" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
         <v>598</v>
       </c>
@@ -7429,29 +8996,29 @@
         <v>61</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>571</v>
+        <v>687</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>572</v>
+        <v>688</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>573</v>
+        <v>689</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>574</v>
+        <v>690</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>575</v>
+        <v>691</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>576</v>
+        <v>692</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G25" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G25" s="36" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
         <v>2499</v>
       </c>
@@ -7459,29 +9026,29 @@
         <v>61</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>577</v>
+        <v>693</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>578</v>
+        <v>694</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>579</v>
+        <v>695</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>580</v>
+        <v>696</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>575</v>
+        <v>691</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>581</v>
+        <v>697</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>479</v>
-      </c>
-      <c r="G26" s="37" t="n">
+        <v>595</v>
+      </c>
+      <c r="G26" s="36" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
         <v>598</v>
       </c>
@@ -7489,57 +9056,57 @@
         <v>61</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>582</v>
+        <v>698</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>583</v>
+        <v>699</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>584</v>
+        <v>700</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>585</v>
+        <v>701</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>586</v>
+        <v>702</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="F27" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G27" s="37" t="n">
+        <v>703</v>
+      </c>
+      <c r="F27" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G27" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("D1",'Telecom OSP'!A:A,0))</f>
-        <v>1600</v>
+        <v>1425</v>
       </c>
       <c r="H27" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>588</v>
+        <v>704</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>589</v>
+        <v>705</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>590</v>
+        <v>706</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>591</v>
+        <v>707</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>592</v>
+        <v>708</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>593</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>524</v>
+        <v>709</v>
+      </c>
+      <c r="F28" s="54" t="s">
+        <v>640</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>1</v>
@@ -7548,29 +9115,29 @@
         <v>77</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>594</v>
+        <v>710</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>595</v>
+        <v>711</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>596</v>
+        <v>712</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>597</v>
+        <v>713</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>598</v>
+        <v>714</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G29" s="37" t="n">
+        <v>715</v>
+      </c>
+      <c r="F29" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G29" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C1",'Telecom OSP'!A:A,0))</f>
         <v>1407</v>
       </c>
@@ -7578,29 +9145,29 @@
         <v>61</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>600</v>
+        <v>716</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>601</v>
+        <v>717</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>602</v>
+        <v>718</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>603</v>
+        <v>719</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>604</v>
+        <v>720</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="F30" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G30" s="37" t="n">
+        <v>721</v>
+      </c>
+      <c r="F30" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G30" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C7",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C8",'Telecom OSP'!A:A,0))</f>
         <v>42</v>
       </c>
@@ -7608,29 +9175,29 @@
         <v>69</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>606</v>
+        <v>722</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>607</v>
+        <v>723</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>608</v>
+        <v>724</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>609</v>
+        <v>725</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>610</v>
+        <v>726</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>611</v>
-      </c>
-      <c r="F31" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G31" s="37" t="n">
+        <v>727</v>
+      </c>
+      <c r="F31" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G31" s="36" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C10",'Telecom OSP'!A:A,0))</f>
         <v>10</v>
       </c>
@@ -7638,27 +9205,27 @@
         <v>69</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>612</v>
+        <v>728</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>613</v>
+        <v>729</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>614</v>
+        <v>730</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>615</v>
+        <v>731</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>616</v>
+        <v>732</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>617</v>
-      </c>
-      <c r="F32" s="39" t="s">
-        <v>524</v>
+        <v>733</v>
+      </c>
+      <c r="F32" s="54" t="s">
+        <v>640</v>
       </c>
       <c r="G32" s="21" t="n">
         <v>1</v>
@@ -7667,12 +9234,12 @@
         <v>77</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>618</v>
+        <v>734</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>619</v>
+        <v>735</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -7685,22 +9252,22 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>620</v>
+        <v>736</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>621</v>
+        <v>737</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>622</v>
+        <v>738</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>623</v>
+        <v>739</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>624</v>
-      </c>
-      <c r="F34" s="39" t="s">
-        <v>524</v>
+        <v>740</v>
+      </c>
+      <c r="F34" s="54" t="s">
+        <v>640</v>
       </c>
       <c r="G34" s="21" t="n">
         <v>3</v>
@@ -7709,29 +9276,29 @@
         <v>69</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>625</v>
+        <v>741</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="21" t="s">
-        <v>626</v>
+        <v>742</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>627</v>
+        <v>743</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>628</v>
+        <v>744</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>623</v>
+        <v>739</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>629</v>
-      </c>
-      <c r="F35" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G35" s="37" t="n">
+        <v>745</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G35" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B5",Security!A:A,0))</f>
         <v>1</v>
       </c>
@@ -7739,29 +9306,29 @@
         <v>69</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>630</v>
+        <v>746</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="21" t="s">
-        <v>631</v>
+        <v>747</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>632</v>
+        <v>748</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>633</v>
+        <v>749</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>634</v>
+        <v>750</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>635</v>
-      </c>
-      <c r="F36" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G36" s="37" t="n">
+        <v>751</v>
+      </c>
+      <c r="F36" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G36" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A1",Security!A:A,0))</f>
         <v>2</v>
       </c>
@@ -7769,29 +9336,29 @@
         <v>69</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>636</v>
+        <v>752</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="21" t="s">
-        <v>637</v>
+        <v>753</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>638</v>
+        <v>754</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>639</v>
+        <v>755</v>
       </c>
       <c r="D37" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="F37" s="54" t="s">
         <v>640</v>
       </c>
-      <c r="E37" s="7" t="s">
-        <v>641</v>
-      </c>
-      <c r="F37" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G37" s="37" t="n">
+      <c r="G37" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A3",Security!A:A,0))+INDEX(Security!G:G,MATCH("A4",Security!A:A,0))</f>
         <v>2</v>
       </c>
@@ -7799,29 +9366,29 @@
         <v>69</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>642</v>
+        <v>758</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="21" t="s">
-        <v>643</v>
+        <v>759</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>644</v>
+        <v>760</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>645</v>
+        <v>761</v>
       </c>
       <c r="D38" s="7" t="s">
-        <v>646</v>
+        <v>762</v>
       </c>
       <c r="E38" s="7" t="s">
-        <v>647</v>
-      </c>
-      <c r="F38" s="38" t="s">
-        <v>493</v>
-      </c>
-      <c r="G38" s="37" t="n">
+        <v>763</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>609</v>
+      </c>
+      <c r="G38" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B1",Security!A:A,0))+INDEX(Security!G:G,MATCH("B2",Security!A:A,0))</f>
         <v>2</v>
       </c>
@@ -7829,29 +9396,29 @@
         <v>69</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>648</v>
+        <v>764</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>649</v>
+        <v>765</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>650</v>
+        <v>766</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>651</v>
+        <v>767</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>652</v>
+        <v>768</v>
       </c>
       <c r="E39" s="7" t="s">
-        <v>653</v>
-      </c>
-      <c r="F39" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G39" s="37" t="n">
+        <v>769</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G39" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A7",Security!A:A,0))</f>
         <v>3</v>
       </c>
@@ -7859,29 +9426,29 @@
         <v>69</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>654</v>
+        <v>770</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>655</v>
+        <v>771</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>656</v>
+        <v>772</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>657</v>
+        <v>773</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>658</v>
+        <v>774</v>
       </c>
       <c r="E40" s="7" t="s">
-        <v>659</v>
-      </c>
-      <c r="F40" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G40" s="37" t="n">
+        <v>775</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G40" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A6",Security!A:A,0))</f>
         <v>3</v>
       </c>
@@ -7889,61 +9456,61 @@
         <v>69</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>660</v>
+        <v>776</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>661</v>
+        <v>777</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>662</v>
+        <v>778</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>663</v>
+        <v>779</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>664</v>
+        <v>780</v>
       </c>
       <c r="E41" s="7" t="s">
-        <v>665</v>
-      </c>
-      <c r="F41" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G41" s="37" t="n">
+        <v>781</v>
+      </c>
+      <c r="F41" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G41" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("C2",Security!A:A,0))</f>
-        <v>1400</v>
+        <v>1209</v>
       </c>
       <c r="H41" s="21" t="s">
         <v>61</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>666</v>
+        <v>782</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="21" t="s">
-        <v>667</v>
+        <v>783</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>668</v>
+        <v>784</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>669</v>
+        <v>785</v>
       </c>
       <c r="D42" s="7" t="s">
-        <v>670</v>
+        <v>786</v>
       </c>
       <c r="E42" s="7" t="s">
-        <v>671</v>
-      </c>
-      <c r="F42" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G42" s="37" t="n">
+        <v>787</v>
+      </c>
+      <c r="F42" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G42" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("C1",Security!A:A,0))</f>
-        <v>1800</v>
+        <v>1993</v>
       </c>
       <c r="H42" s="21" t="s">
         <v>61</v>
@@ -7952,24 +9519,24 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="21" t="s">
-        <v>672</v>
+        <v>788</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>673</v>
+        <v>789</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>674</v>
+        <v>790</v>
       </c>
       <c r="D43" s="7" t="s">
-        <v>675</v>
+        <v>791</v>
       </c>
       <c r="E43" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="F43" s="39" t="s">
-        <v>524</v>
-      </c>
-      <c r="G43" s="37" t="n">
+        <v>792</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G43" s="36" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B3",Security!A:A,0))</f>
         <v>1</v>
       </c>
@@ -7977,7 +9544,37 @@
         <v>69</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>677</v>
+        <v>793</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>794</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>640</v>
+      </c>
+      <c r="G44" s="36" t="n">
+        <f aca="false">INDEX(Security!G:G,MATCH("C5",Security!A:A,0))</f>
+        <v>1209</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>799</v>
       </c>
     </row>
   </sheetData>
@@ -7991,7 +9588,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -8005,404 +9602,404 @@
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="40" t="s">
-        <v>678</v>
+      <c r="B2" s="55" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="41" t="s">
-        <v>679</v>
-      </c>
-      <c r="C4" s="42"/>
+      <c r="B4" s="56" t="s">
+        <v>801</v>
+      </c>
+      <c r="C4" s="57"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="43" t="s">
-        <v>680</v>
+      <c r="B5" s="58" t="s">
+        <v>802</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>681</v>
+        <v>803</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="43" t="s">
-        <v>682</v>
+      <c r="B6" s="58" t="s">
+        <v>804</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>683</v>
+        <v>805</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="43" t="s">
-        <v>684</v>
+      <c r="B7" s="58" t="s">
+        <v>806</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>685</v>
+        <v>807</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="41" t="s">
-        <v>686</v>
-      </c>
-      <c r="C9" s="42"/>
+      <c r="B9" s="56" t="s">
+        <v>808</v>
+      </c>
+      <c r="C9" s="57"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="43" t="s">
+      <c r="B10" s="58" t="s">
         <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>687</v>
+        <v>809</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="43" t="s">
+      <c r="B11" s="58" t="s">
         <v>277</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>688</v>
+        <v>810</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="43" t="s">
+      <c r="B12" s="58" t="s">
         <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>689</v>
+        <v>811</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="58" t="s">
         <v>149</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>690</v>
+        <v>812</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="43" t="s">
-        <v>691</v>
+      <c r="B14" s="58" t="s">
+        <v>813</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>692</v>
+        <v>814</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="43" t="s">
-        <v>693</v>
+      <c r="B15" s="58" t="s">
+        <v>815</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>694</v>
+        <v>816</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="41" t="s">
-        <v>695</v>
-      </c>
-      <c r="C17" s="42"/>
+      <c r="B17" s="56" t="s">
+        <v>817</v>
+      </c>
+      <c r="C17" s="57"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="43" t="s">
-        <v>696</v>
+      <c r="B18" s="58" t="s">
+        <v>818</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>697</v>
+        <v>819</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="43" t="s">
-        <v>698</v>
+      <c r="B19" s="58" t="s">
+        <v>820</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>699</v>
+        <v>821</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="43" t="s">
-        <v>700</v>
+      <c r="B20" s="58" t="s">
+        <v>822</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>701</v>
+        <v>823</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="43" t="s">
-        <v>702</v>
+      <c r="B21" s="58" t="s">
+        <v>824</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>703</v>
+        <v>825</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="43" t="s">
-        <v>704</v>
+      <c r="B22" s="58" t="s">
+        <v>826</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>705</v>
+        <v>827</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="43" t="s">
-        <v>706</v>
+      <c r="B23" s="58" t="s">
+        <v>828</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>707</v>
+        <v>829</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="43" t="s">
-        <v>708</v>
+      <c r="B24" s="58" t="s">
+        <v>830</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>709</v>
+        <v>831</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="43" t="s">
-        <v>710</v>
+      <c r="B25" s="58" t="s">
+        <v>832</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>711</v>
+        <v>833</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="43" t="s">
-        <v>712</v>
+      <c r="B26" s="58" t="s">
+        <v>834</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>713</v>
+        <v>835</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="43" t="s">
-        <v>714</v>
+      <c r="B27" s="58" t="s">
+        <v>836</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>715</v>
+        <v>837</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="43" t="s">
-        <v>716</v>
+      <c r="B28" s="58" t="s">
+        <v>838</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>717</v>
+        <v>839</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="41" t="s">
-        <v>718</v>
-      </c>
-      <c r="C30" s="42"/>
+      <c r="B30" s="56" t="s">
+        <v>840</v>
+      </c>
+      <c r="C30" s="57"/>
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="43" t="s">
-        <v>719</v>
+      <c r="B31" s="58" t="s">
+        <v>841</v>
       </c>
       <c r="C31" s="8" t="s">
-        <v>720</v>
+        <v>842</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="43" t="s">
-        <v>721</v>
+      <c r="B32" s="58" t="s">
+        <v>843</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>722</v>
+        <v>844</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="43" t="s">
-        <v>723</v>
+      <c r="B33" s="58" t="s">
+        <v>845</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>724</v>
+        <v>846</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="43" t="s">
-        <v>725</v>
+      <c r="B34" s="58" t="s">
+        <v>847</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>726</v>
+        <v>848</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="43" t="s">
-        <v>727</v>
+      <c r="B35" s="58" t="s">
+        <v>849</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>728</v>
+        <v>850</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="43" t="s">
-        <v>729</v>
+      <c r="B36" s="58" t="s">
+        <v>851</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>730</v>
+        <v>852</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="43" t="s">
-        <v>731</v>
+      <c r="B37" s="58" t="s">
+        <v>853</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>732</v>
+        <v>854</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="43" t="s">
-        <v>733</v>
+      <c r="B38" s="58" t="s">
+        <v>855</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>734</v>
+        <v>856</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="41" t="s">
-        <v>735</v>
-      </c>
-      <c r="C40" s="42"/>
+      <c r="B40" s="56" t="s">
+        <v>857</v>
+      </c>
+      <c r="C40" s="57"/>
     </row>
     <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="43" t="s">
-        <v>736</v>
+      <c r="B41" s="58" t="s">
+        <v>858</v>
       </c>
       <c r="C41" s="8" t="s">
-        <v>737</v>
+        <v>859</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="43" t="s">
-        <v>738</v>
+      <c r="B42" s="58" t="s">
+        <v>860</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>739</v>
+        <v>861</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="43" t="s">
-        <v>740</v>
+      <c r="B43" s="58" t="s">
+        <v>862</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>741</v>
+        <v>863</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="43" t="s">
-        <v>742</v>
+      <c r="B44" s="58" t="s">
+        <v>864</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>743</v>
+        <v>865</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="43" t="s">
-        <v>744</v>
+      <c r="B45" s="58" t="s">
+        <v>866</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>745</v>
+        <v>867</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="43" t="s">
-        <v>746</v>
+      <c r="B46" s="58" t="s">
+        <v>868</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>747</v>
+        <v>869</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="43" t="s">
-        <v>748</v>
+      <c r="B47" s="58" t="s">
+        <v>870</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>749</v>
+        <v>871</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="43" t="s">
-        <v>750</v>
+      <c r="B48" s="58" t="s">
+        <v>872</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>751</v>
+        <v>873</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="43" t="s">
-        <v>752</v>
+      <c r="B49" s="58" t="s">
+        <v>874</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>753</v>
+        <v>875</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="43" t="s">
-        <v>754</v>
+      <c r="B50" s="58" t="s">
+        <v>876</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>755</v>
+        <v>877</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="43" t="s">
-        <v>756</v>
+      <c r="B51" s="58" t="s">
+        <v>878</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>757</v>
+        <v>879</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="43" t="s">
-        <v>758</v>
+      <c r="B52" s="58" t="s">
+        <v>880</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>759</v>
+        <v>881</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="43" t="s">
-        <v>760</v>
+      <c r="B53" s="58" t="s">
+        <v>882</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>761</v>
+        <v>883</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="43" t="s">
-        <v>762</v>
+      <c r="B54" s="58" t="s">
+        <v>884</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>763</v>
+        <v>885</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="41" t="s">
-        <v>764</v>
-      </c>
-      <c r="C56" s="42"/>
+      <c r="B56" s="56" t="s">
+        <v>886</v>
+      </c>
+      <c r="C56" s="57"/>
     </row>
     <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="43" t="s">
-        <v>765</v>
+      <c r="B57" s="58" t="s">
+        <v>887</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>766</v>
+        <v>888</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="43" t="s">
-        <v>767</v>
+      <c r="B58" s="58" t="s">
+        <v>889</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>768</v>
+        <v>890</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="43" t="s">
-        <v>769</v>
+      <c r="B59" s="58" t="s">
+        <v>891</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>770</v>
+        <v>892</v>
       </c>
     </row>
   </sheetData>

--- a/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
+++ b/DOE_GJ_Site_Improvement_Exterior_Elec_Comm_Takeoff.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1337" uniqueCount="893">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="962">
   <si>
     <t xml:space="preserve">DETAILED QUANTITY TAKEOFF — EXTERIOR ELECTRICAL &amp; COMMUNICATIONS</t>
   </si>
@@ -757,6 +757,99 @@
     <t xml:space="preserve">Subtotal D</t>
   </si>
   <si>
+    <t xml:space="preserve">E. SITE CONCRETE &amp; REBAR — FOUNDATION VOLUME ROLL-UP (CY figured from counted bases)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete — light pole bases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2'-0" dia x 9'-6" (29.85 CF ea)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi min (Div 03); volume = pi x 1.0^2 x 9.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qty = 18 bases x 1.105 CY. Round form in unpaved / square at paving (square adds ~27% — carried round).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete — bollard bases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1'-2" sq x 3'-0" deep (assumed depth)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi min (Div 03); 4.08 CF ea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base depth not dimensioned on 3/ES601 — 3'-0" assumed, verify.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete — transformer pad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per XE std (8'x8'x10" assumed)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi w/ ground grid per XE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XE standard pad drawing governs — placeholder volume.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete — security pedestal footers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18" dia x 36" (assumed; frost + 20" from curb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi; L-bolts x4 per pedestal template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A1/TSY101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Footer size per pedestal mfr template — 0.2 CY ea assumed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinforcing steel — pole &amp; bollard bases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#5 verts, #3/#4 ties</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gr 60 rebar: ~115 lb/pole base (8-#5 x 9.2' + #4 ties), ~30 lb/bollard base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18x115 + 6x30 = 2,250 lb = 1.1 ton.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Subtotal E</t>
+  </si>
+  <si>
     <t xml:space="preserve">SITE ELECTRICAL TOTAL</t>
   </si>
   <si>
@@ -952,9 +1045,6 @@
     <t xml:space="preserve">TSN100 GN 8/9</t>
   </si>
   <si>
-    <t xml:space="preserve">Calc</t>
-  </si>
-  <si>
     <t xml:space="preserve">Equals sum of all duct bank segments above.</t>
   </si>
   <si>
@@ -970,9 +1060,6 @@
     <t xml:space="preserve">A8/TSN400</t>
   </si>
   <si>
-    <t xml:space="preserve">CY</t>
-  </si>
-  <si>
     <t xml:space="preserve">Qty = DB1 LF x 2.56 SF / 27. Reinforcement may vary w/ soil conditions per structural.</t>
   </si>
   <si>
@@ -1093,6 +1180,87 @@
     <t xml:space="preserve">Most of the 3-cell fabric cells are vacant at turnover (fiber occupies 1 cell on select routes) — seal all.</t>
   </si>
   <si>
+    <t xml:space="preserve">Trench excavation — duct banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DB1 3.0'w x 3.8'd; DB2 3.1' x 4.6'; DB3 2.2' x 3.2'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine excavation, shored/sloped as reqd (encasement width + 12" working, 30" cover)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSN400; GN 8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.42 / 0.53 / 0.26 CY per LF by bank type from the section geometry stated in Size column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trench backfill &amp; compaction — duct banks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Native, compacted in lifts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavation minus concrete encasement (conduit displacement ignored)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Div 31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assumes native backfill approved; import select fill not carried.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spoils load &amp; haul-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Displaced volume: encasement concrete + structure volumes (~81 CY)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81 CY = 4 MH (19 CY ea displaced) + 6 HH (~0.9 CY ea). No swell factor applied — add per hauler.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure excavation, bedding &amp; backfill — MH &amp; HH sets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MH pit ~12'x12'x9'; HH pit ~6'x5'x4.5'; 12"/6" gravel bedding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excavate, bed, set, backfill, compact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H1,A1/TSN400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 MH x 48 CY + 6 HH x 5 CY excavation + 24 CY bedding. Crane set for 9,275-lb MH bases — rigging in unit rate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinforcing steel — duct bank encasement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4-#4 longitudinal + #3 hoops @18"</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gr 60: ~2.67 lb/LF longitudinal + ~1.53 lb/LF hoops (weighted avg perimeter)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A8,A13/TSN400</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~4.2 lb/LF x 1,407 LF = 5,900 lb = 3.0 ton. Reinforcement may increase per soil conditions (TSN400 note).</t>
+  </si>
+  <si>
     <t xml:space="preserve">D. OSP CABLING (TSN300 site one-line)</t>
   </si>
   <si>
@@ -2233,6 +2401,39 @@
     <t xml:space="preserve">Takeoff line Telecom C11.</t>
   </si>
   <si>
+    <t xml:space="preserve">CONCRETE &amp; REBAR (roll-up of all takeoff volume lines)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ready-mix concrete, 3000 psi — encasement + all foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3000 psi min; encasement + bases + pad + footers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local ready-mix supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mix per Div 03 / XE pad spec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duct bank encasement (123.6) + pole bases (19.9) + bollards (0.9) + XFMR pad (2.0) + pedestal footers (0.4). Add waste factor at pricing (~5-8%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reinforcing steel, Gr 60 — encasement + foundations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#3-#5 bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Local fabricator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per TSN400 &amp; ES601 details</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encasement (3.0 T) + base cages (1.1 T). Excludes MH/HH precast (in structure supply).</t>
+  </si>
+  <si>
     <t xml:space="preserve">SECURITY (Div 28 — models per spec; BOD offered where drawings silent)</t>
   </si>
   <si>
@@ -2546,6 +2747,12 @@
   </si>
   <si>
     <t xml:space="preserve">Assumed materials where drawings are silent: PVC Sch 40 for site branch conduits, THWN-2/XHHW-2 Cu conductors, 5/8"x8' Cu-clad ground rods, NEMA 3R/4 exterior enclosures, LC fiber terminations, 1,250-lb mule tape. All flagged '(assumed)' in the Type column.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A3.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concrete &amp; earthwork geometry: trench sections = encasement width + 12" working room x (30" cover + bank height), giving 0.42/0.53/0.26 CY per LF for DB1/DB2/DB3; backfill = excavation minus encasement (native, compacted); spoils = displaced volume with NO swell factor; MH pits 12'x12'x9' w/ 12" bedding, HH pits 6'x5'x4.5' w/ 6" bedding; bollard base depth 3'-0" and pedestal footers 18" dia x 36" assumed (not dimensioned). All volumes are live formulas from the counted/measured quantities.</t>
   </si>
   <si>
     <t xml:space="preserve">4. EXCLUSIONS</t>
@@ -3082,6 +3289,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -3100,10 +3311,6 @@
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -3503,7 +3710,7 @@
         <v>10</v>
       </c>
       <c r="D9" s="9" t="n">
-        <f aca="false">'Site Electrical'!J46</f>
+        <f aca="false">'Site Electrical'!J53</f>
         <v>0</v>
       </c>
       <c r="E9" s="8" t="s">
@@ -3518,7 +3725,7 @@
         <v>13</v>
       </c>
       <c r="D10" s="9" t="n">
-        <f aca="false">'Telecom OSP'!J45</f>
+        <f aca="false">'Telecom OSP'!J50</f>
         <v>0</v>
       </c>
       <c r="E10" s="8" t="s">
@@ -3726,7 +3933,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K46"/>
+  <dimension ref="A1:K53"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -5007,23 +5214,230 @@
       </c>
       <c r="K44" s="28"/>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11"/>
-      <c r="B46" s="10" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="12" t="n">
-        <f aca="false">J16+J24+J38+J44</f>
+      <c r="B45" s="20"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="20"/>
+      <c r="E45" s="20"/>
+      <c r="F45" s="20"/>
+      <c r="G45" s="20"/>
+      <c r="H45" s="20"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+    </row>
+    <row r="46" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
+        <v>244</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G46" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("C4",A:A,0))*29.85/27,1)</f>
+        <v>19.9</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I46" s="23"/>
+      <c r="J46" s="24" t="str">
+        <f aca="false">IF(I46="","",G46*I46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="8" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>252</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G47" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("C7",A:A,0))*4.08/27,1)</f>
+        <v>0.9</v>
+      </c>
+      <c r="H47" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I47" s="23"/>
+      <c r="J47" s="24" t="str">
+        <f aca="false">IF(I47="","",G47*I47)</f>
+        <v/>
+      </c>
+      <c r="K47" s="27" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="s">
+        <v>256</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>257</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="F48" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G48" s="22" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I48" s="23"/>
+      <c r="J48" s="24" t="str">
+        <f aca="false">IF(I48="","",G48*I48)</f>
+        <v/>
+      </c>
+      <c r="K48" s="27" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="s">
+        <v>261</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>262</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>264</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>265</v>
+      </c>
+      <c r="F49" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G49" s="31" t="n">
+        <f aca="false">ROUND(INDEX(Security!G:G,MATCH("A1",Security!A:A,0))*5.3/27,1)</f>
+        <v>0.4</v>
+      </c>
+      <c r="H49" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I49" s="23"/>
+      <c r="J49" s="24" t="str">
+        <f aca="false">IF(I49="","",G49*I49)</f>
+        <v/>
+      </c>
+      <c r="K49" s="27" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
+        <v>267</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="F50" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G50" s="31" t="n">
+        <f aca="false">ROUND((INDEX(G:G,MATCH("C4",A:A,0))*115+INDEX(G:G,MATCH("C7",A:A,0))*30)/2000,1)</f>
+        <v>1.1</v>
+      </c>
+      <c r="H50" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="I50" s="23"/>
+      <c r="J50" s="24" t="str">
+        <f aca="false">IF(I50="","",G50*I50)</f>
+        <v/>
+      </c>
+      <c r="K50" s="8" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="28"/>
+      <c r="B51" s="29" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="28"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="30" t="n">
+        <f aca="false">SUM(J46:J50)</f>
         <v>0</v>
       </c>
-      <c r="K46" s="11"/>
+      <c r="K51" s="28"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="11"/>
+      <c r="B53" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="11"/>
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="12" t="n">
+        <f aca="false">J16+J24+J38+J44+J51</f>
+        <v>0</v>
+      </c>
+      <c r="K53" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -5041,7 +5455,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -5059,7 +5473,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5104,7 +5518,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>245</v>
+        <v>276</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -5122,16 +5536,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>246</v>
+        <v>277</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>248</v>
+        <v>279</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>249</v>
+        <v>280</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>76</v>
@@ -5148,7 +5562,7 @@
         <v/>
       </c>
       <c r="K6" s="8" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5156,16 +5570,16 @@
         <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>76</v>
@@ -5182,7 +5596,7 @@
         <v/>
       </c>
       <c r="K7" s="8" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5190,16 +5604,16 @@
         <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>76</v>
@@ -5216,7 +5630,7 @@
         <v/>
       </c>
       <c r="K8" s="27" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5239,7 +5653,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="19" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -5257,16 +5671,16 @@
         <v>117</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>60</v>
@@ -5283,7 +5697,7 @@
         <v/>
       </c>
       <c r="K11" s="8" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5291,16 +5705,16 @@
         <v>123</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>60</v>
@@ -5317,7 +5731,7 @@
         <v/>
       </c>
       <c r="K12" s="8" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5325,16 +5739,16 @@
         <v>128</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>60</v>
@@ -5351,7 +5765,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5359,16 +5773,16 @@
         <v>133</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E14" s="21" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
       <c r="F14" s="21" t="s">
         <v>60</v>
@@ -5385,7 +5799,7 @@
         <v/>
       </c>
       <c r="K14" s="8" t="s">
-        <v>275</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5393,21 +5807,21 @@
         <v>139</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>276</v>
+        <v>307</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="G15" s="31" t="n">
+        <v>308</v>
+      </c>
+      <c r="G15" s="32" t="n">
         <v>123.1</v>
       </c>
       <c r="H15" s="21" t="s">
@@ -5419,7 +5833,7 @@
         <v/>
       </c>
       <c r="K15" s="8" t="s">
-        <v>278</v>
+        <v>309</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5427,21 +5841,21 @@
         <v>144</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>279</v>
+        <v>310</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>280</v>
+        <v>311</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="G16" s="31" t="n">
+        <v>308</v>
+      </c>
+      <c r="G16" s="32" t="n">
         <v>13.7</v>
       </c>
       <c r="H16" s="21" t="s">
@@ -5453,25 +5867,25 @@
         <v/>
       </c>
       <c r="K16" s="8" t="s">
-        <v>281</v>
+        <v>312</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="32" t="s">
-        <v>282</v>
+      <c r="A17" s="33" t="s">
+        <v>313</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>283</v>
+        <v>314</v>
       </c>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
       <c r="E17" s="28"/>
       <c r="F17" s="28"/>
-      <c r="G17" s="33" t="n">
+      <c r="G17" s="34" t="n">
         <f aca="false">SUM(G11:G16)</f>
         <v>966.8</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="35" t="s">
         <v>61</v>
       </c>
       <c r="I17" s="28"/>
@@ -5480,19 +5894,19 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>60</v>
@@ -5509,29 +5923,29 @@
         <v/>
       </c>
       <c r="K18" s="8" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>288</v>
+        <v>319</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>286</v>
+        <v>317</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="G19" s="31" t="n">
+        <v>308</v>
+      </c>
+      <c r="G19" s="32" t="n">
         <v>21.4</v>
       </c>
       <c r="H19" s="21" t="s">
@@ -5543,25 +5957,25 @@
         <v/>
       </c>
       <c r="K19" s="8" t="s">
-        <v>289</v>
+        <v>320</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="32" t="s">
-        <v>290</v>
+      <c r="A20" s="33" t="s">
+        <v>321</v>
       </c>
       <c r="B20" s="29" t="s">
-        <v>291</v>
+        <v>322</v>
       </c>
       <c r="C20" s="28"/>
       <c r="D20" s="28"/>
       <c r="E20" s="28"/>
       <c r="F20" s="28"/>
-      <c r="G20" s="33" t="n">
+      <c r="G20" s="34" t="n">
         <f aca="false">SUM(G18:G19)</f>
         <v>141.4</v>
       </c>
-      <c r="H20" s="34" t="s">
+      <c r="H20" s="35" t="s">
         <v>61</v>
       </c>
       <c r="I20" s="28"/>
@@ -5570,24 +5984,24 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>293</v>
+        <v>324</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="G21" s="31" t="n">
+        <v>308</v>
+      </c>
+      <c r="G21" s="32" t="n">
         <v>101.5</v>
       </c>
       <c r="H21" s="21" t="s">
@@ -5599,29 +6013,29 @@
         <v/>
       </c>
       <c r="K21" s="27" t="s">
-        <v>296</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>298</v>
+        <v>329</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>294</v>
+        <v>325</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>277</v>
-      </c>
-      <c r="G22" s="31" t="n">
+        <v>308</v>
+      </c>
+      <c r="G22" s="32" t="n">
         <v>197.3</v>
       </c>
       <c r="H22" s="21" t="s">
@@ -5633,25 +6047,25 @@
         <v/>
       </c>
       <c r="K22" s="27" t="s">
-        <v>299</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="32" t="s">
-        <v>300</v>
+      <c r="A23" s="33" t="s">
+        <v>331</v>
       </c>
       <c r="B23" s="29" t="s">
-        <v>301</v>
+        <v>332</v>
       </c>
       <c r="C23" s="28"/>
       <c r="D23" s="28"/>
       <c r="E23" s="28"/>
       <c r="F23" s="28"/>
-      <c r="G23" s="33" t="n">
+      <c r="G23" s="34" t="n">
         <f aca="false">SUM(G21:G22)</f>
         <v>298.8</v>
       </c>
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="35" t="s">
         <v>61</v>
       </c>
       <c r="I23" s="28"/>
@@ -5661,7 +6075,7 @@
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="28"/>
       <c r="B24" s="29" t="s">
-        <v>302</v>
+        <v>333</v>
       </c>
       <c r="C24" s="28"/>
       <c r="D24" s="28"/>
@@ -5678,7 +6092,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>303</v>
+        <v>334</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -5696,19 +6110,19 @@
         <v>153</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>305</v>
+        <v>336</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>306</v>
+        <v>337</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>307</v>
+        <v>338</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>308</v>
+        <v>248</v>
       </c>
       <c r="G26" s="25" t="n">
         <f aca="false">SUM(G11:G16)+SUM(G18:G19)+SUM(G21:G22)</f>
@@ -5718,12 +6132,12 @@
         <v>61</v>
       </c>
       <c r="I26" s="23"/>
-      <c r="J26" s="35" t="str">
+      <c r="J26" s="36" t="str">
         <f aca="false">IF(I26="","",G26*I26)</f>
         <v/>
       </c>
       <c r="K26" s="8" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5731,34 +6145,34 @@
         <v>159</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>310</v>
+        <v>340</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>311</v>
+        <v>341</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>313</v>
+        <v>343</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G27" s="31" t="n">
+        <v>248</v>
+      </c>
+      <c r="G27" s="32" t="n">
         <f aca="false">ROUND(SUM(G11:G16)*2.56/27,1)</f>
         <v>91.7</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="I27" s="23"/>
-      <c r="J27" s="35" t="str">
+      <c r="J27" s="36" t="str">
         <f aca="false">IF(I27="","",G27*I27)</f>
         <v/>
       </c>
       <c r="K27" s="8" t="s">
-        <v>315</v>
+        <v>344</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5766,34 +6180,34 @@
         <v>163</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>316</v>
+        <v>345</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>317</v>
+        <v>346</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>312</v>
+        <v>342</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>318</v>
+        <v>347</v>
       </c>
       <c r="F28" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G28" s="31" t="n">
+        <v>248</v>
+      </c>
+      <c r="G28" s="32" t="n">
         <f aca="false">ROUND(SUM(G18:G19)*4.34/27,1)</f>
         <v>22.7</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="I28" s="23"/>
-      <c r="J28" s="35" t="str">
+      <c r="J28" s="36" t="str">
         <f aca="false">IF(I28="","",G28*I28)</f>
         <v/>
       </c>
       <c r="K28" s="8" t="s">
-        <v>319</v>
+        <v>348</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5801,34 +6215,34 @@
         <v>167</v>
       </c>
       <c r="B29" s="26" t="s">
-        <v>320</v>
+        <v>349</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>321</v>
+        <v>350</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>323</v>
+        <v>352</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G29" s="31" t="n">
+        <v>248</v>
+      </c>
+      <c r="G29" s="32" t="n">
         <f aca="false">ROUND(SUM(G21:G22)*0.83/27,1)</f>
         <v>9.2</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>314</v>
+        <v>249</v>
       </c>
       <c r="I29" s="23"/>
-      <c r="J29" s="35" t="str">
+      <c r="J29" s="36" t="str">
         <f aca="false">IF(I29="","",G29*I29)</f>
         <v/>
       </c>
       <c r="K29" s="27" t="s">
-        <v>324</v>
+        <v>353</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5836,16 +6250,16 @@
         <v>173</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>325</v>
+        <v>354</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>326</v>
+        <v>355</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>327</v>
+        <v>356</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>328</v>
+        <v>357</v>
       </c>
       <c r="F30" s="21" t="s">
         <v>149</v>
@@ -5868,16 +6282,16 @@
         <v>179</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>329</v>
+        <v>358</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>330</v>
+        <v>359</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>149</v>
@@ -5900,16 +6314,16 @@
         <v>184</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>332</v>
+        <v>361</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>335</v>
+        <v>364</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>76</v>
@@ -5926,7 +6340,7 @@
         <v/>
       </c>
       <c r="K32" s="8" t="s">
-        <v>336</v>
+        <v>365</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5934,16 +6348,16 @@
         <v>190</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>337</v>
+        <v>366</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="D33" s="7" t="s">
-        <v>339</v>
+        <v>368</v>
       </c>
       <c r="E33" s="21" t="s">
-        <v>340</v>
+        <v>369</v>
       </c>
       <c r="F33" s="21" t="s">
         <v>76</v>
@@ -5960,7 +6374,7 @@
         <v/>
       </c>
       <c r="K33" s="8" t="s">
-        <v>341</v>
+        <v>370</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5968,16 +6382,16 @@
         <v>195</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>342</v>
+        <v>371</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>343</v>
+        <v>372</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>345</v>
+        <v>374</v>
       </c>
       <c r="F34" s="21" t="s">
         <v>76</v>
@@ -5994,7 +6408,7 @@
         <v/>
       </c>
       <c r="K34" s="8" t="s">
-        <v>346</v>
+        <v>375</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6002,16 +6416,16 @@
         <v>201</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>347</v>
+        <v>376</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>333</v>
+        <v>362</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>348</v>
+        <v>377</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="F35" s="21" t="s">
         <v>149</v>
@@ -6028,7 +6442,7 @@
         <v/>
       </c>
       <c r="K35" s="27" t="s">
-        <v>350</v>
+        <v>379</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6036,16 +6450,16 @@
         <v>207</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>351</v>
+        <v>380</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>352</v>
+        <v>381</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>353</v>
+        <v>382</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>331</v>
+        <v>360</v>
       </c>
       <c r="F36" s="21" t="s">
         <v>149</v>
@@ -6062,67 +6476,104 @@
         <v/>
       </c>
       <c r="K36" s="8" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="28"/>
-      <c r="B37" s="29" t="s">
-        <v>218</v>
-      </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="30" t="n">
-        <f aca="false">SUM(J26:J36)</f>
-        <v>0</v>
-      </c>
-      <c r="K37" s="28"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="B38" s="20"/>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
+        <v>383</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>385</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G37" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("B7",A:A,0))*0.42+INDEX(G:G,MATCH("B10",A:A,0))*0.53+INDEX(G:G,MATCH("B13",A:A,0))*0.26,0)</f>
+        <v>559</v>
+      </c>
+      <c r="H37" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I37" s="23"/>
+      <c r="J37" s="24" t="str">
+        <f aca="false">IF(I37="","",G37*I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="27" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>390</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>391</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>392</v>
+      </c>
+      <c r="E38" s="21" t="s">
+        <v>393</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G38" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("C12",A:A,0))-INDEX(G:G,MATCH("C2",A:A,0))-INDEX(G:G,MATCH("C3",A:A,0))-INDEX(G:G,MATCH("C4",A:A,0)),0)</f>
+        <v>435</v>
+      </c>
+      <c r="H38" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I38" s="23"/>
+      <c r="J38" s="24" t="str">
+        <f aca="false">IF(I38="","",G38*I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="27" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="21" t="s">
-        <v>220</v>
+        <v>395</v>
       </c>
       <c r="B39" s="26" t="s">
-        <v>356</v>
+        <v>396</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>357</v>
+        <v>65</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>358</v>
+        <v>397</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>359</v>
+        <v>65</v>
       </c>
       <c r="F39" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G39" s="36" t="n">
-        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-FIBER",'Cable Schedule'!A:A,0))</f>
-        <v>1425</v>
+        <v>248</v>
+      </c>
+      <c r="G39" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("C2",A:A,0))+INDEX(G:G,MATCH("C3",A:A,0))+INDEX(G:G,MATCH("C4",A:A,0))+81,0)</f>
+        <v>205</v>
       </c>
       <c r="H39" s="21" t="s">
-        <v>61</v>
+        <v>249</v>
       </c>
       <c r="I39" s="23"/>
       <c r="J39" s="24" t="str">
@@ -6130,144 +6581,281 @@
         <v/>
       </c>
       <c r="K39" s="27" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>361</v>
+        <v>399</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>400</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>362</v>
+        <v>401</v>
       </c>
       <c r="D40" s="7" t="s">
-        <v>363</v>
+        <v>402</v>
       </c>
       <c r="E40" s="21" t="s">
-        <v>364</v>
+        <v>403</v>
       </c>
       <c r="F40" s="21" t="s">
         <v>149</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>1</v>
+        <v>246</v>
       </c>
       <c r="H40" s="21" t="s">
-        <v>77</v>
+        <v>249</v>
       </c>
       <c r="I40" s="23"/>
       <c r="J40" s="24" t="str">
         <f aca="false">IF(I40="","",G40*I40)</f>
         <v/>
       </c>
-      <c r="K40" s="8" t="s">
-        <v>365</v>
+      <c r="K40" s="27" t="s">
+        <v>404</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="21" t="s">
-        <v>231</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>366</v>
+        <v>405</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>406</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>367</v>
+        <v>407</v>
       </c>
       <c r="D41" s="7" t="s">
-        <v>368</v>
+        <v>408</v>
       </c>
       <c r="E41" s="21" t="s">
-        <v>369</v>
+        <v>409</v>
       </c>
       <c r="F41" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="G41" s="22" t="n">
-        <v>1</v>
+        <v>248</v>
+      </c>
+      <c r="G41" s="31" t="n">
+        <f aca="false">ROUND(INDEX(G:G,MATCH("C1",A:A,0))*4.2/2000,1)</f>
+        <v>3</v>
       </c>
       <c r="H41" s="21" t="s">
-        <v>77</v>
+        <v>271</v>
       </c>
       <c r="I41" s="23"/>
       <c r="J41" s="24" t="str">
         <f aca="false">IF(I41="","",G41*I41)</f>
         <v/>
       </c>
-      <c r="K41" s="27" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
+      <c r="K41" s="8" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="28"/>
+      <c r="B42" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="C42" s="28"/>
+      <c r="D42" s="28"/>
+      <c r="E42" s="28"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="28"/>
+      <c r="H42" s="28"/>
+      <c r="I42" s="28"/>
+      <c r="J42" s="30" t="n">
+        <f aca="false">SUM(J26:J41)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="28"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+    </row>
+    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>220</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>412</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>413</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="E44" s="21" t="s">
+        <v>415</v>
+      </c>
+      <c r="F44" s="21" t="s">
+        <v>248</v>
+      </c>
+      <c r="G44" s="31" t="n">
+        <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-FIBER",'Cable Schedule'!A:A,0))</f>
+        <v>1425</v>
+      </c>
+      <c r="H44" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="I44" s="23"/>
+      <c r="J44" s="24" t="str">
+        <f aca="false">IF(I44="","",G44*I44)</f>
+        <v/>
+      </c>
+      <c r="K44" s="27" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="E45" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F45" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G45" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H45" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I45" s="23"/>
+      <c r="J45" s="24" t="str">
+        <f aca="false">IF(I45="","",G45*I45)</f>
+        <v/>
+      </c>
+      <c r="K45" s="8" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="F46" s="21" t="s">
+        <v>149</v>
+      </c>
+      <c r="G46" s="22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H46" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I46" s="23"/>
+      <c r="J46" s="24" t="str">
+        <f aca="false">IF(I46="","",G46*I46)</f>
+        <v/>
+      </c>
+      <c r="K46" s="27" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
         <v>237</v>
       </c>
-      <c r="B42" s="7" t="s">
-        <v>371</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>372</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>373</v>
-      </c>
-      <c r="E42" s="21" t="s">
-        <v>364</v>
-      </c>
-      <c r="F42" s="21" t="s">
+      <c r="B47" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="F47" s="21" t="s">
         <v>68</v>
       </c>
-      <c r="G42" s="25" t="n">
+      <c r="G47" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="H42" s="21" t="s">
+      <c r="H47" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="I42" s="23"/>
-      <c r="J42" s="24" t="str">
-        <f aca="false">IF(I42="","",G42*I42)</f>
+      <c r="I47" s="23"/>
+      <c r="J47" s="24" t="str">
+        <f aca="false">IF(I47="","",G47*I47)</f>
         <v/>
       </c>
-      <c r="K42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="28"/>
-      <c r="B43" s="29" t="s">
+      <c r="K47" s="8"/>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="28"/>
+      <c r="B48" s="29" t="s">
         <v>242</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="30" t="n">
-        <f aca="false">SUM(J39:J42)</f>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28"/>
+      <c r="H48" s="28"/>
+      <c r="I48" s="28"/>
+      <c r="J48" s="30" t="n">
+        <f aca="false">SUM(J44:J47)</f>
         <v>0</v>
       </c>
-      <c r="K43" s="28"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="11"/>
-      <c r="B45" s="10" t="s">
-        <v>374</v>
-      </c>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="11"/>
-      <c r="G45" s="11"/>
-      <c r="H45" s="11"/>
-      <c r="I45" s="11"/>
-      <c r="J45" s="12" t="n">
-        <f aca="false">J9+J24+J37+J43</f>
+      <c r="K48" s="28"/>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="11"/>
+      <c r="B50" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+      <c r="H50" s="11"/>
+      <c r="I50" s="11"/>
+      <c r="J50" s="12" t="n">
+        <f aca="false">J9+J24+J42+J48</f>
         <v>0</v>
       </c>
-      <c r="K45" s="11"/>
+      <c r="K50" s="11"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -6303,7 +6891,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>375</v>
+        <v>431</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6348,7 +6936,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>376</v>
+        <v>432</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -6366,16 +6954,16 @@
         <v>55</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>377</v>
+        <v>433</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>378</v>
+        <v>434</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>379</v>
+        <v>435</v>
       </c>
       <c r="E6" s="21" t="s">
-        <v>380</v>
+        <v>436</v>
       </c>
       <c r="F6" s="21" t="s">
         <v>76</v>
@@ -6392,7 +6980,7 @@
         <v/>
       </c>
       <c r="K6" s="27" t="s">
-        <v>381</v>
+        <v>437</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6400,16 +6988,16 @@
         <v>63</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>382</v>
+        <v>438</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>384</v>
+        <v>440</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="F7" s="21" t="s">
         <v>76</v>
@@ -6432,16 +7020,16 @@
         <v>71</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>386</v>
+        <v>442</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>387</v>
+        <v>443</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>388</v>
+        <v>444</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>385</v>
+        <v>441</v>
       </c>
       <c r="F8" s="21" t="s">
         <v>76</v>
@@ -6458,7 +7046,7 @@
         <v/>
       </c>
       <c r="K8" s="27" t="s">
-        <v>389</v>
+        <v>445</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6466,16 +7054,16 @@
         <v>79</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>390</v>
+        <v>446</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>391</v>
+        <v>447</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>392</v>
+        <v>448</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>393</v>
+        <v>449</v>
       </c>
       <c r="F9" s="21" t="s">
         <v>76</v>
@@ -6492,7 +7080,7 @@
         <v/>
       </c>
       <c r="K9" s="27" t="s">
-        <v>394</v>
+        <v>450</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6500,16 +7088,16 @@
         <v>85</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>395</v>
+        <v>451</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>396</v>
+        <v>452</v>
       </c>
       <c r="E10" s="21" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="F10" s="21" t="s">
         <v>76</v>
@@ -6526,7 +7114,7 @@
         <v/>
       </c>
       <c r="K10" s="8" t="s">
-        <v>398</v>
+        <v>454</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6534,16 +7122,16 @@
         <v>91</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>399</v>
+        <v>455</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>400</v>
+        <v>456</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>401</v>
+        <v>457</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="F11" s="21" t="s">
         <v>76</v>
@@ -6566,16 +7154,16 @@
         <v>96</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>402</v>
+        <v>458</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>403</v>
+        <v>459</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>404</v>
+        <v>460</v>
       </c>
       <c r="F12" s="21" t="s">
         <v>76</v>
@@ -6592,7 +7180,7 @@
         <v/>
       </c>
       <c r="K12" s="27" t="s">
-        <v>405</v>
+        <v>461</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6600,16 +7188,16 @@
         <v>101</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>406</v>
+        <v>462</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>407</v>
+        <v>463</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>408</v>
+        <v>464</v>
       </c>
       <c r="E13" s="21" t="s">
-        <v>409</v>
+        <v>465</v>
       </c>
       <c r="F13" s="21" t="s">
         <v>76</v>
@@ -6626,7 +7214,7 @@
         <v/>
       </c>
       <c r="K13" s="8" t="s">
-        <v>410</v>
+        <v>466</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6649,7 +7237,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="19" t="s">
-        <v>411</v>
+        <v>467</v>
       </c>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -6667,16 +7255,16 @@
         <v>117</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>412</v>
+        <v>468</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>413</v>
+        <v>469</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>414</v>
+        <v>470</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>415</v>
+        <v>471</v>
       </c>
       <c r="F16" s="21" t="s">
         <v>76</v>
@@ -6699,16 +7287,16 @@
         <v>123</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>416</v>
+        <v>472</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>417</v>
+        <v>473</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>418</v>
+        <v>474</v>
       </c>
       <c r="E17" s="21" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="F17" s="21" t="s">
         <v>76</v>
@@ -6725,7 +7313,7 @@
         <v/>
       </c>
       <c r="K17" s="27" t="s">
-        <v>420</v>
+        <v>476</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6733,16 +7321,16 @@
         <v>128</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>421</v>
+        <v>477</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>422</v>
+        <v>478</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>423</v>
+        <v>479</v>
       </c>
       <c r="E18" s="21" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="F18" s="21" t="s">
         <v>76</v>
@@ -6765,16 +7353,16 @@
         <v>133</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>424</v>
+        <v>480</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>425</v>
+        <v>481</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>426</v>
+        <v>482</v>
       </c>
       <c r="E19" s="21" t="s">
-        <v>427</v>
+        <v>483</v>
       </c>
       <c r="F19" s="21" t="s">
         <v>76</v>
@@ -6797,16 +7385,16 @@
         <v>139</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>428</v>
+        <v>484</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>429</v>
+        <v>485</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>430</v>
+        <v>486</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>397</v>
+        <v>453</v>
       </c>
       <c r="F20" s="21" t="s">
         <v>76</v>
@@ -6823,7 +7411,7 @@
         <v/>
       </c>
       <c r="K20" s="8" t="s">
-        <v>431</v>
+        <v>487</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6831,16 +7419,16 @@
         <v>144</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>432</v>
+        <v>488</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>433</v>
+        <v>489</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>434</v>
+        <v>490</v>
       </c>
       <c r="E21" s="21" t="s">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>68</v>
@@ -6860,10 +7448,10 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>282</v>
+        <v>313</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>436</v>
+        <v>492</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>65</v>
@@ -6872,10 +7460,10 @@
         <v>65</v>
       </c>
       <c r="E22" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F22" s="21" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="G22" s="25" t="n">
         <v>0</v>
@@ -6884,26 +7472,26 @@
         <v>69</v>
       </c>
       <c r="I22" s="37"/>
-      <c r="J22" s="35"/>
+      <c r="J22" s="36"/>
       <c r="K22" s="27" t="s">
-        <v>439</v>
+        <v>495</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>440</v>
+        <v>496</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>441</v>
+        <v>497</v>
       </c>
       <c r="E23" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>149</v>
@@ -6941,7 +7529,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="19" t="s">
-        <v>442</v>
+        <v>498</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -6959,21 +7547,21 @@
         <v>153</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>443</v>
+        <v>499</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>444</v>
+        <v>500</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>445</v>
+        <v>501</v>
       </c>
       <c r="E26" s="21" t="s">
-        <v>446</v>
+        <v>502</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G26" s="36" t="n">
+        <v>248</v>
+      </c>
+      <c r="G26" s="31" t="n">
         <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-ACS",'Cable Schedule'!A:A,0))</f>
         <v>1993</v>
       </c>
@@ -6986,7 +7574,7 @@
         <v/>
       </c>
       <c r="K26" s="27" t="s">
-        <v>447</v>
+        <v>503</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6994,21 +7582,21 @@
         <v>159</v>
       </c>
       <c r="B27" s="26" t="s">
-        <v>448</v>
+        <v>504</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>449</v>
+        <v>505</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>450</v>
+        <v>506</v>
       </c>
       <c r="E27" s="21" t="s">
-        <v>451</v>
+        <v>507</v>
       </c>
       <c r="F27" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G27" s="36" t="n">
+        <v>248</v>
+      </c>
+      <c r="G27" s="31" t="n">
         <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-DATA",'Cable Schedule'!A:A,0))</f>
         <v>1209</v>
       </c>
@@ -7021,7 +7609,7 @@
         <v/>
       </c>
       <c r="K27" s="27" t="s">
-        <v>452</v>
+        <v>508</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7029,7 +7617,7 @@
         <v>163</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>453</v>
+        <v>509</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>65</v>
@@ -7038,7 +7626,7 @@
         <v>65</v>
       </c>
       <c r="E28" s="21" t="s">
-        <v>419</v>
+        <v>475</v>
       </c>
       <c r="F28" s="21" t="s">
         <v>68</v>
@@ -7050,9 +7638,9 @@
         <v>77</v>
       </c>
       <c r="I28" s="37"/>
-      <c r="J28" s="35"/>
+      <c r="J28" s="36"/>
       <c r="K28" s="8" t="s">
-        <v>454</v>
+        <v>510</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7060,16 +7648,16 @@
         <v>167</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>455</v>
+        <v>511</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>65</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>456</v>
+        <v>512</v>
       </c>
       <c r="E29" s="21" t="s">
-        <v>457</v>
+        <v>513</v>
       </c>
       <c r="F29" s="21" t="s">
         <v>149</v>
@@ -7092,21 +7680,21 @@
         <v>173</v>
       </c>
       <c r="B30" s="26" t="s">
-        <v>458</v>
+        <v>514</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>459</v>
+        <v>515</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>460</v>
+        <v>516</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>461</v>
+        <v>517</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="G30" s="36" t="n">
+        <v>248</v>
+      </c>
+      <c r="G30" s="31" t="n">
         <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-DPS",'Cable Schedule'!A:A,0))</f>
         <v>1209</v>
       </c>
@@ -7119,7 +7707,7 @@
         <v/>
       </c>
       <c r="K30" s="27" t="s">
-        <v>462</v>
+        <v>518</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7127,21 +7715,21 @@
         <v>179</v>
       </c>
       <c r="B31" s="26" t="s">
-        <v>463</v>
+        <v>519</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>464</v>
+        <v>520</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>465</v>
+        <v>521</v>
       </c>
       <c r="E31" s="21" t="s">
-        <v>466</v>
+        <v>522</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G31" s="36" t="n">
+      <c r="G31" s="31" t="n">
         <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-C1IN",'Cable Schedule'!A:A,0))</f>
         <v>140</v>
       </c>
@@ -7154,7 +7742,7 @@
         <v/>
       </c>
       <c r="K31" s="27" t="s">
-        <v>467</v>
+        <v>523</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7162,21 +7750,21 @@
         <v>184</v>
       </c>
       <c r="B32" s="26" t="s">
-        <v>468</v>
+        <v>524</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>469</v>
+        <v>525</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>470</v>
+        <v>526</v>
       </c>
       <c r="E32" s="21" t="s">
-        <v>471</v>
+        <v>527</v>
       </c>
       <c r="F32" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="G32" s="36" t="n">
+      <c r="G32" s="31" t="n">
         <f aca="false">INDEX('Cable Schedule'!E:E,MATCH("TOT-C34",'Cable Schedule'!A:A,0))</f>
         <v>85</v>
       </c>
@@ -7189,7 +7777,7 @@
         <v/>
       </c>
       <c r="K32" s="27" t="s">
-        <v>472</v>
+        <v>528</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7212,7 +7800,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>473</v>
+        <v>529</v>
       </c>
       <c r="B34" s="20"/>
       <c r="C34" s="20"/>
@@ -7230,7 +7818,7 @@
         <v>220</v>
       </c>
       <c r="B35" s="26" t="s">
-        <v>474</v>
+        <v>530</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>65</v>
@@ -7239,10 +7827,10 @@
         <v>65</v>
       </c>
       <c r="E35" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F35" s="21" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="G35" s="25" t="n">
         <v>0</v>
@@ -7251,9 +7839,9 @@
         <v>65</v>
       </c>
       <c r="I35" s="37"/>
-      <c r="J35" s="35"/>
+      <c r="J35" s="36"/>
       <c r="K35" s="27" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7261,7 +7849,7 @@
         <v>226</v>
       </c>
       <c r="B36" s="26" t="s">
-        <v>476</v>
+        <v>532</v>
       </c>
       <c r="C36" s="7" t="s">
         <v>65</v>
@@ -7270,10 +7858,10 @@
         <v>65</v>
       </c>
       <c r="E36" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F36" s="21" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="G36" s="25" t="n">
         <v>0</v>
@@ -7282,9 +7870,9 @@
         <v>65</v>
       </c>
       <c r="I36" s="37"/>
-      <c r="J36" s="35"/>
+      <c r="J36" s="36"/>
       <c r="K36" s="27" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7292,7 +7880,7 @@
         <v>231</v>
       </c>
       <c r="B37" s="26" t="s">
-        <v>477</v>
+        <v>533</v>
       </c>
       <c r="C37" s="7" t="s">
         <v>65</v>
@@ -7301,10 +7889,10 @@
         <v>65</v>
       </c>
       <c r="E37" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F37" s="21" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="G37" s="25" t="n">
         <v>0</v>
@@ -7313,9 +7901,9 @@
         <v>65</v>
       </c>
       <c r="I37" s="37"/>
-      <c r="J37" s="35"/>
+      <c r="J37" s="36"/>
       <c r="K37" s="27" t="s">
-        <v>478</v>
+        <v>534</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7323,7 +7911,7 @@
         <v>237</v>
       </c>
       <c r="B38" s="26" t="s">
-        <v>479</v>
+        <v>535</v>
       </c>
       <c r="C38" s="7" t="s">
         <v>65</v>
@@ -7332,10 +7920,10 @@
         <v>65</v>
       </c>
       <c r="E38" s="21" t="s">
-        <v>437</v>
+        <v>493</v>
       </c>
       <c r="F38" s="21" t="s">
-        <v>438</v>
+        <v>494</v>
       </c>
       <c r="G38" s="25" t="n">
         <v>0</v>
@@ -7344,15 +7932,15 @@
         <v>65</v>
       </c>
       <c r="I38" s="37"/>
-      <c r="J38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="27" t="s">
-        <v>475</v>
+        <v>531</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11"/>
       <c r="B40" s="10" t="s">
-        <v>480</v>
+        <v>536</v>
       </c>
       <c r="C40" s="11"/>
       <c r="D40" s="11"/>
@@ -7397,22 +7985,22 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>481</v>
+        <v>537</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>482</v>
+        <v>538</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>483</v>
+        <v>539</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="4" t="s">
-        <v>484</v>
+        <v>540</v>
       </c>
       <c r="C5" s="38" t="n">
         <v>50</v>
@@ -7421,23 +8009,23 @@
         <v>61</v>
       </c>
       <c r="E5" s="39" t="s">
-        <v>485</v>
+        <v>541</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>486</v>
+        <v>542</v>
       </c>
       <c r="C6" s="40" t="n">
         <v>0.1</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>487</v>
+        <v>543</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>488</v>
+        <v>544</v>
       </c>
       <c r="C7" s="38" t="n">
         <v>50</v>
@@ -7448,33 +8036,33 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="5" t="s">
-        <v>489</v>
+        <v>545</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>490</v>
+        <v>546</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>491</v>
+        <v>547</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>492</v>
+        <v>548</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>493</v>
+        <v>549</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>494</v>
+        <v>550</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>53</v>
@@ -7482,13 +8070,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="41" t="s">
-        <v>498</v>
+        <v>554</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>499</v>
+        <v>555</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="D11" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7512,13 +8100,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="41" t="s">
-        <v>501</v>
+        <v>557</v>
       </c>
       <c r="B12" s="27" t="s">
-        <v>502</v>
+        <v>558</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>500</v>
+        <v>556</v>
       </c>
       <c r="D12" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7539,18 +8127,18 @@
       </c>
       <c r="I12" s="44"/>
       <c r="J12" s="45" t="s">
-        <v>503</v>
+        <v>559</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="41" t="s">
-        <v>504</v>
+        <v>560</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>505</v>
+        <v>561</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>506</v>
+        <v>562</v>
       </c>
       <c r="D13" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B4",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7574,13 +8162,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="41" t="s">
-        <v>507</v>
+        <v>563</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>508</v>
+        <v>564</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>509</v>
+        <v>565</v>
       </c>
       <c r="D14" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7604,13 +8192,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="41" t="s">
-        <v>510</v>
+        <v>566</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>511</v>
+        <v>567</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>512</v>
+        <v>568</v>
       </c>
       <c r="D15" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B12",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7634,10 +8222,10 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="29" t="s">
-        <v>513</v>
+        <v>569</v>
       </c>
       <c r="B16" s="29" t="s">
-        <v>514</v>
+        <v>570</v>
       </c>
       <c r="C16" s="28"/>
       <c r="D16" s="28"/>
@@ -7655,10 +8243,10 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="29" t="s">
-        <v>515</v>
+        <v>571</v>
       </c>
       <c r="B17" s="29" t="s">
-        <v>516</v>
+        <v>572</v>
       </c>
       <c r="C17" s="28"/>
       <c r="D17" s="28"/>
@@ -7676,10 +8264,10 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="29" t="s">
-        <v>517</v>
+        <v>573</v>
       </c>
       <c r="B18" s="29" t="s">
-        <v>518</v>
+        <v>574</v>
       </c>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
@@ -7697,35 +8285,35 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="s">
-        <v>519</v>
+        <v>575</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>490</v>
+        <v>546</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>520</v>
+        <v>576</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>492</v>
+        <v>548</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>493</v>
+        <v>549</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>494</v>
+        <v>550</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="41" t="s">
-        <v>521</v>
+        <v>577</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>522</v>
+        <v>578</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>523</v>
+        <v>579</v>
       </c>
       <c r="D22" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B3",'Telecom OSP'!A:A,0))</f>
@@ -7743,13 +8331,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="41" t="s">
-        <v>524</v>
+        <v>580</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>525</v>
+        <v>581</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>526</v>
+        <v>582</v>
       </c>
       <c r="D23" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B4",'Telecom OSP'!A:A,0))</f>
@@ -7767,13 +8355,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="41" t="s">
-        <v>527</v>
+        <v>583</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>528</v>
+        <v>584</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>529</v>
+        <v>585</v>
       </c>
       <c r="D24" s="42" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B5",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B6",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B11",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B12",'Telecom OSP'!A:A,0))</f>
@@ -7791,10 +8379,10 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="29" t="s">
-        <v>530</v>
+        <v>586</v>
       </c>
       <c r="B25" s="29" t="s">
-        <v>531</v>
+        <v>587</v>
       </c>
       <c r="C25" s="28"/>
       <c r="D25" s="28"/>
@@ -7812,13 +8400,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>532</v>
+        <v>588</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>533</v>
+        <v>589</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>534</v>
+        <v>590</v>
       </c>
       <c r="D26" s="48" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("B1",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B2",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B8",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("B9",'Telecom OSP'!A:A,0))</f>
@@ -7827,38 +8415,38 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="5" t="s">
-        <v>535</v>
+        <v>591</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>536</v>
+        <v>592</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>537</v>
+        <v>593</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>538</v>
+        <v>594</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>539</v>
+        <v>595</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>540</v>
+        <v>596</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="41" t="s">
-        <v>541</v>
+        <v>597</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>542</v>
+        <v>598</v>
       </c>
       <c r="C30" s="41" t="s">
-        <v>543</v>
+        <v>599</v>
       </c>
       <c r="D30" s="41" t="n">
         <v>2</v>
@@ -7877,13 +8465,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="41" t="s">
-        <v>544</v>
+        <v>600</v>
       </c>
       <c r="B31" s="8" t="s">
-        <v>545</v>
+        <v>601</v>
       </c>
       <c r="C31" s="41" t="s">
-        <v>543</v>
+        <v>599</v>
       </c>
       <c r="D31" s="41" t="n">
         <v>1</v>
@@ -7902,13 +8490,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="41" t="s">
-        <v>546</v>
+        <v>602</v>
       </c>
       <c r="B32" s="8" t="s">
-        <v>547</v>
+        <v>603</v>
       </c>
       <c r="C32" s="41" t="s">
-        <v>543</v>
+        <v>599</v>
       </c>
       <c r="D32" s="41" t="n">
         <v>4</v>
@@ -7927,13 +8515,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="41" t="s">
-        <v>548</v>
+        <v>604</v>
       </c>
       <c r="B33" s="8" t="s">
-        <v>549</v>
+        <v>605</v>
       </c>
       <c r="C33" s="41" t="s">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="D33" s="41" t="n">
         <v>2</v>
@@ -7952,13 +8540,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="41" t="s">
-        <v>551</v>
+        <v>607</v>
       </c>
       <c r="B34" s="8" t="s">
-        <v>552</v>
+        <v>608</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>550</v>
+        <v>606</v>
       </c>
       <c r="D34" s="41" t="n">
         <v>3</v>
@@ -7977,10 +8565,10 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="29" t="s">
-        <v>553</v>
+        <v>609</v>
       </c>
       <c r="B35" s="29" t="s">
-        <v>554</v>
+        <v>610</v>
       </c>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
@@ -7996,10 +8584,10 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="29" t="s">
-        <v>555</v>
+        <v>611</v>
       </c>
       <c r="B36" s="29" t="s">
-        <v>556</v>
+        <v>612</v>
       </c>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
@@ -8015,50 +8603,50 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="5" t="s">
-        <v>557</v>
+        <v>613</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="6" t="s">
-        <v>558</v>
+        <v>614</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>559</v>
+        <v>615</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>560</v>
+        <v>616</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>495</v>
+        <v>551</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>496</v>
+        <v>552</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>497</v>
+        <v>553</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>561</v>
+        <v>617</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>562</v>
+        <v>618</v>
       </c>
       <c r="I39" s="6" t="s">
-        <v>563</v>
+        <v>619</v>
       </c>
       <c r="J39" s="6" t="s">
-        <v>564</v>
+        <v>620</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="41" t="s">
-        <v>287</v>
+        <v>318</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>565</v>
+        <v>621</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>566</v>
+        <v>622</v>
       </c>
       <c r="D40" s="41" t="n">
         <v>5</v>
@@ -8080,18 +8668,18 @@
         <v>12</v>
       </c>
       <c r="J40" s="50" t="s">
-        <v>567</v>
+        <v>623</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="41" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="B41" s="8" t="s">
-        <v>568</v>
+        <v>624</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>566</v>
+        <v>622</v>
       </c>
       <c r="D41" s="41" t="n">
         <v>3</v>
@@ -8119,10 +8707,10 @@
         <v>139</v>
       </c>
       <c r="B42" s="8" t="s">
-        <v>569</v>
+        <v>625</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D42" s="41" t="n">
         <v>2</v>
@@ -8150,10 +8738,10 @@
         <v>144</v>
       </c>
       <c r="B43" s="8" t="s">
-        <v>571</v>
+        <v>627</v>
       </c>
       <c r="C43" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D43" s="41" t="n">
         <v>2</v>
@@ -8178,13 +8766,13 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="41" t="s">
-        <v>292</v>
+        <v>323</v>
       </c>
       <c r="B44" s="8" t="s">
-        <v>572</v>
+        <v>628</v>
       </c>
       <c r="C44" s="41" t="s">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="D44" s="41" t="n">
         <v>2</v>
@@ -8209,13 +8797,13 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="41" t="s">
-        <v>297</v>
+        <v>328</v>
       </c>
       <c r="B45" s="8" t="s">
-        <v>574</v>
+        <v>630</v>
       </c>
       <c r="C45" s="41" t="s">
-        <v>573</v>
+        <v>629</v>
       </c>
       <c r="D45" s="41" t="n">
         <v>1</v>
@@ -8243,10 +8831,10 @@
         <v>128</v>
       </c>
       <c r="B46" s="8" t="s">
-        <v>575</v>
+        <v>631</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D46" s="41" t="n">
         <v>2</v>
@@ -8274,10 +8862,10 @@
         <v>133</v>
       </c>
       <c r="B47" s="8" t="s">
-        <v>576</v>
+        <v>632</v>
       </c>
       <c r="C47" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D47" s="41" t="n">
         <v>1</v>
@@ -8305,10 +8893,10 @@
         <v>123</v>
       </c>
       <c r="B48" s="8" t="s">
-        <v>577</v>
+        <v>633</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D48" s="41" t="n">
         <v>0</v>
@@ -8330,7 +8918,7 @@
         <v>6</v>
       </c>
       <c r="J48" s="50" t="s">
-        <v>578</v>
+        <v>634</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8338,10 +8926,10 @@
         <v>117</v>
       </c>
       <c r="B49" s="8" t="s">
-        <v>579</v>
+        <v>635</v>
       </c>
       <c r="C49" s="41" t="s">
-        <v>570</v>
+        <v>626</v>
       </c>
       <c r="D49" s="41" t="n">
         <v>0</v>
@@ -8363,15 +8951,15 @@
         <v>6</v>
       </c>
       <c r="J49" s="50" t="s">
-        <v>578</v>
+        <v>634</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="51" t="s">
-        <v>580</v>
+        <v>636</v>
       </c>
       <c r="B51" s="52" t="s">
-        <v>581</v>
+        <v>637</v>
       </c>
       <c r="C51" s="52"/>
       <c r="D51" s="52"/>
@@ -8400,7 +8988,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
@@ -8416,32 +9004,32 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="18" t="s">
-        <v>582</v>
+        <v>638</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>583</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>584</v>
+        <v>640</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>44</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>585</v>
+        <v>641</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>586</v>
+        <v>642</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>587</v>
+        <v>643</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>588</v>
+        <v>644</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>50</v>
@@ -8455,7 +9043,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>589</v>
+        <v>645</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -8468,24 +9056,24 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="21" t="s">
-        <v>590</v>
+        <v>646</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>591</v>
+        <v>647</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>593</v>
+        <v>649</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>594</v>
+        <v>650</v>
       </c>
       <c r="F6" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G6" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G6" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C1",'Site Electrical'!A:A,0))</f>
         <v>9</v>
       </c>
@@ -8493,29 +9081,29 @@
         <v>69</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>596</v>
+        <v>652</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="21" t="s">
-        <v>597</v>
+        <v>653</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>598</v>
+        <v>654</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>593</v>
+        <v>649</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>599</v>
+        <v>655</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G7" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G7" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C2",'Site Electrical'!A:A,0))</f>
         <v>7</v>
       </c>
@@ -8523,29 +9111,29 @@
         <v>69</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>600</v>
+        <v>656</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="21" t="s">
-        <v>601</v>
+        <v>657</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>602</v>
+        <v>658</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>592</v>
+        <v>648</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>593</v>
+        <v>649</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>603</v>
+        <v>659</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G8" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G8" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C3",'Site Electrical'!A:A,0))</f>
         <v>2</v>
       </c>
@@ -8556,24 +9144,24 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>604</v>
+        <v>660</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>605</v>
+        <v>661</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>606</v>
+        <v>662</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>607</v>
+        <v>663</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>608</v>
+        <v>664</v>
       </c>
       <c r="F9" s="53" t="s">
-        <v>609</v>
-      </c>
-      <c r="G9" s="36" t="n">
+        <v>665</v>
+      </c>
+      <c r="G9" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C4",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
@@ -8581,29 +9169,29 @@
         <v>69</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>610</v>
+        <v>666</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="21" t="s">
-        <v>611</v>
+        <v>667</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>612</v>
+        <v>668</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>613</v>
+        <v>669</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>614</v>
+        <v>670</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>615</v>
+        <v>671</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G10" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G10" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C6",'Site Electrical'!A:A,0))</f>
         <v>6</v>
       </c>
@@ -8611,29 +9199,29 @@
         <v>69</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>616</v>
+        <v>672</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="21" t="s">
-        <v>617</v>
+        <v>673</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>618</v>
+        <v>674</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>619</v>
+        <v>675</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>620</v>
+        <v>676</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>621</v>
+        <v>677</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G11" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G11" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C8",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -8641,29 +9229,29 @@
         <v>69</v>
       </c>
       <c r="I11" s="8" t="s">
-        <v>622</v>
+        <v>678</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="21" t="s">
-        <v>623</v>
+        <v>679</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>624</v>
+        <v>680</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>625</v>
+        <v>681</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>626</v>
+        <v>682</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="F12" s="53" t="s">
-        <v>609</v>
-      </c>
-      <c r="G12" s="36" t="n">
+        <v>665</v>
+      </c>
+      <c r="G12" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C9",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
@@ -8671,12 +9259,12 @@
         <v>69</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>627</v>
+        <v>683</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="19" t="s">
-        <v>628</v>
+        <v>684</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -8689,22 +9277,22 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="21" t="s">
-        <v>629</v>
+        <v>685</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>630</v>
+        <v>686</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>631</v>
+        <v>687</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>632</v>
+        <v>688</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="F14" s="34" t="s">
-        <v>633</v>
+      <c r="F14" s="35" t="s">
+        <v>689</v>
       </c>
       <c r="G14" s="21" t="n">
         <v>1</v>
@@ -8713,29 +9301,29 @@
         <v>69</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>634</v>
+        <v>690</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="21" t="s">
-        <v>635</v>
+        <v>691</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>636</v>
+        <v>692</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>637</v>
+        <v>693</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>638</v>
+        <v>694</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>639</v>
+        <v>695</v>
       </c>
       <c r="F15" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G15" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G15" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("B3",'Site Electrical'!A:A,0))</f>
         <v>1</v>
       </c>
@@ -8743,29 +9331,29 @@
         <v>69</v>
       </c>
       <c r="I15" s="8" t="s">
-        <v>641</v>
+        <v>697</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="21" t="s">
-        <v>642</v>
+        <v>698</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>643</v>
+        <v>699</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>644</v>
+        <v>700</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>645</v>
+        <v>701</v>
       </c>
       <c r="E16" s="7" t="s">
-        <v>646</v>
+        <v>702</v>
       </c>
       <c r="F16" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G16" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G16" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D1",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -8773,29 +9361,29 @@
         <v>69</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>647</v>
+        <v>703</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="21" t="s">
-        <v>648</v>
+        <v>704</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>649</v>
+        <v>705</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>650</v>
+        <v>706</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>651</v>
+        <v>707</v>
       </c>
       <c r="E17" s="7" t="s">
-        <v>652</v>
+        <v>708</v>
       </c>
       <c r="F17" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G17" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G17" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C5",'Site Electrical'!A:A,0))</f>
         <v>18</v>
       </c>
@@ -8803,29 +9391,29 @@
         <v>69</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>653</v>
+        <v>709</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="21" t="s">
-        <v>654</v>
+        <v>710</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>655</v>
+        <v>711</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>656</v>
+        <v>712</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>657</v>
+        <v>713</v>
       </c>
       <c r="E18" s="7" t="s">
-        <v>658</v>
+        <v>714</v>
       </c>
       <c r="F18" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G18" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G18" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("D4",'Site Electrical'!A:A,0))</f>
         <v>3</v>
       </c>
@@ -8833,29 +9421,29 @@
         <v>69</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>659</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="21" t="s">
-        <v>660</v>
+        <v>716</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>661</v>
+        <v>717</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>233</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>662</v>
+        <v>718</v>
       </c>
       <c r="E19" s="7" t="s">
-        <v>663</v>
+        <v>719</v>
       </c>
       <c r="F19" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G19" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G19" s="31" t="n">
         <f aca="false">INDEX('Site Electrical'!G:G,MATCH("C12",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("D3",'Site Electrical'!A:A,0))</f>
         <v>56</v>
       </c>
@@ -8863,12 +9451,12 @@
         <v>69</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>664</v>
+        <v>720</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="19" t="s">
-        <v>665</v>
+        <v>721</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -8881,24 +9469,24 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="21" t="s">
-        <v>666</v>
+        <v>722</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>667</v>
+        <v>723</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>668</v>
+        <v>724</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>669</v>
+        <v>725</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>670</v>
+        <v>726</v>
       </c>
       <c r="F21" s="53" t="s">
-        <v>609</v>
-      </c>
-      <c r="G21" s="36" t="n">
+        <v>665</v>
+      </c>
+      <c r="G21" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A1",'Telecom OSP'!A:A,0))</f>
         <v>4</v>
       </c>
@@ -8906,29 +9494,29 @@
         <v>69</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>671</v>
+        <v>727</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>672</v>
+        <v>728</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>673</v>
+        <v>729</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>674</v>
+        <v>730</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>675</v>
+        <v>731</v>
       </c>
       <c r="F22" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G22" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G22" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("A2",'Telecom OSP'!A:A,0))</f>
         <v>5</v>
       </c>
@@ -8936,29 +9524,29 @@
         <v>69</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>676</v>
+        <v>732</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>677</v>
+        <v>733</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>678</v>
+        <v>734</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>679</v>
+        <v>735</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>680</v>
+        <v>736</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>681</v>
+        <v>737</v>
       </c>
       <c r="F23" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G23" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G23" s="31" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
         <v>2499</v>
       </c>
@@ -8966,29 +9554,29 @@
         <v>61</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>682</v>
+        <v>738</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>683</v>
+        <v>739</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>684</v>
+        <v>740</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>685</v>
+        <v>741</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>680</v>
+        <v>736</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>686</v>
+        <v>742</v>
       </c>
       <c r="F24" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G24" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G24" s="31" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
         <v>598</v>
       </c>
@@ -8996,29 +9584,29 @@
         <v>61</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>687</v>
+        <v>743</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="21" t="s">
-        <v>688</v>
+        <v>744</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>689</v>
+        <v>745</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>690</v>
+        <v>746</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>691</v>
+        <v>747</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>692</v>
+        <v>748</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G25" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G25" s="31" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B7",'Telecom OSP'!A:A,0))*2+INDEX('Telecom OSP'!G:G,MATCH("B10",'Telecom OSP'!A:A,0))*4,0)</f>
         <v>2499</v>
       </c>
@@ -9026,29 +9614,29 @@
         <v>61</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>693</v>
+        <v>749</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="21" t="s">
-        <v>694</v>
+        <v>750</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>695</v>
+        <v>751</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>696</v>
+        <v>752</v>
       </c>
       <c r="D26" s="7" t="s">
-        <v>691</v>
+        <v>747</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>697</v>
+        <v>753</v>
       </c>
       <c r="F26" s="21" t="s">
-        <v>595</v>
-      </c>
-      <c r="G26" s="36" t="n">
+        <v>651</v>
+      </c>
+      <c r="G26" s="31" t="n">
         <f aca="false">ROUND(INDEX('Telecom OSP'!G:G,MATCH("B13",'Telecom OSP'!A:A,0))*2,0)</f>
         <v>598</v>
       </c>
@@ -9056,29 +9644,29 @@
         <v>61</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>698</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="21" t="s">
-        <v>699</v>
+        <v>755</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>700</v>
+        <v>756</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>701</v>
+        <v>757</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>702</v>
+        <v>758</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>703</v>
+        <v>759</v>
       </c>
       <c r="F27" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G27" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G27" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("D1",'Telecom OSP'!A:A,0))</f>
         <v>1425</v>
       </c>
@@ -9086,27 +9674,27 @@
         <v>61</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>704</v>
+        <v>760</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="21" t="s">
-        <v>705</v>
+        <v>761</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>706</v>
+        <v>762</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>707</v>
+        <v>763</v>
       </c>
       <c r="D28" s="7" t="s">
-        <v>708</v>
+        <v>764</v>
       </c>
       <c r="E28" s="7" t="s">
-        <v>709</v>
+        <v>765</v>
       </c>
       <c r="F28" s="54" t="s">
-        <v>640</v>
+        <v>696</v>
       </c>
       <c r="G28" s="21" t="n">
         <v>1</v>
@@ -9115,29 +9703,29 @@
         <v>77</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>710</v>
+        <v>766</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="21" t="s">
-        <v>711</v>
+        <v>767</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>712</v>
+        <v>768</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>713</v>
+        <v>769</v>
       </c>
       <c r="D29" s="7" t="s">
-        <v>714</v>
+        <v>770</v>
       </c>
       <c r="E29" s="7" t="s">
-        <v>715</v>
+        <v>771</v>
       </c>
       <c r="F29" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G29" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G29" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C1",'Telecom OSP'!A:A,0))</f>
         <v>1407</v>
       </c>
@@ -9145,29 +9733,29 @@
         <v>61</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>716</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="21" t="s">
-        <v>717</v>
+        <v>773</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>718</v>
+        <v>774</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>719</v>
+        <v>775</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>720</v>
+        <v>776</v>
       </c>
       <c r="E30" s="7" t="s">
-        <v>721</v>
+        <v>777</v>
       </c>
       <c r="F30" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G30" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G30" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C7",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C8",'Telecom OSP'!A:A,0))</f>
         <v>42</v>
       </c>
@@ -9175,29 +9763,29 @@
         <v>69</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>722</v>
+        <v>778</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>723</v>
+        <v>779</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>724</v>
+        <v>780</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>725</v>
+        <v>781</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>726</v>
+        <v>782</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>727</v>
+        <v>783</v>
       </c>
       <c r="F31" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G31" s="36" t="n">
+        <v>696</v>
+      </c>
+      <c r="G31" s="31" t="n">
         <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C9",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C10",'Telecom OSP'!A:A,0))</f>
         <v>10</v>
       </c>
@@ -9205,27 +9793,27 @@
         <v>69</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>728</v>
+        <v>784</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="21" t="s">
-        <v>729</v>
+        <v>785</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>730</v>
+        <v>786</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>731</v>
+        <v>787</v>
       </c>
       <c r="D32" s="7" t="s">
-        <v>732</v>
+        <v>788</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>733</v>
+        <v>789</v>
       </c>
       <c r="F32" s="54" t="s">
-        <v>640</v>
+        <v>696</v>
       </c>
       <c r="G32" s="21" t="n">
         <v>1</v>
@@ -9234,12 +9822,12 @@
         <v>77</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>734</v>
+        <v>790</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>735</v>
+        <v>791</v>
       </c>
       <c r="B33" s="20"/>
       <c r="C33" s="20"/>
@@ -9252,329 +9840,402 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="21" t="s">
-        <v>736</v>
+        <v>554</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>737</v>
+        <v>792</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>738</v>
+        <v>793</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>739</v>
+        <v>794</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>740</v>
+        <v>795</v>
       </c>
       <c r="F34" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G34" s="21" t="n">
+        <v>696</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C2",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C3",'Telecom OSP'!A:A,0))+INDEX('Telecom OSP'!G:G,MATCH("C4",'Telecom OSP'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("E1",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("E2",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("E3",'Site Electrical'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("E4",'Site Electrical'!A:A,0))</f>
+        <v>146.8</v>
+      </c>
+      <c r="H34" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="I34" s="8" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="F35" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G35" s="31" t="n">
+        <f aca="false">INDEX('Telecom OSP'!G:G,MATCH("C16",'Telecom OSP'!A:A,0))+INDEX('Site Electrical'!G:G,MATCH("E5",'Site Electrical'!A:A,0))</f>
+        <v>4.1</v>
+      </c>
+      <c r="H35" s="21" t="s">
+        <v>271</v>
+      </c>
+      <c r="I35" s="8" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="19" t="s">
+        <v>802</v>
+      </c>
+      <c r="B36" s="20"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="20"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
+      <c r="G36" s="20"/>
+      <c r="H36" s="20"/>
+      <c r="I36" s="20"/>
+    </row>
+    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
+        <v>803</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="F37" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G37" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H37" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I34" s="8" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
-        <v>742</v>
-      </c>
-      <c r="B35" s="7" t="s">
-        <v>743</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>744</v>
-      </c>
-      <c r="D35" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="E35" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="F35" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G35" s="36" t="n">
+      <c r="I37" s="8" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
+        <v>809</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G38" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B5",Security!A:A,0))</f>
         <v>1</v>
       </c>
-      <c r="H35" s="21" t="s">
+      <c r="H38" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="8" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
-        <v>747</v>
-      </c>
-      <c r="B36" s="7" t="s">
-        <v>748</v>
-      </c>
-      <c r="C36" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="D36" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="E36" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="F36" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G36" s="36" t="n">
+      <c r="I38" s="8" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
+        <v>814</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>818</v>
+      </c>
+      <c r="F39" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G39" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A1",Security!A:A,0))</f>
         <v>2</v>
       </c>
-      <c r="H36" s="21" t="s">
+      <c r="H39" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I36" s="8" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
-        <v>753</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>757</v>
-      </c>
-      <c r="F37" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G37" s="36" t="n">
+      <c r="I39" s="8" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
+        <v>820</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>823</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="F40" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G40" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A3",Security!A:A,0))+INDEX(Security!G:G,MATCH("A4",Security!A:A,0))</f>
         <v>2</v>
       </c>
-      <c r="H37" s="21" t="s">
+      <c r="H40" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I37" s="8" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
-        <v>759</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>762</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>763</v>
-      </c>
-      <c r="F38" s="53" t="s">
-        <v>609</v>
-      </c>
-      <c r="G38" s="36" t="n">
+      <c r="I40" s="8" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
+        <v>826</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>828</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="F41" s="53" t="s">
+        <v>665</v>
+      </c>
+      <c r="G41" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B1",Security!A:A,0))+INDEX(Security!G:G,MATCH("B2",Security!A:A,0))</f>
         <v>2</v>
       </c>
-      <c r="H38" s="21" t="s">
+      <c r="H41" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I38" s="8" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
-        <v>765</v>
-      </c>
-      <c r="B39" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="C39" s="7" t="s">
-        <v>767</v>
-      </c>
-      <c r="D39" s="7" t="s">
-        <v>768</v>
-      </c>
-      <c r="E39" s="7" t="s">
-        <v>769</v>
-      </c>
-      <c r="F39" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G39" s="36" t="n">
+      <c r="I41" s="8" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="21" t="s">
+        <v>832</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>833</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>834</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>835</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>836</v>
+      </c>
+      <c r="F42" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G42" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A7",Security!A:A,0))</f>
         <v>3</v>
       </c>
-      <c r="H39" s="21" t="s">
+      <c r="H42" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I39" s="8" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
-        <v>771</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>772</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>773</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="F40" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G40" s="36" t="n">
+      <c r="I42" s="8" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="21" t="s">
+        <v>838</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>841</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="F43" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G43" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("A6",Security!A:A,0))</f>
         <v>3</v>
       </c>
-      <c r="H40" s="21" t="s">
+      <c r="H43" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I40" s="8" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21" t="s">
-        <v>777</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>778</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="F41" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G41" s="36" t="n">
+      <c r="I43" s="8" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="21" t="s">
+        <v>844</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>845</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="F44" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G44" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("C2",Security!A:A,0))</f>
         <v>1209</v>
       </c>
-      <c r="H41" s="21" t="s">
+      <c r="H44" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I41" s="8" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
-        <v>783</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>787</v>
-      </c>
-      <c r="F42" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G42" s="36" t="n">
+      <c r="I44" s="8" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
+        <v>850</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>851</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="F45" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G45" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("C1",Security!A:A,0))</f>
         <v>1993</v>
       </c>
-      <c r="H42" s="21" t="s">
+      <c r="H45" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I42" s="8"/>
-    </row>
-    <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
-        <v>788</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>792</v>
-      </c>
-      <c r="F43" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G43" s="36" t="n">
+      <c r="I45" s="8"/>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
+        <v>855</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>856</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>857</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>858</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="F46" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G46" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("B3",Security!A:A,0))</f>
         <v>1</v>
       </c>
-      <c r="H43" s="21" t="s">
+      <c r="H46" s="21" t="s">
         <v>69</v>
       </c>
-      <c r="I43" s="8" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="s">
-        <v>794</v>
-      </c>
-      <c r="B44" s="7" t="s">
-        <v>795</v>
-      </c>
-      <c r="C44" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="D44" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="E44" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="F44" s="54" t="s">
-        <v>640</v>
-      </c>
-      <c r="G44" s="36" t="n">
+      <c r="I46" s="8" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
+        <v>861</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>863</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="F47" s="54" t="s">
+        <v>696</v>
+      </c>
+      <c r="G47" s="31" t="n">
         <f aca="false">INDEX(Security!G:G,MATCH("C5",Security!A:A,0))</f>
         <v>1209</v>
       </c>
-      <c r="H44" s="21" t="s">
+      <c r="H47" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="I44" s="8" t="s">
-        <v>799</v>
+      <c r="I47" s="8" t="s">
+        <v>866</v>
       </c>
     </row>
   </sheetData>
@@ -9593,7 +10254,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C59"/>
+  <dimension ref="B2:C60"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -9603,42 +10264,42 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="55" t="s">
-        <v>800</v>
+        <v>867</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="56" t="s">
-        <v>801</v>
+        <v>868</v>
       </c>
       <c r="C4" s="57"/>
     </row>
     <row r="5" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="58" t="s">
-        <v>802</v>
+        <v>869</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>803</v>
+        <v>870</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="58" t="s">
-        <v>804</v>
+        <v>871</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>805</v>
+        <v>872</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="58" t="s">
-        <v>806</v>
+        <v>873</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>807</v>
+        <v>874</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="56" t="s">
-        <v>808</v>
+        <v>875</v>
       </c>
       <c r="C9" s="57"/>
     </row>
@@ -9647,15 +10308,15 @@
         <v>76</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>809</v>
+        <v>876</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="58" t="s">
-        <v>277</v>
+        <v>308</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>810</v>
+        <v>877</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9663,7 +10324,7 @@
         <v>60</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>811</v>
+        <v>878</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -9671,335 +10332,343 @@
         <v>149</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>812</v>
+        <v>879</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="58" t="s">
-        <v>813</v>
+        <v>880</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>814</v>
+        <v>881</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B15" s="58" t="s">
-        <v>815</v>
+        <v>882</v>
       </c>
       <c r="C15" s="8" t="s">
-        <v>816</v>
+        <v>883</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="56" t="s">
-        <v>817</v>
+        <v>884</v>
       </c>
       <c r="C17" s="57"/>
     </row>
     <row r="18" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="58" t="s">
-        <v>818</v>
+        <v>885</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>819</v>
+        <v>886</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="58" t="s">
-        <v>820</v>
+        <v>887</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>821</v>
+        <v>888</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="58" t="s">
-        <v>822</v>
+        <v>889</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>823</v>
+        <v>890</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="58" t="s">
-        <v>824</v>
+        <v>891</v>
       </c>
       <c r="C21" s="8" t="s">
-        <v>825</v>
+        <v>892</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B22" s="58" t="s">
-        <v>826</v>
+        <v>893</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>827</v>
+        <v>894</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="58" t="s">
-        <v>828</v>
+        <v>895</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>829</v>
+        <v>896</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="58" t="s">
-        <v>830</v>
+        <v>897</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>831</v>
+        <v>898</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="58" t="s">
-        <v>832</v>
+        <v>899</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>833</v>
+        <v>900</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="58" t="s">
-        <v>834</v>
+        <v>901</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>835</v>
+        <v>902</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="58" t="s">
-        <v>836</v>
+        <v>903</v>
       </c>
       <c r="C27" s="8" t="s">
-        <v>837</v>
+        <v>904</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="58" t="s">
-        <v>838</v>
+        <v>905</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="56" t="s">
-        <v>840</v>
-      </c>
-      <c r="C30" s="57"/>
-    </row>
-    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="58" t="s">
-        <v>841</v>
-      </c>
-      <c r="C31" s="8" t="s">
-        <v>842</v>
-      </c>
+        <v>906</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="60" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B29" s="58" t="s">
+        <v>907</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="56" t="s">
+        <v>909</v>
+      </c>
+      <c r="C31" s="57"/>
     </row>
     <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="58" t="s">
-        <v>843</v>
+        <v>910</v>
       </c>
       <c r="C32" s="8" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="58" t="s">
-        <v>845</v>
+        <v>912</v>
       </c>
       <c r="C33" s="8" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="58" t="s">
-        <v>847</v>
+        <v>914</v>
       </c>
       <c r="C34" s="8" t="s">
-        <v>848</v>
+        <v>915</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="58" t="s">
-        <v>849</v>
+        <v>916</v>
       </c>
       <c r="C35" s="8" t="s">
-        <v>850</v>
+        <v>917</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="58" t="s">
-        <v>851</v>
+        <v>918</v>
       </c>
       <c r="C36" s="8" t="s">
-        <v>852</v>
+        <v>919</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B37" s="58" t="s">
-        <v>853</v>
+        <v>920</v>
       </c>
       <c r="C37" s="8" t="s">
-        <v>854</v>
+        <v>921</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="58" t="s">
-        <v>855</v>
+        <v>922</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="56" t="s">
-        <v>857</v>
-      </c>
-      <c r="C40" s="57"/>
-    </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="58" t="s">
-        <v>858</v>
-      </c>
-      <c r="C41" s="8" t="s">
-        <v>859</v>
-      </c>
+        <v>923</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="58" t="s">
+        <v>924</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="56" t="s">
+        <v>926</v>
+      </c>
+      <c r="C41" s="57"/>
     </row>
     <row r="42" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B42" s="58" t="s">
-        <v>860</v>
+        <v>927</v>
       </c>
       <c r="C42" s="8" t="s">
-        <v>861</v>
+        <v>928</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B43" s="58" t="s">
-        <v>862</v>
+        <v>929</v>
       </c>
       <c r="C43" s="8" t="s">
-        <v>863</v>
+        <v>930</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B44" s="58" t="s">
-        <v>864</v>
+        <v>931</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>865</v>
+        <v>932</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B45" s="58" t="s">
-        <v>866</v>
+        <v>933</v>
       </c>
       <c r="C45" s="8" t="s">
-        <v>867</v>
+        <v>934</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B46" s="58" t="s">
-        <v>868</v>
+        <v>935</v>
       </c>
       <c r="C46" s="8" t="s">
-        <v>869</v>
+        <v>936</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B47" s="58" t="s">
-        <v>870</v>
+        <v>937</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>871</v>
+        <v>938</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B48" s="58" t="s">
-        <v>872</v>
+        <v>939</v>
       </c>
       <c r="C48" s="8" t="s">
-        <v>873</v>
+        <v>940</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B49" s="58" t="s">
-        <v>874</v>
+        <v>941</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>875</v>
+        <v>942</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B50" s="58" t="s">
-        <v>876</v>
+        <v>943</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>877</v>
+        <v>944</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B51" s="58" t="s">
-        <v>878</v>
+        <v>945</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>879</v>
+        <v>946</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B52" s="58" t="s">
-        <v>880</v>
+        <v>947</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>881</v>
+        <v>948</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B53" s="58" t="s">
-        <v>882</v>
+        <v>949</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>883</v>
+        <v>950</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B54" s="58" t="s">
-        <v>884</v>
+        <v>951</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="56" t="s">
-        <v>886</v>
-      </c>
-      <c r="C56" s="57"/>
-    </row>
-    <row r="57" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="58" t="s">
-        <v>887</v>
-      </c>
-      <c r="C57" s="8" t="s">
-        <v>888</v>
-      </c>
+        <v>952</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="58" t="s">
+        <v>953</v>
+      </c>
+      <c r="C55" s="8" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="56" t="s">
+        <v>955</v>
+      </c>
+      <c r="C57" s="57"/>
     </row>
     <row r="58" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B58" s="58" t="s">
-        <v>889</v>
+        <v>956</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B59" s="58" t="s">
-        <v>891</v>
+        <v>958</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>892</v>
+        <v>959</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="58" t="s">
+        <v>960</v>
+      </c>
+      <c r="C60" s="8" t="s">
+        <v>961</v>
       </c>
     </row>
   </sheetData>
